--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB68E30-ACB0-4B56-BECA-64376F7D14E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F94E61-9B1C-4604-BDA5-201BFC97F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4043" yWindow="4043" windowWidth="21599" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -1060,18 +1060,192 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
@@ -1096,22 +1270,16 @@
     <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
   </si>
   <si>
     <t>distr_solelc_spv_015</t>
@@ -1132,34 +1300,10 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
   </si>
   <si>
     <t>distr_solelc_spv_010</t>
@@ -1180,156 +1324,99 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w107937167-400,e_r17287657-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>e_w208749745-400,e_w156418705-400,e_ZA7-400</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w162871098-400</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400,e_w105759402-400,e_ZA31-400</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>e_w102925909-400,e_ZA24-400,e_w105759402-400,e_w98231311-400,e_ZA26-400,e_w179136373-400,e_w178968761-400</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
+  </si>
+  <si>
+    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
+  </si>
+  <si>
+    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
+  </si>
+  <si>
+    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
+  </si>
+  <si>
+    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
+  </si>
+  <si>
+    <t>e_ZA25-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>e_w156418705-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_ZA39-400</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_ZA28-765,e_w496302277-400,e_w92348290-765,e_w181366662-765</t>
+  </si>
+  <si>
+    <t>e_w685294883-400,e_w1146812331-400,e_ZA4-400,e_w1146878078-400,e_w184560833-400,e_w184552955-400,e_w156418705-400,e_ZA7-400</t>
+  </si>
+  <si>
+    <t>e_w176362710-400,e_ZA33-400,e_ZA31-400,e_ZA30-400,e_w107391770-400,e_w181284049-400,e_w167648085-400</t>
+  </si>
+  <si>
+    <t>e_ZA23-400,e_w260486370-400,e_w156418705-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
+  </si>
+  <si>
+    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
+  </si>
+  <si>
     <t>e_w102682082-400,e_w177800991-400</t>
   </si>
   <si>
@@ -1345,13 +1432,10 @@
     <t>e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
   </si>
   <si>
-    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
-  </si>
-  <si>
-    <t>e_w156418705-400,e_ZA11-400</t>
+    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
+  </si>
+  <si>
+    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
   </si>
   <si>
     <t>e_w90454383-400,e_w169647963-400</t>
@@ -1363,19 +1447,7 @@
     <t>e_w107391770-400,e_w120941269-400,e_w219596295-400</t>
   </si>
   <si>
-    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_ZA24-400,e_w105759402-400,e_w98231311-400,e_ZA26-400,e_w179136373-400,e_w178968761-400</t>
+    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
   </si>
   <si>
     <t>e_w836844162-400,e_w107431792-400,e_w545652232-400,e_ZA43-400,e_w182042518-400,e_w193978748-400</t>
@@ -1387,76 +1459,190 @@
     <t>e_w208749745-400,e_ZA7-400,e_w156418705-400</t>
   </si>
   <si>
-    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
-  </si>
-  <si>
-    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w162871098-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400,e_w105759402-400,e_ZA31-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
-  </si>
-  <si>
-    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_r17287657-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400,e_w156418705-400,e_ZA7-400</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_ZA39-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_ZA28-765,e_w496302277-400,e_w92348290-765,e_w181366662-765</t>
-  </si>
-  <si>
-    <t>e_w685294883-400,e_w1146812331-400,e_ZA4-400,e_w1146878078-400,e_w184560833-400,e_w184552955-400,e_w156418705-400,e_ZA7-400</t>
-  </si>
-  <si>
-    <t>e_w176362710-400,e_ZA33-400,e_ZA31-400,e_ZA30-400,e_w107391770-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>e_ZA23-400,e_w260486370-400,e_w156418705-400,e_ZA11-400</t>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_024</t>
@@ -1465,70 +1651,52 @@
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
   </si>
   <si>
     <t>distr_wonelc_won_037</t>
@@ -1543,172 +1711,184 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400,e_ZA26-400,e_w179136373-400,e_w104080393-400,e_w213181313-400</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400</t>
+  </si>
+  <si>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_w200757306-400,e_ZA28-765,e_w181366662-400,e_w92348290-765,e_w181366662-765</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w162871098-400,e_w125754107-400</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_w934819484-400,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400,e_w89637370-400,e_w142414070-400,e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400,e_w663042845-400</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400,e_w230551819-400,e_ZA2-400,e_ZA14-400,e_w685294883-400,e_w170672051-400</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
   </si>
   <si>
     <t>elc_won_024</t>
@@ -1717,67 +1897,52 @@
     <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w182408147-400</t>
   </si>
   <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400,e_ZA26-400,e_w179136373-400,e_w104080393-400,e_w213181313-400</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400,e_w92348290-765</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
   </si>
   <si>
     <t>elc_won_037</t>
@@ -1792,169 +1957,46 @@
     <t>e_ZA11-400,e_w156418705-400,e_ZA7-400,e_w208749745-400</t>
   </si>
   <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w200757306-400,e_ZA28-765,e_w181366662-400,e_w92348290-765,e_w181366662-765</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w92348290-765</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400,e_w230551819-400,e_ZA2-400,e_ZA14-400,e_w685294883-400,e_w170672051-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w162871098-400,e_w125754107-400</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400,e_w89637370-400,e_w142414070-400,e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_005</t>
@@ -1975,12 +2017,6 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_002</t>
   </si>
   <si>
@@ -1993,88 +2029,88 @@
     <t>connecting wind offshore to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_020</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w169647963-400,e_r17287657-400</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400</t>
+  </si>
+  <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
   </si>
   <si>
     <t>elc_wof_005</t>
@@ -2092,9 +2128,6 @@
     <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w131625968-400</t>
   </si>
   <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
     <t>elc_wof_002</t>
   </si>
   <si>
@@ -2107,79 +2140,46 @@
     <t>e_w102682082-400,e_w177800991-400,e_w934819484-400</t>
   </si>
   <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400,e_w102682082-400</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w934819484-400</t>
+  </si>
+  <si>
     <t>elc_wof_020</t>
   </si>
   <si>
     <t>e_w934819484-400,e_w169789536-400,e_w90454383-400</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400,e_w102682082-400</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w169647963-400,e_r17287657-400</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7505,7 +7505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A860DFC2-8764-45C8-94AD-9883EC54E772}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378C9409-619D-4E7F-AA54-753B64A3BB1C}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7743,16 +7743,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99456731509164431</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB11">
-        <v>99.599223319854588</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7785,10 +7785,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99576662598769528</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP11">
-        <v>77.611856892252987</v>
+        <v>59.260154763351615</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7818,13 +7818,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>532</v>
+        <v>568</v>
       </c>
       <c r="BC11">
-        <v>0.99581145929743231</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD11">
-        <v>76.789912880408167</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7889,16 +7889,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99635213764962971</v>
+        <v>0.99565105035038126</v>
       </c>
       <c r="AB12">
-        <v>66.877476423454894</v>
+        <v>79.730743576343073</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7931,10 +7931,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99676762792199902</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP12">
-        <v>59.260154763351615</v>
+        <v>90.729435350939028</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7967,10 +7967,10 @@
         <v>651</v>
       </c>
       <c r="BC12">
-        <v>0.99582070241731502</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD12">
-        <v>76.620455682557321</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8035,16 +8035,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99331818519922233</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB13">
-        <v>122.49993801425808</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8077,10 +8077,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99468222901836267</v>
+        <v>0.9979252881755144</v>
       </c>
       <c r="AP13">
-        <v>97.492467996683757</v>
+        <v>38.036383448902463</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8113,10 +8113,10 @@
         <v>653</v>
       </c>
       <c r="BC13">
-        <v>0.99501631001524238</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD13">
-        <v>91.367649720556983</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8181,16 +8181,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99849240016674334</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB14">
-        <v>27.639330276371737</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8223,10 +8223,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.98687966194564902</v>
+        <v>0.99509878714312805</v>
       </c>
       <c r="AP14">
-        <v>240.53953099643502</v>
+        <v>89.85556904265141</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8256,13 +8256,13 @@
         <v>654</v>
       </c>
       <c r="BB14" t="s">
-        <v>540</v>
+        <v>655</v>
       </c>
       <c r="BC14">
-        <v>0.99507162964364948</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD14">
-        <v>90.353456533092867</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8327,16 +8327,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99484635552608569</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB15">
-        <v>94.483482021761333</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8369,10 +8369,10 @@
         <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.98860885963065015</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP15">
-        <v>208.83757343808102</v>
+        <v>150.6984130259078</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8399,16 +8399,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB15" t="s">
-        <v>656</v>
+        <v>436</v>
       </c>
       <c r="BC15">
-        <v>0.991900752046595</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD15">
-        <v>148.48621247909063</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8473,16 +8473,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99341896335341162</v>
+        <v>0.99599691424900794</v>
       </c>
       <c r="AB16">
-        <v>120.65233852078616</v>
+        <v>73.389905434855194</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8515,10 +8515,10 @@
         <v>538</v>
       </c>
       <c r="AO16">
-        <v>0.99164055829901554</v>
+        <v>0.99333523291287673</v>
       </c>
       <c r="AP16">
-        <v>153.25643118471478</v>
+        <v>122.18739659725948</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8551,10 +8551,10 @@
         <v>658</v>
       </c>
       <c r="BC16">
-        <v>0.99231435496704667</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD16">
-        <v>140.90349227081035</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8619,16 +8619,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>305</v>
+        <v>266</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99315245009067388</v>
+        <v>0.99297090277863642</v>
       </c>
       <c r="AB17">
-        <v>125.5384150043114</v>
+        <v>128.86678239166531</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8661,10 +8661,10 @@
         <v>540</v>
       </c>
       <c r="AO17">
-        <v>0.99692167417445865</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP17">
-        <v>56.43597346825765</v>
+        <v>146.36407875211563</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8697,10 +8697,10 @@
         <v>660</v>
       </c>
       <c r="BC17">
-        <v>0.99229811324031303</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD17">
-        <v>141.20125726092687</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8765,16 +8765,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99197366299435197</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB18">
-        <v>147.14951177021345</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8807,10 +8807,10 @@
         <v>542</v>
       </c>
       <c r="AO18">
-        <v>0.99677069953771458</v>
+        <v>0.9960576359591049</v>
       </c>
       <c r="AP18">
-        <v>59.203841808565592</v>
+        <v>72.276674083075989</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,13 +8840,13 @@
         <v>661</v>
       </c>
       <c r="BB18" t="s">
-        <v>426</v>
+        <v>560</v>
       </c>
       <c r="BC18">
-        <v>0.98830355217046739</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD18">
-        <v>214.43487687476414</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8911,16 +8911,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99399085439572143</v>
+        <v>0.99681605507557702</v>
       </c>
       <c r="AB19">
-        <v>110.16766941177411</v>
+        <v>58.372323614420687</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8953,10 +8953,10 @@
         <v>544</v>
       </c>
       <c r="AO19">
-        <v>0.99398790580290575</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP19">
-        <v>110.2217269467279</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8989,10 +8989,10 @@
         <v>663</v>
       </c>
       <c r="BC19">
-        <v>0.98743040674179927</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD19">
-        <v>230.44254306701379</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99601337563103476</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB20">
-        <v>73.088113431029612</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9099,10 +9099,10 @@
         <v>546</v>
       </c>
       <c r="AO20">
-        <v>0.99646273950702013</v>
+        <v>0.99515836501188337</v>
       </c>
       <c r="AP20">
-        <v>64.84977570462992</v>
+        <v>88.763308115471318</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9135,10 +9135,10 @@
         <v>665</v>
       </c>
       <c r="BC20">
-        <v>0.99279657608325511</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD20">
-        <v>132.06277180699064</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9203,16 +9203,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99758018972146978</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB21">
-        <v>44.363188439721</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9242,13 +9242,13 @@
         <v>547</v>
       </c>
       <c r="AN21" t="s">
-        <v>434</v>
+        <v>548</v>
       </c>
       <c r="AO21">
-        <v>0.99599400380931946</v>
+        <v>0.99399231910847008</v>
       </c>
       <c r="AP21">
-        <v>73.443263495810669</v>
+        <v>110.14081634471604</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,13 +9278,13 @@
         <v>666</v>
       </c>
       <c r="BB21" t="s">
-        <v>532</v>
+        <v>667</v>
       </c>
       <c r="BC21">
-        <v>0.99223220184557481</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD21">
-        <v>142.40963283112865</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9349,16 +9349,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99299045119957896</v>
+        <v>0.99672872587342576</v>
       </c>
       <c r="AB22">
-        <v>128.50839467438524</v>
+        <v>59.973358987194473</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9385,16 +9385,16 @@
         <v>465</v>
       </c>
       <c r="AM22" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN22" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO22">
-        <v>0.99788320682147802</v>
+        <v>0.99398790580290575</v>
       </c>
       <c r="AP22">
-        <v>38.807874939569167</v>
+        <v>110.2217269467279</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9421,16 +9421,16 @@
         <v>631</v>
       </c>
       <c r="BA22" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="BB22" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="BC22">
-        <v>0.99429876975975018</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD22">
-        <v>104.52255440457925</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9495,16 +9495,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99495781957805363</v>
+        <v>0.99450846292949968</v>
       </c>
       <c r="AB23">
-        <v>92.439974402351027</v>
+        <v>100.67817962584009</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9531,16 +9531,16 @@
         <v>467</v>
       </c>
       <c r="AM23" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO23">
-        <v>0.99504825389388352</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP23">
-        <v>90.782011945468795</v>
+        <v>64.84977570462992</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9567,16 +9567,16 @@
         <v>633</v>
       </c>
       <c r="BA23" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="BB23" t="s">
-        <v>670</v>
+        <v>560</v>
       </c>
       <c r="BC23">
-        <v>0.99672758029478525</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD23">
-        <v>59.994361262269514</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9641,16 +9641,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99672872587342576</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB24">
-        <v>59.973358987194473</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9677,16 +9677,16 @@
         <v>469</v>
       </c>
       <c r="AM24" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN24" t="s">
-        <v>553</v>
+        <v>414</v>
       </c>
       <c r="AO24">
-        <v>0.99247550518926964</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP24">
-        <v>137.94907153005732</v>
+        <v>73.443263495810669</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9719,10 +9719,10 @@
         <v>672</v>
       </c>
       <c r="BC24">
-        <v>0.98805842341846151</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD24">
-        <v>218.92890399487229</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9787,16 +9787,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99466941924265306</v>
+        <v>0.99493070276109996</v>
       </c>
       <c r="AB25">
-        <v>97.727313884694652</v>
+        <v>92.937116046500407</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9829,10 +9829,10 @@
         <v>555</v>
       </c>
       <c r="AO25">
-        <v>0.99333523291287673</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP25">
-        <v>122.18739659725948</v>
+        <v>38.807874939569167</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9865,10 +9865,10 @@
         <v>674</v>
       </c>
       <c r="BC25">
-        <v>0.99462081464868646</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD25">
-        <v>98.618398107414592</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9933,16 +9933,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99599691424900794</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB26">
-        <v>73.389905434855194</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9975,10 +9975,10 @@
         <v>557</v>
       </c>
       <c r="AO26">
-        <v>0.99201650479533909</v>
+        <v>0.99576958396989479</v>
       </c>
       <c r="AP26">
-        <v>146.36407875211563</v>
+        <v>77.557627218594661</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10011,10 +10011,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.99447517161328947</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD26">
-        <v>101.28852042302684</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10079,16 +10079,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99715230385125297</v>
+        <v>0.99520836470773288</v>
       </c>
       <c r="AB27">
-        <v>52.207762727027884</v>
+        <v>87.846647024897322</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10118,13 +10118,13 @@
         <v>558</v>
       </c>
       <c r="AN27" t="s">
-        <v>559</v>
+        <v>401</v>
       </c>
       <c r="AO27">
-        <v>0.99433440313430599</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP27">
-        <v>103.86927587105613</v>
+        <v>92.557267939235231</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10154,13 +10154,13 @@
         <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>678</v>
+        <v>423</v>
       </c>
       <c r="BC27">
-        <v>0.99481516601444531</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD27">
-        <v>95.055289735168813</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10225,16 +10225,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99545552704228712</v>
+        <v>0.99492063738174197</v>
       </c>
       <c r="AB28">
-        <v>83.315337558069643</v>
+        <v>93.121648001396338</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10261,16 +10261,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
+        <v>559</v>
+      </c>
+      <c r="AN28" t="s">
         <v>560</v>
       </c>
-      <c r="AN28" t="s">
-        <v>561</v>
-      </c>
       <c r="AO28">
-        <v>0.99165427860211908</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP28">
-        <v>153.00489229448431</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10297,16 +10297,16 @@
         <v>643</v>
       </c>
       <c r="BA28" t="s">
+        <v>678</v>
+      </c>
+      <c r="BB28" t="s">
         <v>679</v>
       </c>
-      <c r="BB28" t="s">
-        <v>680</v>
-      </c>
       <c r="BC28">
-        <v>0.99545422785121029</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD28">
-        <v>83.33915606114418</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10371,16 +10371,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.9895807450862778</v>
+        <v>0.99698749491520611</v>
       </c>
       <c r="AB29">
-        <v>191.01967341824059</v>
+        <v>55.229259887887068</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10407,16 +10407,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AN29" t="s">
         <v>562</v>
       </c>
-      <c r="AN29" t="s">
-        <v>563</v>
-      </c>
       <c r="AO29">
-        <v>0.99572967547870339</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP29">
-        <v>78.289282890438841</v>
+        <v>240.53953099643502</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10443,16 +10443,16 @@
         <v>645</v>
       </c>
       <c r="BA29" t="s">
+        <v>680</v>
+      </c>
+      <c r="BB29" t="s">
         <v>681</v>
       </c>
-      <c r="BB29" t="s">
-        <v>682</v>
-      </c>
       <c r="BC29">
-        <v>0.98843991010136767</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD29">
-        <v>211.93498147492642</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10517,16 +10517,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99536059527709431</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB30">
-        <v>85.055753253270055</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10553,16 +10553,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
+        <v>563</v>
+      </c>
+      <c r="AN30" t="s">
         <v>564</v>
       </c>
-      <c r="AN30" t="s">
-        <v>565</v>
-      </c>
       <c r="AO30">
-        <v>0.99620690928326405</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP30">
-        <v>69.53999647349201</v>
+        <v>208.83757343808102</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10589,16 +10589,16 @@
         <v>647</v>
       </c>
       <c r="BA30" t="s">
+        <v>682</v>
+      </c>
+      <c r="BB30" t="s">
         <v>683</v>
       </c>
-      <c r="BB30" t="s">
-        <v>408</v>
-      </c>
       <c r="BC30">
-        <v>0.99010219056094972</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD30">
-        <v>181.45983971592244</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10663,16 +10663,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99695083910621241</v>
+        <v>0.99567492323161799</v>
       </c>
       <c r="AB31">
-        <v>55.901283052772143</v>
+        <v>79.293074087003873</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10699,16 +10699,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
+        <v>565</v>
+      </c>
+      <c r="AN31" t="s">
         <v>566</v>
       </c>
-      <c r="AN31" t="s">
-        <v>567</v>
-      </c>
       <c r="AO31">
-        <v>0.99830579859179591</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP31">
-        <v>31.060359150407386</v>
+        <v>153.25643118471478</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10773,16 +10773,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99464845307754257</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB32">
-        <v>98.111693578387175</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10809,16 +10809,16 @@
         <v>485</v>
       </c>
       <c r="AM32" t="s">
+        <v>567</v>
+      </c>
+      <c r="AN32" t="s">
         <v>568</v>
       </c>
-      <c r="AN32" t="s">
-        <v>569</v>
-      </c>
       <c r="AO32">
-        <v>0.9951764810877296</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP32">
-        <v>88.431180058290352</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10883,16 +10883,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.9951066982538278</v>
+        <v>0.99315245009067388</v>
       </c>
       <c r="AB33">
-        <v>89.710532013157362</v>
+        <v>125.5384150043114</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10919,16 +10919,16 @@
         <v>487</v>
       </c>
       <c r="AM33" t="s">
+        <v>569</v>
+      </c>
+      <c r="AN33" t="s">
         <v>570</v>
       </c>
-      <c r="AN33" t="s">
-        <v>571</v>
-      </c>
       <c r="AO33">
-        <v>0.99606892759117205</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP33">
-        <v>72.069660828511601</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10993,16 +10993,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99297090277863642</v>
+        <v>0.99590798933590385</v>
       </c>
       <c r="AB34">
-        <v>128.86678239166531</v>
+        <v>75.020195508429936</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11029,16 +11029,16 @@
         <v>489</v>
       </c>
       <c r="AM34" t="s">
+        <v>571</v>
+      </c>
+      <c r="AN34" t="s">
         <v>572</v>
       </c>
-      <c r="AN34" t="s">
-        <v>573</v>
-      </c>
       <c r="AO34">
-        <v>0.99824683646529189</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP34">
-        <v>32.141331469648897</v>
+        <v>83.095996952896456</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11103,16 +11103,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>301</v>
+        <v>270</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99726845868655478</v>
+        <v>0.99588491419783987</v>
       </c>
       <c r="AB35">
-        <v>50.078257413162468</v>
+        <v>75.443239706269793</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11139,16 +11139,16 @@
         <v>491</v>
       </c>
       <c r="AM35" t="s">
+        <v>573</v>
+      </c>
+      <c r="AN35" t="s">
         <v>574</v>
       </c>
-      <c r="AN35" t="s">
-        <v>575</v>
-      </c>
       <c r="AO35">
-        <v>0.99546749107529653</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP35">
-        <v>83.095996952896456</v>
+        <v>72.069660828511601</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11213,16 +11213,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99681605507557702</v>
+        <v>0.99021378007306371</v>
       </c>
       <c r="AB36">
-        <v>58.372323614420687</v>
+        <v>179.41403199383166</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11249,16 +11249,16 @@
         <v>493</v>
       </c>
       <c r="AM36" t="s">
+        <v>575</v>
+      </c>
+      <c r="AN36" t="s">
         <v>576</v>
       </c>
-      <c r="AN36" t="s">
-        <v>577</v>
-      </c>
       <c r="AO36">
-        <v>0.99509878714312805</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP36">
-        <v>89.85556904265141</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11323,16 +11323,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99590798933590385</v>
+        <v>0.99315447263323475</v>
       </c>
       <c r="AB37">
-        <v>75.020195508429936</v>
+        <v>125.50133505736341</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11359,16 +11359,16 @@
         <v>495</v>
       </c>
       <c r="AM37" t="s">
+        <v>577</v>
+      </c>
+      <c r="AN37" t="s">
         <v>578</v>
       </c>
-      <c r="AN37" t="s">
-        <v>579</v>
-      </c>
       <c r="AO37">
-        <v>0.99178008656222316</v>
+        <v>0.99606896061575723</v>
       </c>
       <c r="AP37">
-        <v>150.6984130259078</v>
+        <v>72.069055377783442</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11433,16 +11433,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>270</v>
+        <v>302</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99588491419783987</v>
+        <v>0.99649986768340049</v>
       </c>
       <c r="AB38">
-        <v>75.443239706269793</v>
+        <v>64.16909247099106</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11469,16 +11469,16 @@
         <v>497</v>
       </c>
       <c r="AM38" t="s">
+        <v>579</v>
+      </c>
+      <c r="AN38" t="s">
         <v>580</v>
       </c>
-      <c r="AN38" t="s">
-        <v>581</v>
-      </c>
       <c r="AO38">
-        <v>0.99606896061575723</v>
+        <v>0.99415308404615776</v>
       </c>
       <c r="AP38">
-        <v>72.069055377783442</v>
+        <v>107.19345915377383</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11543,16 +11543,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99021378007306371</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB39">
-        <v>179.41403199383166</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11579,16 +11579,16 @@
         <v>499</v>
       </c>
       <c r="AM39" t="s">
+        <v>581</v>
+      </c>
+      <c r="AN39" t="s">
         <v>582</v>
       </c>
-      <c r="AN39" t="s">
-        <v>583</v>
-      </c>
       <c r="AO39">
-        <v>0.99415308404615776</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP39">
-        <v>107.19345915377383</v>
+        <v>77.236409972479407</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11653,16 +11653,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99315447263323475</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB40">
-        <v>125.50133505736341</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11689,16 +11689,16 @@
         <v>501</v>
       </c>
       <c r="AM40" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN40" t="s">
         <v>584</v>
       </c>
-      <c r="AN40" t="s">
-        <v>585</v>
-      </c>
       <c r="AO40">
-        <v>0.99578710491059208</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP40">
-        <v>77.236409972479407</v>
+        <v>29.627234098515917</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11763,16 +11763,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99649986768340049</v>
+        <v>0.99635213764962971</v>
       </c>
       <c r="AB41">
-        <v>64.16909247099106</v>
+        <v>66.877476423454894</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11799,16 +11799,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
+        <v>585</v>
+      </c>
+      <c r="AN41" t="s">
         <v>586</v>
       </c>
-      <c r="AN41" t="s">
-        <v>587</v>
-      </c>
       <c r="AO41">
-        <v>0.99838396904917182</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP41">
-        <v>29.627234098515917</v>
+        <v>37.384485603890518</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11873,16 +11873,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99827081845920873</v>
+        <v>0.99331818519922233</v>
       </c>
       <c r="AB42">
-        <v>31.701661581174136</v>
+        <v>122.49993801425808</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11909,16 +11909,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
+        <v>587</v>
+      </c>
+      <c r="AN42" t="s">
         <v>588</v>
       </c>
-      <c r="AN42" t="s">
-        <v>589</v>
-      </c>
       <c r="AO42">
-        <v>0.99796084623978776</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP42">
-        <v>37.384485603890518</v>
+        <v>77.611856892252987</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11983,16 +11983,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99450846292949968</v>
+        <v>0.99849240016674334</v>
       </c>
       <c r="AB43">
-        <v>100.67817962584009</v>
+        <v>27.639330276371737</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12019,16 +12019,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
+        <v>589</v>
+      </c>
+      <c r="AN43" t="s">
         <v>590</v>
       </c>
-      <c r="AN43" t="s">
-        <v>591</v>
-      </c>
       <c r="AO43">
-        <v>0.99505112170813059</v>
+        <v>0.99433440313430599</v>
       </c>
       <c r="AP43">
-        <v>90.729435350939028</v>
+        <v>103.86927587105613</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12093,16 +12093,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.98298990306503153</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB44">
-        <v>311.85177714108931</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12129,16 +12129,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
+        <v>591</v>
+      </c>
+      <c r="AN44" t="s">
         <v>592</v>
       </c>
-      <c r="AN44" t="s">
-        <v>593</v>
-      </c>
       <c r="AO44">
-        <v>0.9979252881755144</v>
+        <v>0.99165427860211908</v>
       </c>
       <c r="AP44">
-        <v>38.036383448902463</v>
+        <v>153.00489229448431</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12203,16 +12203,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>299</v>
+        <v>267</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99493070276109996</v>
+        <v>0.99536059527709431</v>
       </c>
       <c r="AB45">
-        <v>92.937116046500407</v>
+        <v>85.055753253270055</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12239,16 +12239,16 @@
         <v>511</v>
       </c>
       <c r="AM45" t="s">
+        <v>593</v>
+      </c>
+      <c r="AN45" t="s">
         <v>594</v>
       </c>
-      <c r="AN45" t="s">
-        <v>595</v>
-      </c>
       <c r="AO45">
-        <v>0.9960576359591049</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP45">
-        <v>72.276674083075989</v>
+        <v>78.289282890438841</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12313,16 +12313,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99615584710269711</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB46">
-        <v>70.476136450553028</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12349,16 +12349,16 @@
         <v>513</v>
       </c>
       <c r="AM46" t="s">
+        <v>595</v>
+      </c>
+      <c r="AN46" t="s">
         <v>596</v>
       </c>
-      <c r="AN46" t="s">
-        <v>597</v>
-      </c>
       <c r="AO46">
-        <v>0.99514523900053742</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP46">
-        <v>89.003951656813172</v>
+        <v>69.53999647349201</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12423,16 +12423,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99565105035038126</v>
+        <v>0.99399085439572143</v>
       </c>
       <c r="AB47">
-        <v>79.730743576343073</v>
+        <v>110.16766941177411</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12459,16 +12459,16 @@
         <v>515</v>
       </c>
       <c r="AM47" t="s">
+        <v>597</v>
+      </c>
+      <c r="AN47" t="s">
         <v>598</v>
       </c>
-      <c r="AN47" t="s">
-        <v>599</v>
-      </c>
       <c r="AO47">
-        <v>0.99515836501188337</v>
+        <v>0.99830579859179591</v>
       </c>
       <c r="AP47">
-        <v>88.763308115471318</v>
+        <v>31.060359150407386</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12533,16 +12533,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99528373638972145</v>
+        <v>0.99601337563103476</v>
       </c>
       <c r="AB48">
-        <v>86.464832855106309</v>
+        <v>73.088113431029612</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12569,16 +12569,16 @@
         <v>517</v>
       </c>
       <c r="AM48" t="s">
+        <v>599</v>
+      </c>
+      <c r="AN48" t="s">
         <v>600</v>
       </c>
-      <c r="AN48" t="s">
-        <v>601</v>
-      </c>
       <c r="AO48">
-        <v>0.99399231910847008</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP48">
-        <v>110.14081634471604</v>
+        <v>88.431180058290352</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12643,16 +12643,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99520836470773288</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB49">
-        <v>87.846647024897322</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12679,16 +12679,16 @@
         <v>519</v>
       </c>
       <c r="AM49" t="s">
+        <v>601</v>
+      </c>
+      <c r="AN49" t="s">
         <v>602</v>
       </c>
-      <c r="AN49" t="s">
-        <v>603</v>
-      </c>
       <c r="AO49">
-        <v>0.99576958396989479</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP49">
-        <v>77.557627218594661</v>
+        <v>75.626528315847352</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12753,16 +12753,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>269</v>
+        <v>303</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99492063738174197</v>
+        <v>0.99528373638972145</v>
       </c>
       <c r="AB50">
-        <v>93.121648001396338</v>
+        <v>86.464832855106309</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12789,16 +12789,16 @@
         <v>521</v>
       </c>
       <c r="AM50" t="s">
+        <v>603</v>
+      </c>
+      <c r="AN50" t="s">
         <v>604</v>
       </c>
-      <c r="AN50" t="s">
-        <v>436</v>
-      </c>
       <c r="AO50">
-        <v>0.99495142174876894</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP50">
-        <v>92.557267939235231</v>
+        <v>100.63855719912947</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12863,16 +12863,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99698749491520611</v>
+        <v>0.99715230385125297</v>
       </c>
       <c r="AB51">
-        <v>55.229259887887068</v>
+        <v>52.207762727027884</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12905,10 +12905,10 @@
         <v>606</v>
       </c>
       <c r="AO51">
-        <v>0.99587491663731742</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP51">
-        <v>75.626528315847352</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12973,16 +12973,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99766238113026029</v>
+        <v>0.99545552704228712</v>
       </c>
       <c r="AB52">
-        <v>42.856345945228725</v>
+        <v>83.315337558069643</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13015,10 +13015,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.9945106241527748</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP52">
-        <v>100.63855719912947</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13083,16 +13083,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99567492323161799</v>
+        <v>0.9895807450862778</v>
       </c>
       <c r="AB53">
-        <v>79.293074087003873</v>
+        <v>191.01967341824059</v>
       </c>
     </row>
   </sheetData>
@@ -13101,7 +13101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05A54B08-349C-4532-B9F9-7BC6B40E43DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AF16AC-D37C-4468-BB19-E9B31F4C3BAB}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13213,7 +13213,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13246,7 +13246,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>677</v>
+        <v>657</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13281,7 +13281,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>600</v>
+        <v>547</v>
       </c>
       <c r="L12">
         <v>41.625170147271362</v>
@@ -13314,7 +13314,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13349,7 +13349,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>596</v>
+        <v>543</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13382,7 +13382,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>679</v>
+        <v>659</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13417,7 +13417,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13450,7 +13450,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13485,7 +13485,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L15">
         <v>14.248215224493222</v>
@@ -13518,7 +13518,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13553,7 +13553,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>576</v>
+        <v>533</v>
       </c>
       <c r="L16">
         <v>60.246276232111249</v>
@@ -13586,7 +13586,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13621,7 +13621,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>537</v>
+        <v>565</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13654,7 +13654,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13689,7 +13689,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13722,7 +13722,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13757,7 +13757,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>566</v>
+        <v>597</v>
       </c>
       <c r="L19">
         <v>15.921767829784981</v>
@@ -13790,7 +13790,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13825,7 +13825,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>541</v>
+        <v>569</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13858,7 +13858,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13893,7 +13893,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>592</v>
+        <v>531</v>
       </c>
       <c r="L21">
         <v>11.156586435503245</v>
@@ -13926,7 +13926,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>675</v>
+        <v>652</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13961,7 +13961,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>602</v>
+        <v>556</v>
       </c>
       <c r="L22">
         <v>6.3773535033999496</v>
@@ -13994,7 +13994,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14029,7 +14029,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>598</v>
+        <v>545</v>
       </c>
       <c r="L23">
         <v>4.8861340927283274</v>
@@ -14062,7 +14062,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>681</v>
+        <v>654</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14097,7 +14097,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="L24">
         <v>13.571087213989722</v>
@@ -14130,7 +14130,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14165,7 +14165,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14198,7 +14198,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14233,7 +14233,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>568</v>
+        <v>599</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14266,7 +14266,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14301,7 +14301,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>539</v>
+        <v>567</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14334,7 +14334,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>683</v>
+        <v>656</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14369,7 +14369,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>564</v>
+        <v>595</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14402,7 +14402,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>673</v>
+        <v>650</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14437,7 +14437,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14470,7 +14470,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14505,7 +14505,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>604</v>
+        <v>558</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14538,7 +14538,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>659</v>
+        <v>682</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14573,7 +14573,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>552</v>
+        <v>607</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14608,7 +14608,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14643,7 +14643,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>590</v>
+        <v>529</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14678,7 +14678,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>527</v>
+        <v>587</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14713,7 +14713,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14748,7 +14748,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14783,7 +14783,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14818,7 +14818,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14853,7 +14853,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>554</v>
+        <v>537</v>
       </c>
       <c r="L39">
         <v>26.32580391715549</v>
@@ -14888,7 +14888,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>556</v>
+        <v>539</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14923,7 +14923,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>562</v>
+        <v>593</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14958,7 +14958,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>535</v>
+        <v>563</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14993,7 +14993,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>578</v>
+        <v>535</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15028,7 +15028,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15063,7 +15063,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="L45">
         <v>11.262860315683808</v>
@@ -15098,7 +15098,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>594</v>
+        <v>541</v>
       </c>
       <c r="L46">
         <v>34.610640160809844</v>
@@ -15133,7 +15133,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>550</v>
+        <v>605</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15168,7 +15168,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>531</v>
+        <v>559</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15203,7 +15203,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="L49">
         <v>63.11239557797159</v>
@@ -15238,7 +15238,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="L50">
         <v>38.222782480143309</v>
@@ -15273,7 +15273,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15308,7 +15308,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15323,7 +15323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EAA025B-C668-4E4C-9D02-BA54DAA3482A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B960E65-D6C2-4E9C-AD54-75C4A8E44757}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17140,7 +17140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACA29F99-4719-4A38-A680-FF44FC87B6D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD756840-1B04-4CB8-9377-1AC392DAF6C5}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{72F94E61-9B1C-4604-BDA5-201BFC97F104}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C271548F-F627-43F4-BB3A-1A5446F7890E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,24 +1060,192 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_034</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 34</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_025</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_014</t>
   </si>
   <si>
@@ -1090,6 +1258,60 @@
     <t>connecting solar to buses in cluster 33</t>
   </si>
   <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_016</t>
   </si>
   <si>
@@ -1102,361 +1324,337 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w102682082-400,e_w177800991-400</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400,e_w586032034-765</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w167590549-400</t>
+  </si>
+  <si>
+    <t>e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
+  </si>
+  <si>
+    <t>e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w169647963-400</t>
+  </si>
+  <si>
+    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>e_w107391770-400,e_w120941269-400,e_w219596295-400</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_ZA39-400</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_ZA28-765,e_w496302277-400,e_w92348290-765,e_w181366662-765</t>
+  </si>
+  <si>
+    <t>e_w685294883-400,e_w1146812331-400,e_ZA4-400,e_w1146878078-400,e_w184560833-400,e_w184552955-400,e_w156418705-400,e_ZA7-400</t>
+  </si>
+  <si>
+    <t>e_w176362710-400,e_ZA33-400,e_ZA31-400,e_ZA30-400,e_w107391770-400,e_w181284049-400,e_w167648085-400</t>
+  </si>
+  <si>
+    <t>e_ZA23-400,e_w260486370-400,e_w156418705-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>e_w836844162-400,e_w107431792-400,e_w545652232-400,e_ZA43-400,e_w182042518-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_w586032034-400,e_w934819484-400,e_w586032034-765,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>e_w208749745-400,e_ZA7-400,e_w156418705-400</t>
+  </si>
+  <si>
+    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
+  </si>
+  <si>
+    <t>e_ZA25-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
     <t>e_w107937167-400,e_r17287657-400,e_w631673098-400</t>
   </si>
   <si>
     <t>e_w208749745-400,e_w156418705-400,e_ZA7-400</t>
   </si>
   <si>
+    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
+  </si>
+  <si>
+    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
+  </si>
+  <si>
+    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
+  </si>
+  <si>
+    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
+  </si>
+  <si>
+    <t>e_w156418705-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
+  </si>
+  <si>
+    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
+  </si>
+  <si>
     <t>e_w193465369-400,e_w162871098-400</t>
   </si>
   <si>
     <t>e_w631673098-400,e_w207991752-400,e_w127585817-400,e_w105759402-400,e_ZA31-400</t>
   </si>
   <si>
+    <t>e_w193465369-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
+  </si>
+  <si>
+    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
+  </si>
+  <si>
+    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
+  </si>
+  <si>
     <t>e_w90454383-400,e_w89637370-400</t>
   </si>
   <si>
     <t>e_w102925909-400,e_ZA24-400,e_w105759402-400,e_w98231311-400,e_ZA26-400,e_w179136373-400,e_w178968761-400</t>
   </si>
   <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
-  </si>
-  <si>
-    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w156418705-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_ZA39-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_ZA28-765,e_w496302277-400,e_w92348290-765,e_w181366662-765</t>
-  </si>
-  <si>
-    <t>e_w685294883-400,e_w1146812331-400,e_ZA4-400,e_w1146878078-400,e_w184560833-400,e_w184552955-400,e_w156418705-400,e_ZA7-400</t>
-  </si>
-  <si>
-    <t>e_w176362710-400,e_ZA33-400,e_ZA31-400,e_ZA30-400,e_w107391770-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>e_ZA23-400,e_w260486370-400,e_w156418705-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400,e_w586032034-765</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
-  </si>
-  <si>
-    <t>e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
-  </si>
-  <si>
-    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>e_w107391770-400,e_w120941269-400,e_w219596295-400</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
-  </si>
-  <si>
-    <t>e_w836844162-400,e_w107431792-400,e_w545652232-400,e_ZA43-400,e_w182042518-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_w586032034-400,e_w934819484-400,e_w586032034-765,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400,e_ZA7-400,e_w156418705-400</t>
+    <t>distr_wonelc_won_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wonelc_won_008</t>
@@ -1465,42 +1663,6 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_036</t>
   </si>
   <si>
@@ -1525,28 +1687,16 @@
     <t>connecting wind onshore to buses in cluster 2</t>
   </si>
   <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_012</t>
@@ -1561,154 +1711,199 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
+    <t>elc_won_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_w200757306-400,e_ZA28-765,e_w181366662-400,e_w92348290-765,e_w181366662-765</t>
+  </si>
+  <si>
+    <t>elc_won_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>elc_won_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400,e_w230551819-400,e_ZA2-400,e_ZA14-400,e_w685294883-400,e_w170672051-400</t>
+  </si>
+  <si>
+    <t>elc_won_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w182408147-400</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
+  </si>
+  <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400,e_w663042845-400</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400,e_w92348290-765</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
   </si>
   <si>
     <t>elc_won_008</t>
@@ -1717,42 +1912,6 @@
     <t>e_w105759402-400,e_ZA26-400,e_w179136373-400,e_w104080393-400,e_w213181313-400</t>
   </si>
   <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w200757306-400,e_ZA28-765,e_w181366662-400,e_w92348290-765,e_w181366662-765</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w107937167-400</t>
-  </si>
-  <si>
     <t>elc_won_036</t>
   </si>
   <si>
@@ -1777,25 +1936,16 @@
     <t>e_w89173873-400,e_w89637370-400,e_w142414070-400,e_w107937167-400,e_w631673098-400</t>
   </si>
   <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400,e_w125754107-400</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400,e_w156418705-400,e_ZA7-400,e_w208749745-400</t>
   </si>
   <si>
     <t>elc_won_012</t>
@@ -1807,154 +1957,52 @@
     <t>elc_won_020</t>
   </si>
   <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400,e_w230551819-400,e_ZA2-400,e_ZA14-400,e_w685294883-400,e_w170672051-400</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w182408147-400</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w92348290-765</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w125754107-400</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400,e_w156418705-400,e_ZA7-400,e_w208749745-400</t>
+    <t>distr_wofelc_wof_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_009</t>
@@ -1969,34 +2017,40 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_011</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wofelc_wof_005</t>
@@ -2017,66 +2071,54 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_020</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
+    <t>elc_wof_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_wof_017</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400,e_w102682082-400</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
+  </si>
+  <si>
     <t>elc_wof_009</t>
   </si>
   <si>
@@ -2086,31 +2128,37 @@
     <t>e_w90454383-400,e_w169647963-400,e_r17287657-400</t>
   </si>
   <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w934819484-400</t>
+  </si>
+  <si>
     <t>elc_wof_011</t>
   </si>
   <si>
     <t>e_w131625968-400</t>
   </si>
   <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w107431792-400,e_w193978748-400,e_w836844162-400</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w177800991-400,e_w934819484-400</t>
   </si>
   <si>
     <t>elc_wof_005</t>
@@ -2126,54 +2174,6 @@
   </si>
   <si>
     <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w131625968-400</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w107431792-400,e_w193978748-400,e_w836844162-400</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400,e_w102682082-400</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w934819484-400</t>
   </si>
   <si>
     <t>elc_wof_020</t>
@@ -7505,7 +7505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{378C9409-619D-4E7F-AA54-753B64A3BB1C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19B27A8-AD7B-406B-A39E-5E1B267765CF}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7743,16 +7743,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99615584710269711</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB11">
-        <v>70.476136450553028</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7785,10 +7785,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99676762792199902</v>
+        <v>0.99333523291287673</v>
       </c>
       <c r="AP11">
-        <v>59.260154763351615</v>
+        <v>122.18739659725948</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7818,13 +7818,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>568</v>
+        <v>650</v>
       </c>
       <c r="BC11">
-        <v>0.99507162964364948</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD11">
-        <v>90.353456533092867</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7889,16 +7889,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99565105035038126</v>
+        <v>0.99635213764962971</v>
       </c>
       <c r="AB12">
-        <v>79.730743576343073</v>
+        <v>66.877476423454894</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7931,10 +7931,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99505112170813059</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP12">
-        <v>90.729435350939028</v>
+        <v>146.36407875211563</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7961,16 +7961,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BB12" t="s">
-        <v>651</v>
+        <v>405</v>
       </c>
       <c r="BC12">
-        <v>0.99462081464868646</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD12">
-        <v>98.618398107414592</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8035,16 +8035,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99464845307754257</v>
+        <v>0.99331818519922233</v>
       </c>
       <c r="AB13">
-        <v>98.111693578387175</v>
+        <v>122.49993801425808</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8077,10 +8077,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.9979252881755144</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP13">
-        <v>38.036383448902463</v>
+        <v>83.095996952896456</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8110,13 +8110,13 @@
         <v>652</v>
       </c>
       <c r="BB13" t="s">
-        <v>653</v>
+        <v>550</v>
       </c>
       <c r="BC13">
-        <v>0.99447517161328947</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD13">
-        <v>101.28852042302684</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8181,16 +8181,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.9951066982538278</v>
+        <v>0.99849240016674334</v>
       </c>
       <c r="AB14">
-        <v>89.710532013157362</v>
+        <v>27.639330276371737</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8223,10 +8223,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.99509878714312805</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP14">
-        <v>89.85556904265141</v>
+        <v>77.611856892252987</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8253,16 +8253,16 @@
         <v>615</v>
       </c>
       <c r="BA14" t="s">
+        <v>653</v>
+      </c>
+      <c r="BB14" t="s">
         <v>654</v>
       </c>
-      <c r="BB14" t="s">
-        <v>655</v>
-      </c>
       <c r="BC14">
-        <v>0.98843991010136767</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD14">
-        <v>211.93498147492642</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8327,16 +8327,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99466941924265306</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB15">
-        <v>97.727313884694652</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8369,10 +8369,10 @@
         <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.99178008656222316</v>
+        <v>0.99606896061575723</v>
       </c>
       <c r="AP15">
-        <v>150.6984130259078</v>
+        <v>72.069055377783442</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8399,16 +8399,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
+        <v>655</v>
+      </c>
+      <c r="BB15" t="s">
         <v>656</v>
       </c>
-      <c r="BB15" t="s">
-        <v>436</v>
-      </c>
       <c r="BC15">
-        <v>0.99010219056094972</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD15">
-        <v>181.45983971592244</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8473,16 +8473,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99599691424900794</v>
+        <v>0.99399085439572143</v>
       </c>
       <c r="AB16">
-        <v>73.389905434855194</v>
+        <v>110.16766941177411</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8515,10 +8515,10 @@
         <v>538</v>
       </c>
       <c r="AO16">
-        <v>0.99333523291287673</v>
+        <v>0.99415308404615776</v>
       </c>
       <c r="AP16">
-        <v>122.18739659725948</v>
+        <v>107.19345915377383</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8551,10 +8551,10 @@
         <v>658</v>
       </c>
       <c r="BC16">
-        <v>0.99481516601444531</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD16">
-        <v>95.055289735168813</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8619,16 +8619,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99297090277863642</v>
+        <v>0.99601337563103476</v>
       </c>
       <c r="AB17">
-        <v>128.86678239166531</v>
+        <v>73.088113431029612</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8661,10 +8661,10 @@
         <v>540</v>
       </c>
       <c r="AO17">
-        <v>0.99201650479533909</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP17">
-        <v>146.36407875211563</v>
+        <v>77.236409972479407</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8697,10 +8697,10 @@
         <v>660</v>
       </c>
       <c r="BC17">
-        <v>0.99545422785121029</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD17">
-        <v>83.33915606114418</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8765,16 +8765,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99726845868655478</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB18">
-        <v>50.078257413162468</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8807,10 +8807,10 @@
         <v>542</v>
       </c>
       <c r="AO18">
-        <v>0.9960576359591049</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP18">
-        <v>72.276674083075989</v>
+        <v>29.627234098515917</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,13 +8840,13 @@
         <v>661</v>
       </c>
       <c r="BB18" t="s">
-        <v>560</v>
+        <v>662</v>
       </c>
       <c r="BC18">
-        <v>0.99581145929743231</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD18">
-        <v>76.789912880408167</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8911,16 +8911,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99681605507557702</v>
+        <v>0.99520836470773288</v>
       </c>
       <c r="AB19">
-        <v>58.372323614420687</v>
+        <v>87.846647024897322</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8953,10 +8953,10 @@
         <v>544</v>
       </c>
       <c r="AO19">
-        <v>0.99514523900053742</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP19">
-        <v>89.003951656813172</v>
+        <v>37.384485603890518</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8983,16 +8983,16 @@
         <v>625</v>
       </c>
       <c r="BA19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="BB19" t="s">
-        <v>663</v>
+        <v>558</v>
       </c>
       <c r="BC19">
-        <v>0.99582070241731502</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD19">
-        <v>76.620455682557321</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99299045119957896</v>
+        <v>0.99492063738174197</v>
       </c>
       <c r="AB20">
-        <v>128.50839467438524</v>
+        <v>93.121648001396338</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9099,10 +9099,10 @@
         <v>546</v>
       </c>
       <c r="AO20">
-        <v>0.99515836501188337</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP20">
-        <v>88.763308115471318</v>
+        <v>75.626528315847352</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9135,10 +9135,10 @@
         <v>665</v>
       </c>
       <c r="BC20">
-        <v>0.99501631001524238</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD20">
-        <v>91.367649720556983</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9203,16 +9203,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99495781957805363</v>
+        <v>0.99698749491520611</v>
       </c>
       <c r="AB21">
-        <v>92.439974402351027</v>
+        <v>55.229259887887068</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9245,10 +9245,10 @@
         <v>548</v>
       </c>
       <c r="AO21">
-        <v>0.99399231910847008</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP21">
-        <v>110.14081634471604</v>
+        <v>100.63855719912947</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,13 +9278,13 @@
         <v>666</v>
       </c>
       <c r="BB21" t="s">
-        <v>667</v>
+        <v>432</v>
       </c>
       <c r="BC21">
-        <v>0.991900752046595</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD21">
-        <v>148.48621247909063</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9349,16 +9349,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99672872587342576</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB22">
-        <v>59.973358987194473</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9391,10 +9391,10 @@
         <v>550</v>
       </c>
       <c r="AO22">
-        <v>0.99398790580290575</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP22">
-        <v>110.2217269467279</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9421,16 +9421,16 @@
         <v>631</v>
       </c>
       <c r="BA22" t="s">
+        <v>667</v>
+      </c>
+      <c r="BB22" t="s">
         <v>668</v>
       </c>
-      <c r="BB22" t="s">
-        <v>669</v>
-      </c>
       <c r="BC22">
-        <v>0.99231435496704667</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD22">
-        <v>140.90349227081035</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9495,16 +9495,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99450846292949968</v>
+        <v>0.99567492323161799</v>
       </c>
       <c r="AB23">
-        <v>100.67817962584009</v>
+        <v>79.293074087003873</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9537,10 +9537,10 @@
         <v>552</v>
       </c>
       <c r="AO23">
-        <v>0.99646273950702013</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP23">
-        <v>64.84977570462992</v>
+        <v>240.53953099643502</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9567,16 +9567,16 @@
         <v>633</v>
       </c>
       <c r="BA23" t="s">
+        <v>669</v>
+      </c>
+      <c r="BB23" t="s">
         <v>670</v>
       </c>
-      <c r="BB23" t="s">
-        <v>560</v>
-      </c>
       <c r="BC23">
-        <v>0.99223220184557481</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD23">
-        <v>142.40963283112865</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9641,16 +9641,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.98298990306503153</v>
+        <v>0.99715230385125297</v>
       </c>
       <c r="AB24">
-        <v>311.85177714108931</v>
+        <v>52.207762727027884</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9680,13 +9680,13 @@
         <v>553</v>
       </c>
       <c r="AN24" t="s">
-        <v>414</v>
+        <v>554</v>
       </c>
       <c r="AO24">
-        <v>0.99599400380931946</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP24">
-        <v>73.443263495810669</v>
+        <v>208.83757343808102</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9719,10 +9719,10 @@
         <v>672</v>
       </c>
       <c r="BC24">
-        <v>0.99429876975975018</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD24">
-        <v>104.52255440457925</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9787,16 +9787,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99493070276109996</v>
+        <v>0.99545552704228712</v>
       </c>
       <c r="AB25">
-        <v>92.937116046500407</v>
+        <v>83.315337558069643</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9823,16 +9823,16 @@
         <v>471</v>
       </c>
       <c r="AM25" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN25" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO25">
-        <v>0.99788320682147802</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP25">
-        <v>38.807874939569167</v>
+        <v>153.25643118471478</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9865,10 +9865,10 @@
         <v>674</v>
       </c>
       <c r="BC25">
-        <v>0.99672758029478525</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD25">
-        <v>59.994361262269514</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9933,16 +9933,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99197366299435197</v>
+        <v>0.9895807450862778</v>
       </c>
       <c r="AB26">
-        <v>147.14951177021345</v>
+        <v>191.01967341824059</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9969,16 +9969,16 @@
         <v>473</v>
       </c>
       <c r="AM26" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN26" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO26">
-        <v>0.99576958396989479</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP26">
-        <v>77.557627218594661</v>
+        <v>56.43597346825765</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10011,10 +10011,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.98805842341846151</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD26">
-        <v>218.92890399487229</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10079,16 +10079,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99520836470773288</v>
+        <v>0.99450846292949968</v>
       </c>
       <c r="AB27">
-        <v>87.846647024897322</v>
+        <v>100.67817962584009</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10115,16 +10115,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN27" t="s">
-        <v>401</v>
+        <v>560</v>
       </c>
       <c r="AO27">
-        <v>0.99495142174876894</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP27">
-        <v>92.557267939235231</v>
+        <v>59.203841808565592</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10154,13 +10154,13 @@
         <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>423</v>
+        <v>550</v>
       </c>
       <c r="BC27">
-        <v>0.98830355217046739</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD27">
-        <v>214.43487687476414</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10225,16 +10225,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99492063738174197</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB28">
-        <v>93.121648001396338</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10261,16 +10261,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="AN28" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AO28">
-        <v>0.99468222901836267</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP28">
-        <v>97.492467996683757</v>
+        <v>72.069660828511601</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10303,10 +10303,10 @@
         <v>679</v>
       </c>
       <c r="BC28">
-        <v>0.98743040674179927</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD28">
-        <v>230.44254306701379</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10371,16 +10371,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99698749491520611</v>
+        <v>0.99493070276109996</v>
       </c>
       <c r="AB29">
-        <v>55.229259887887068</v>
+        <v>92.937116046500407</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10407,16 +10407,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AN29" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AO29">
-        <v>0.98687966194564902</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP29">
-        <v>240.53953099643502</v>
+        <v>32.141331469648897</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10449,10 +10449,10 @@
         <v>681</v>
       </c>
       <c r="BC29">
-        <v>0.99279657608325511</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD29">
-        <v>132.06277180699064</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10517,16 +10517,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99766238113026029</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB30">
-        <v>42.856345945228725</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10553,16 +10553,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AN30" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AO30">
-        <v>0.98860885963065015</v>
+        <v>0.99433440313430599</v>
       </c>
       <c r="AP30">
-        <v>208.83757343808102</v>
+        <v>103.86927587105613</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10663,16 +10663,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99567492323161799</v>
+        <v>0.99565105035038126</v>
       </c>
       <c r="AB31">
-        <v>79.293074087003873</v>
+        <v>79.730743576343073</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10699,16 +10699,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AN31" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AO31">
-        <v>0.99164055829901554</v>
+        <v>0.99165427860211908</v>
       </c>
       <c r="AP31">
-        <v>153.25643118471478</v>
+        <v>153.00489229448431</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10809,16 +10809,16 @@
         <v>485</v>
       </c>
       <c r="AM32" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AN32" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AO32">
-        <v>0.99692167417445865</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP32">
-        <v>56.43597346825765</v>
+        <v>78.289282890438841</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10919,16 +10919,16 @@
         <v>487</v>
       </c>
       <c r="AM33" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN33" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO33">
-        <v>0.99677069953771458</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP33">
-        <v>59.203841808565592</v>
+        <v>69.53999647349201</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10993,16 +10993,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99590798933590385</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB34">
-        <v>75.020195508429936</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11029,16 +11029,16 @@
         <v>489</v>
       </c>
       <c r="AM34" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AN34" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AO34">
-        <v>0.99546749107529653</v>
+        <v>0.99830579859179591</v>
       </c>
       <c r="AP34">
-        <v>83.095996952896456</v>
+        <v>31.060359150407386</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11103,16 +11103,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99588491419783987</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB35">
-        <v>75.443239706269793</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11139,16 +11139,16 @@
         <v>491</v>
       </c>
       <c r="AM35" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AN35" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AO35">
-        <v>0.99606892759117205</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP35">
-        <v>72.069660828511601</v>
+        <v>88.431180058290352</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11213,16 +11213,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99021378007306371</v>
+        <v>0.99672872587342576</v>
       </c>
       <c r="AB36">
-        <v>179.41403199383166</v>
+        <v>59.973358987194473</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11249,16 +11249,16 @@
         <v>493</v>
       </c>
       <c r="AM36" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AN36" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AO36">
-        <v>0.99824683646529189</v>
+        <v>0.99509878714312805</v>
       </c>
       <c r="AP36">
-        <v>32.141331469648897</v>
+        <v>89.85556904265141</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11323,16 +11323,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99315447263323475</v>
+        <v>0.99528373638972145</v>
       </c>
       <c r="AB37">
-        <v>125.50133505736341</v>
+        <v>86.464832855106309</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11359,16 +11359,16 @@
         <v>495</v>
       </c>
       <c r="AM37" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AN37" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="AO37">
-        <v>0.99606896061575723</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP37">
-        <v>72.069055377783442</v>
+        <v>150.6984130259078</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11433,16 +11433,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99649986768340049</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB38">
-        <v>64.16909247099106</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11469,16 +11469,16 @@
         <v>497</v>
       </c>
       <c r="AM38" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AN38" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AO38">
-        <v>0.99415308404615776</v>
+        <v>0.99398790580290575</v>
       </c>
       <c r="AP38">
-        <v>107.19345915377383</v>
+        <v>110.2217269467279</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11543,16 +11543,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99827081845920873</v>
+        <v>0.99536059527709431</v>
       </c>
       <c r="AB39">
-        <v>31.701661581174136</v>
+        <v>85.055753253270055</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11579,16 +11579,16 @@
         <v>499</v>
       </c>
       <c r="AM39" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AN39" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AO39">
-        <v>0.99578710491059208</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP39">
-        <v>77.236409972479407</v>
+        <v>64.84977570462992</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11653,16 +11653,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99456731509164431</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB40">
-        <v>99.599223319854588</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11689,16 +11689,16 @@
         <v>501</v>
       </c>
       <c r="AM40" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AN40" t="s">
-        <v>584</v>
+        <v>418</v>
       </c>
       <c r="AO40">
-        <v>0.99838396904917182</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP40">
-        <v>29.627234098515917</v>
+        <v>73.443263495810669</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11763,16 +11763,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99635213764962971</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB41">
-        <v>66.877476423454894</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11799,16 +11799,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN41" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO41">
-        <v>0.99796084623978776</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP41">
-        <v>37.384485603890518</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11873,16 +11873,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99331818519922233</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB42">
-        <v>122.49993801425808</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11909,16 +11909,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN42" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO42">
-        <v>0.99576662598769528</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP42">
-        <v>77.611856892252987</v>
+        <v>90.729435350939028</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11983,16 +11983,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99849240016674334</v>
+        <v>0.99590798933590385</v>
       </c>
       <c r="AB43">
-        <v>27.639330276371737</v>
+        <v>75.020195508429936</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12019,16 +12019,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AN43" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO43">
-        <v>0.99433440313430599</v>
+        <v>0.9979252881755144</v>
       </c>
       <c r="AP43">
-        <v>103.86927587105613</v>
+        <v>38.036383448902463</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12093,16 +12093,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>295</v>
+        <v>270</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99484635552608569</v>
+        <v>0.99588491419783987</v>
       </c>
       <c r="AB44">
-        <v>94.483482021761333</v>
+        <v>75.443239706269793</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12129,16 +12129,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN44" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO44">
-        <v>0.99165427860211908</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP44">
-        <v>153.00489229448431</v>
+        <v>59.260154763351615</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12203,16 +12203,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99536059527709431</v>
+        <v>0.99021378007306371</v>
       </c>
       <c r="AB45">
-        <v>85.055753253270055</v>
+        <v>179.41403199383166</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12239,16 +12239,16 @@
         <v>511</v>
       </c>
       <c r="AM45" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN45" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO45">
-        <v>0.99572967547870339</v>
+        <v>0.9960576359591049</v>
       </c>
       <c r="AP45">
-        <v>78.289282890438841</v>
+        <v>72.276674083075989</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12313,16 +12313,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99695083910621241</v>
+        <v>0.99315447263323475</v>
       </c>
       <c r="AB46">
-        <v>55.901283052772143</v>
+        <v>125.50133505736341</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12349,16 +12349,16 @@
         <v>513</v>
       </c>
       <c r="AM46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN46" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO46">
-        <v>0.99620690928326405</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP46">
-        <v>69.53999647349201</v>
+        <v>89.003951656813172</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12423,16 +12423,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99399085439572143</v>
+        <v>0.99649986768340049</v>
       </c>
       <c r="AB47">
-        <v>110.16766941177411</v>
+        <v>64.16909247099106</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12459,16 +12459,16 @@
         <v>515</v>
       </c>
       <c r="AM47" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN47" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO47">
-        <v>0.99830579859179591</v>
+        <v>0.99515836501188337</v>
       </c>
       <c r="AP47">
-        <v>31.060359150407386</v>
+        <v>88.763308115471318</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12533,16 +12533,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99601337563103476</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB48">
-        <v>73.088113431029612</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12569,16 +12569,16 @@
         <v>517</v>
       </c>
       <c r="AM48" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO48">
-        <v>0.9951764810877296</v>
+        <v>0.99399231910847008</v>
       </c>
       <c r="AP48">
-        <v>88.431180058290352</v>
+        <v>110.14081634471604</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12643,16 +12643,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99758018972146978</v>
+        <v>0.99297090277863642</v>
       </c>
       <c r="AB49">
-        <v>44.363188439721</v>
+        <v>128.86678239166531</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12679,16 +12679,16 @@
         <v>519</v>
       </c>
       <c r="AM49" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO49">
-        <v>0.99587491663731742</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP49">
-        <v>75.626528315847352</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12753,16 +12753,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99528373638972145</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB50">
-        <v>86.464832855106309</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12789,16 +12789,16 @@
         <v>521</v>
       </c>
       <c r="AM50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AN50" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO50">
-        <v>0.9945106241527748</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP50">
-        <v>100.63855719912947</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12863,16 +12863,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99715230385125297</v>
+        <v>0.99681605507557702</v>
       </c>
       <c r="AB51">
-        <v>52.207762727027884</v>
+        <v>58.372323614420687</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12899,16 +12899,16 @@
         <v>523</v>
       </c>
       <c r="AM51" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN51" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AO51">
-        <v>0.99504825389388352</v>
+        <v>0.99576958396989479</v>
       </c>
       <c r="AP51">
-        <v>90.782011945468795</v>
+        <v>77.557627218594661</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12973,16 +12973,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99545552704228712</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB52">
-        <v>83.315337558069643</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13009,16 +13009,16 @@
         <v>525</v>
       </c>
       <c r="AM52" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN52" t="s">
-        <v>608</v>
+        <v>420</v>
       </c>
       <c r="AO52">
-        <v>0.99247550518926964</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP52">
-        <v>137.94907153005732</v>
+        <v>92.557267939235231</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13083,16 +13083,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.9895807450862778</v>
+        <v>0.99599691424900794</v>
       </c>
       <c r="AB53">
-        <v>191.01967341824059</v>
+        <v>73.389905434855194</v>
       </c>
     </row>
   </sheetData>
@@ -13101,7 +13101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AF16AC-D37C-4468-BB19-E9B31F4C3BAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B27809-3719-48DF-B819-A835FE7203A0}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13213,7 +13213,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>553</v>
+        <v>585</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13246,7 +13246,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13281,7 +13281,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>547</v>
+        <v>600</v>
       </c>
       <c r="L12">
         <v>41.625170147271362</v>
@@ -13314,7 +13314,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13349,7 +13349,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>543</v>
+        <v>596</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13382,7 +13382,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13417,7 +13417,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>601</v>
+        <v>545</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13450,7 +13450,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>677</v>
+        <v>666</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13485,7 +13485,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>579</v>
+        <v>537</v>
       </c>
       <c r="L15">
         <v>14.248215224493222</v>
@@ -13518,7 +13518,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13553,7 +13553,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="L16">
         <v>60.246276232111249</v>
@@ -13586,7 +13586,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13621,7 +13621,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13654,7 +13654,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>662</v>
+        <v>678</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13689,7 +13689,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>527</v>
+        <v>592</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13722,7 +13722,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13757,7 +13757,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>597</v>
+        <v>573</v>
       </c>
       <c r="L19">
         <v>15.921767829784981</v>
@@ -13790,7 +13790,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13825,7 +13825,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13858,7 +13858,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13893,7 +13893,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>531</v>
+        <v>590</v>
       </c>
       <c r="L21">
         <v>11.156586435503245</v>
@@ -13926,7 +13926,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>652</v>
+        <v>671</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13961,7 +13961,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>556</v>
+        <v>606</v>
       </c>
       <c r="L22">
         <v>6.3773535033999496</v>
@@ -13994,7 +13994,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>664</v>
+        <v>680</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14029,7 +14029,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>545</v>
+        <v>598</v>
       </c>
       <c r="L23">
         <v>4.8861340927283274</v>
@@ -14062,7 +14062,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14097,7 +14097,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>591</v>
+        <v>567</v>
       </c>
       <c r="L24">
         <v>13.571087213989722</v>
@@ -14130,7 +14130,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14165,7 +14165,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>575</v>
+        <v>563</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14198,7 +14198,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14233,7 +14233,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>599</v>
+        <v>575</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14266,7 +14266,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14301,7 +14301,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14334,7 +14334,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14369,7 +14369,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>595</v>
+        <v>571</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14402,7 +14402,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>650</v>
+        <v>664</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14437,7 +14437,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>554</v>
+        <v>586</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14470,7 +14470,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>680</v>
+        <v>669</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14505,7 +14505,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>558</v>
+        <v>608</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14573,7 +14573,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14608,7 +14608,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>585</v>
+        <v>543</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14643,7 +14643,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>529</v>
+        <v>588</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14678,7 +14678,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>587</v>
+        <v>533</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14713,7 +14713,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>583</v>
+        <v>541</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14748,7 +14748,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>571</v>
+        <v>531</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14783,7 +14783,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>581</v>
+        <v>539</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14818,7 +14818,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>551</v>
+        <v>583</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14853,7 +14853,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="L39">
         <v>26.32580391715549</v>
@@ -14888,7 +14888,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>539</v>
+        <v>529</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14923,7 +14923,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>593</v>
+        <v>569</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14958,7 +14958,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14993,7 +14993,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>535</v>
+        <v>579</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15028,7 +15028,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>603</v>
+        <v>547</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15063,7 +15063,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>577</v>
+        <v>535</v>
       </c>
       <c r="L45">
         <v>11.262860315683808</v>
@@ -15098,7 +15098,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>541</v>
+        <v>594</v>
       </c>
       <c r="L46">
         <v>34.610640160809844</v>
@@ -15133,7 +15133,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15168,7 +15168,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15203,7 +15203,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>589</v>
+        <v>565</v>
       </c>
       <c r="L49">
         <v>63.11239557797159</v>
@@ -15238,7 +15238,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>549</v>
+        <v>581</v>
       </c>
       <c r="L50">
         <v>38.222782480143309</v>
@@ -15273,7 +15273,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15308,7 +15308,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15323,7 +15323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B960E65-D6C2-4E9C-AD54-75C4A8E44757}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCB57C0B-8F62-4875-AD09-B39D723ADD42}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17140,7 +17140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD756840-1B04-4CB8-9377-1AC392DAF6C5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F9577A-6611-466A-914F-46AEDD88A9BD}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C271548F-F627-43F4-BB3A-1A5446F7890E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{888C9B7D-BC79-4146-8DE4-02217DE4D6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,18 +1060,210 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_018</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_011</t>
   </si>
   <si>
@@ -1096,22 +1288,10 @@
     <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
+    <t>distr_solelc_spv_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_solelc_spv_013</t>
@@ -1144,192 +1324,108 @@
     <t>connecting solar to buses in cluster 23</t>
   </si>
   <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
+  </si>
+  <si>
+    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
+  </si>
+  <si>
+    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w162871098-400</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400,e_w105759402-400,e_ZA31-400</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>e_w102925909-400,e_ZA24-400,e_w105759402-400,e_w98231311-400,e_ZA26-400,e_w179136373-400,e_w178968761-400</t>
+  </si>
+  <si>
+    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
+  </si>
+  <si>
+    <t>e_ZA25-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
+  </si>
+  <si>
+    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_r17287657-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>e_w208749745-400,e_w156418705-400,e_ZA7-400</t>
+  </si>
+  <si>
+    <t>e_w836844162-400,e_w107431792-400,e_w545652232-400,e_ZA43-400,e_w182042518-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_w586032034-400,e_w934819484-400,e_w586032034-765,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>e_w208749745-400,e_ZA7-400,e_w156418705-400</t>
+  </si>
+  <si>
+    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
+  </si>
+  <si>
+    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
+  </si>
+  <si>
+    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
+  </si>
+  <si>
+    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
+  </si>
+  <si>
+    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w169647963-400</t>
+  </si>
+  <si>
+    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>e_w107391770-400,e_w120941269-400,e_w219596295-400</t>
+  </si>
+  <si>
     <t>e_w102682082-400,e_w177800991-400</t>
   </si>
   <si>
@@ -1345,13 +1441,7 @@
     <t>e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
   </si>
   <si>
-    <t>e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>e_w107391770-400,e_w120941269-400,e_w219596295-400</t>
+    <t>e_w156418705-400,e_ZA11-400</t>
   </si>
   <si>
     <t>e_w125754107-400,e_ZA39-400</t>
@@ -1369,94 +1459,22 @@
     <t>e_ZA23-400,e_w260486370-400,e_w156418705-400,e_ZA11-400</t>
   </si>
   <si>
-    <t>e_w836844162-400,e_w107431792-400,e_w545652232-400,e_ZA43-400,e_w182042518-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_w586032034-400,e_w934819484-400,e_w586032034-765,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400,e_ZA7-400,e_w156418705-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_r17287657-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400,e_w156418705-400,e_ZA7-400</t>
-  </si>
-  <si>
-    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
-  </si>
-  <si>
-    <t>e_w156418705-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
-  </si>
-  <si>
-    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w162871098-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400,e_w105759402-400,e_ZA31-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
-  </si>
-  <si>
-    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_ZA24-400,e_w105759402-400,e_w98231311-400,e_ZA26-400,e_w179136373-400,e_w178968761-400</t>
+    <t>distr_wonelc_won_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_029</t>
@@ -1471,244 +1489,244 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
+    <t>distr_wonelc_won_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_026</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 26</t>
   </si>
   <si>
+    <t>distr_wonelc_won_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_024</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>elc_won_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400,e_ZA26-400,e_w179136373-400,e_w104080393-400,e_w213181313-400</t>
+  </si>
+  <si>
+    <t>elc_won_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
+  </si>
+  <si>
+    <t>elc_won_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
   </si>
   <si>
     <t>elc_won_029</t>
@@ -1723,238 +1741,328 @@
     <t>e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w107937167-400</t>
   </si>
   <si>
+    <t>elc_won_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w162871098-400,e_w125754107-400</t>
+  </si>
+  <si>
+    <t>elc_won_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400</t>
+  </si>
+  <si>
+    <t>elc_won_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400,e_w934819484-400,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_won_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400,e_w89637370-400,e_w142414070-400,e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>elc_won_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
+  </si>
+  <si>
+    <t>elc_won_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
+  </si>
+  <si>
+    <t>elc_won_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400,e_w92348290-765</t>
+  </si>
+  <si>
+    <t>elc_won_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
+  </si>
+  <si>
+    <t>elc_won_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
+  </si>
+  <si>
+    <t>elc_won_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400</t>
+  </si>
+  <si>
+    <t>elc_won_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400,e_w663042845-400</t>
+  </si>
+  <si>
+    <t>elc_won_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
+  </si>
+  <si>
+    <t>elc_won_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
+  </si>
+  <si>
+    <t>elc_won_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400,e_w207991752-400</t>
+  </si>
+  <si>
+    <t>elc_won_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
+  </si>
+  <si>
+    <t>elc_won_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
+  </si>
+  <si>
+    <t>elc_won_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
+  </si>
+  <si>
+    <t>elc_won_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
+  </si>
+  <si>
+    <t>elc_won_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
+  </si>
+  <si>
+    <t>elc_won_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
+  </si>
+  <si>
     <t>elc_won_026</t>
   </si>
   <si>
     <t>e_w184581460-400,e_w230551819-400,e_ZA2-400,e_ZA14-400,e_w685294883-400,e_w170672051-400</t>
   </si>
   <si>
+    <t>elc_won_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
+  </si>
+  <si>
+    <t>elc_won_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
+  </si>
+  <si>
+    <t>elc_won_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
+  </si>
+  <si>
+    <t>elc_won_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400</t>
+  </si>
+  <si>
+    <t>elc_won_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
+  </si>
+  <si>
+    <t>elc_won_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
+  </si>
+  <si>
+    <t>elc_won_001</t>
+  </si>
+  <si>
+    <t>elc_won_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
+  </si>
+  <si>
+    <t>elc_won_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
+  </si>
+  <si>
+    <t>elc_won_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
+  </si>
+  <si>
+    <t>elc_won_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>elc_won_020</t>
+  </si>
+  <si>
+    <t>elc_won_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400,e_w125754107-400</t>
+  </si>
+  <si>
+    <t>elc_won_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400,e_w156418705-400,e_ZA7-400,e_w208749745-400</t>
+  </si>
+  <si>
     <t>elc_won_024</t>
   </si>
   <si>
     <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w182408147-400</t>
   </si>
   <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w92348290-765</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400,e_ZA26-400,e_w179136373-400,e_w104080393-400,e_w213181313-400</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w162871098-400,e_w125754107-400</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400,e_w89637370-400,e_w142414070-400,e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w125754107-400</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400,e_w156418705-400,e_ZA7-400,e_w208749745-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
+    <t>distr_wofelc_wof_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
     <t>distr_wofelc_wof_013</t>
@@ -1969,112 +2077,100 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>elc_wof_009</t>
+  </si>
+  <si>
+    <t>elc_wof_020</t>
+  </si>
+  <si>
+    <t>e_w934819484-400,e_w169789536-400,e_w90454383-400</t>
+  </si>
+  <si>
+    <t>elc_wof_005</t>
+  </si>
+  <si>
+    <t>elc_wof_007</t>
+  </si>
+  <si>
+    <t>e_r17287657-400,e_w631673098-400</t>
+  </si>
+  <si>
+    <t>elc_wof_012</t>
+  </si>
+  <si>
+    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w131625968-400</t>
+  </si>
+  <si>
+    <t>elc_wof_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400,e_w169647963-400,e_r17287657-400</t>
+  </si>
+  <si>
+    <t>elc_wof_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400</t>
+  </si>
+  <si>
+    <t>elc_wof_004</t>
+  </si>
+  <si>
+    <t>elc_wof_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
+  </si>
+  <si>
+    <t>elc_wof_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400,e_w934819484-400</t>
+  </si>
+  <si>
+    <t>elc_wof_006</t>
+  </si>
+  <si>
+    <t>elc_wof_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400,e_w102682082-400</t>
+  </si>
+  <si>
+    <t>elc_wof_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400</t>
+  </si>
+  <si>
+    <t>elc_wof_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
+  </si>
+  <si>
+    <t>elc_wof_002</t>
+  </si>
+  <si>
+    <t>e_w193465369-400,e_w107431792-400,e_w193978748-400,e_w836844162-400</t>
+  </si>
+  <si>
+    <t>elc_wof_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400,e_w177800991-400,e_w934819484-400</t>
+  </si>
+  <si>
+    <t>elc_wof_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
+  </si>
+  <si>
+    <t>elc_wof_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
   </si>
   <si>
     <t>elc_wof_013</t>
@@ -2084,102 +2180,6 @@
   </si>
   <si>
     <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400,e_w102682082-400</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w169647963-400,e_r17287657-400</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w107431792-400,e_w193978748-400,e_w836844162-400</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_r17287657-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w131625968-400</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w934819484-400,e_w169789536-400,e_w90454383-400</t>
   </si>
   <si>
     <t>e_won_001</t>
@@ -7505,7 +7505,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C19B27A8-AD7B-406B-A39E-5E1B267765CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55544942-4C2D-43AE-807F-081B3263B226}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7743,16 +7743,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99456731509164431</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB11">
-        <v>99.599223319854588</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7785,10 +7785,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99333523291287673</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP11">
-        <v>122.18739659725948</v>
+        <v>59.260154763351615</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7818,13 +7818,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>650</v>
+        <v>566</v>
       </c>
       <c r="BC11">
-        <v>0.98843991010136767</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD11">
-        <v>211.93498147492642</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7889,16 +7889,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99635213764962971</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB12">
-        <v>66.877476423454894</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7931,10 +7931,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99201650479533909</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP12">
-        <v>146.36407875211563</v>
+        <v>72.069660828511601</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7961,16 +7961,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
+        <v>650</v>
+      </c>
+      <c r="BB12" t="s">
         <v>651</v>
       </c>
-      <c r="BB12" t="s">
-        <v>405</v>
-      </c>
       <c r="BC12">
-        <v>0.99010219056094972</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD12">
-        <v>181.45983971592244</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8035,16 +8035,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99331818519922233</v>
+        <v>0.99672872587342576</v>
       </c>
       <c r="AB13">
-        <v>122.49993801425808</v>
+        <v>59.973358987194473</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8077,10 +8077,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99546749107529653</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP13">
-        <v>83.095996952896456</v>
+        <v>32.141331469648897</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8110,13 +8110,13 @@
         <v>652</v>
       </c>
       <c r="BB13" t="s">
-        <v>550</v>
+        <v>558</v>
       </c>
       <c r="BC13">
-        <v>0.99223220184557481</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD13">
-        <v>142.40963283112865</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8181,16 +8181,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99849240016674334</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB14">
-        <v>27.639330276371737</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8223,10 +8223,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.99576662598769528</v>
+        <v>0.99333523291287673</v>
       </c>
       <c r="AP14">
-        <v>77.611856892252987</v>
+        <v>122.18739659725948</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8259,10 +8259,10 @@
         <v>654</v>
       </c>
       <c r="BC14">
-        <v>0.99429876975975018</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD14">
-        <v>104.52255440457925</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8327,16 +8327,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99484635552608569</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB15">
-        <v>94.483482021761333</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8369,10 +8369,10 @@
         <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.99606896061575723</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP15">
-        <v>72.069055377783442</v>
+        <v>146.36407875211563</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8405,10 +8405,10 @@
         <v>656</v>
       </c>
       <c r="BC15">
-        <v>0.99672758029478525</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD15">
-        <v>59.994361262269514</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8473,16 +8473,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99399085439572143</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB16">
-        <v>110.16766941177411</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8515,10 +8515,10 @@
         <v>538</v>
       </c>
       <c r="AO16">
-        <v>0.99415308404615776</v>
+        <v>0.9960576359591049</v>
       </c>
       <c r="AP16">
-        <v>107.19345915377383</v>
+        <v>72.276674083075989</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8551,10 +8551,10 @@
         <v>658</v>
       </c>
       <c r="BC16">
-        <v>0.98805842341846151</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD16">
-        <v>218.92890399487229</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8619,16 +8619,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99601337563103476</v>
+        <v>0.99599691424900794</v>
       </c>
       <c r="AB17">
-        <v>73.088113431029612</v>
+        <v>73.389905434855194</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8661,10 +8661,10 @@
         <v>540</v>
       </c>
       <c r="AO17">
-        <v>0.99578710491059208</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP17">
-        <v>77.236409972479407</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8697,10 +8697,10 @@
         <v>660</v>
       </c>
       <c r="BC17">
-        <v>0.99481516601444531</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD17">
-        <v>95.055289735168813</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8765,16 +8765,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99758018972146978</v>
+        <v>0.99450846292949968</v>
       </c>
       <c r="AB18">
-        <v>44.363188439721</v>
+        <v>100.67817962584009</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8807,10 +8807,10 @@
         <v>542</v>
       </c>
       <c r="AO18">
-        <v>0.99838396904917182</v>
+        <v>0.99515836501188337</v>
       </c>
       <c r="AP18">
-        <v>29.627234098515917</v>
+        <v>88.763308115471318</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,13 +8840,13 @@
         <v>661</v>
       </c>
       <c r="BB18" t="s">
-        <v>662</v>
+        <v>421</v>
       </c>
       <c r="BC18">
-        <v>0.99545422785121029</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD18">
-        <v>83.33915606114418</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8911,16 +8911,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99520836470773288</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB19">
-        <v>87.846647024897322</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8953,10 +8953,10 @@
         <v>544</v>
       </c>
       <c r="AO19">
-        <v>0.99796084623978776</v>
+        <v>0.99399231910847008</v>
       </c>
       <c r="AP19">
-        <v>37.384485603890518</v>
+        <v>110.14081634471604</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8983,16 +8983,16 @@
         <v>625</v>
       </c>
       <c r="BA19" t="s">
+        <v>662</v>
+      </c>
+      <c r="BB19" t="s">
         <v>663</v>
       </c>
-      <c r="BB19" t="s">
-        <v>558</v>
-      </c>
       <c r="BC19">
-        <v>0.99507162964364948</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD19">
-        <v>90.353456533092867</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9057,16 +9057,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>269</v>
+        <v>299</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99492063738174197</v>
+        <v>0.99493070276109996</v>
       </c>
       <c r="AB20">
-        <v>93.121648001396338</v>
+        <v>92.937116046500407</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9099,10 +9099,10 @@
         <v>546</v>
       </c>
       <c r="AO20">
-        <v>0.99587491663731742</v>
+        <v>0.99433440313430599</v>
       </c>
       <c r="AP20">
-        <v>75.626528315847352</v>
+        <v>103.86927587105613</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9135,10 +9135,10 @@
         <v>665</v>
       </c>
       <c r="BC20">
-        <v>0.99462081464868646</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD20">
-        <v>98.618398107414592</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9203,16 +9203,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99698749491520611</v>
+        <v>0.99536059527709431</v>
       </c>
       <c r="AB21">
-        <v>55.229259887887068</v>
+        <v>85.055753253270055</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9245,10 +9245,10 @@
         <v>548</v>
       </c>
       <c r="AO21">
-        <v>0.9945106241527748</v>
+        <v>0.99165427860211908</v>
       </c>
       <c r="AP21">
-        <v>100.63855719912947</v>
+        <v>153.00489229448431</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,13 +9278,13 @@
         <v>666</v>
       </c>
       <c r="BB21" t="s">
-        <v>432</v>
+        <v>558</v>
       </c>
       <c r="BC21">
-        <v>0.98830355217046739</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD21">
-        <v>214.43487687476414</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9349,16 +9349,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99766238113026029</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB22">
-        <v>42.856345945228725</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9391,10 +9391,10 @@
         <v>550</v>
       </c>
       <c r="AO22">
-        <v>0.99468222901836267</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP22">
-        <v>97.492467996683757</v>
+        <v>78.289282890438841</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9427,10 +9427,10 @@
         <v>668</v>
       </c>
       <c r="BC22">
-        <v>0.98743040674179927</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD22">
-        <v>230.44254306701379</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9495,16 +9495,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99567492323161799</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB23">
-        <v>79.293074087003873</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9537,10 +9537,10 @@
         <v>552</v>
       </c>
       <c r="AO23">
-        <v>0.98687966194564902</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP23">
-        <v>240.53953099643502</v>
+        <v>69.53999647349201</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9573,10 +9573,10 @@
         <v>670</v>
       </c>
       <c r="BC23">
-        <v>0.99279657608325511</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD23">
-        <v>132.06277180699064</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9641,16 +9641,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99715230385125297</v>
+        <v>0.99565105035038126</v>
       </c>
       <c r="AB24">
-        <v>52.207762727027884</v>
+        <v>79.730743576343073</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9683,10 +9683,10 @@
         <v>554</v>
       </c>
       <c r="AO24">
-        <v>0.98860885963065015</v>
+        <v>0.99830579859179591</v>
       </c>
       <c r="AP24">
-        <v>208.83757343808102</v>
+        <v>31.060359150407386</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9719,10 +9719,10 @@
         <v>672</v>
       </c>
       <c r="BC24">
-        <v>0.99447517161328947</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD24">
-        <v>101.28852042302684</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9787,16 +9787,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99545552704228712</v>
+        <v>0.99715230385125297</v>
       </c>
       <c r="AB25">
-        <v>83.315337558069643</v>
+        <v>52.207762727027884</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9829,10 +9829,10 @@
         <v>556</v>
       </c>
       <c r="AO25">
-        <v>0.99164055829901554</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP25">
-        <v>153.25643118471478</v>
+        <v>88.431180058290352</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9933,16 +9933,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.9895807450862778</v>
+        <v>0.99545552704228712</v>
       </c>
       <c r="AB26">
-        <v>191.01967341824059</v>
+        <v>83.315337558069643</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9975,10 +9975,10 @@
         <v>558</v>
       </c>
       <c r="AO26">
-        <v>0.99692167417445865</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP26">
-        <v>56.43597346825765</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10079,16 +10079,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99450846292949968</v>
+        <v>0.9895807450862778</v>
       </c>
       <c r="AB27">
-        <v>100.67817962584009</v>
+        <v>191.01967341824059</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10121,10 +10121,10 @@
         <v>560</v>
       </c>
       <c r="AO27">
-        <v>0.99677069953771458</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP27">
-        <v>59.203841808565592</v>
+        <v>240.53953099643502</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10154,13 +10154,13 @@
         <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>550</v>
+        <v>678</v>
       </c>
       <c r="BC27">
-        <v>0.99581145929743231</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD27">
-        <v>76.789912880408167</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10225,16 +10225,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.98298990306503153</v>
+        <v>0.99528373638972145</v>
       </c>
       <c r="AB28">
-        <v>311.85177714108931</v>
+        <v>86.464832855106309</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10267,10 +10267,10 @@
         <v>562</v>
       </c>
       <c r="AO28">
-        <v>0.99606892759117205</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP28">
-        <v>72.069660828511601</v>
+        <v>208.83757343808102</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10297,16 +10297,16 @@
         <v>643</v>
       </c>
       <c r="BA28" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="BB28" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="BC28">
-        <v>0.99582070241731502</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD28">
-        <v>76.620455682557321</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10371,16 +10371,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>299</v>
+        <v>266</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99493070276109996</v>
+        <v>0.99297090277863642</v>
       </c>
       <c r="AB29">
-        <v>92.937116046500407</v>
+        <v>128.86678239166531</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10413,10 +10413,10 @@
         <v>564</v>
       </c>
       <c r="AO29">
-        <v>0.99824683646529189</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP29">
-        <v>32.141331469648897</v>
+        <v>153.25643118471478</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10443,16 +10443,16 @@
         <v>645</v>
       </c>
       <c r="BA29" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="BB29" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="BC29">
-        <v>0.99501631001524238</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD29">
-        <v>91.367649720556983</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10517,16 +10517,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99615584710269711</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB30">
-        <v>70.476136450553028</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10559,10 +10559,10 @@
         <v>566</v>
       </c>
       <c r="AO30">
-        <v>0.99433440313430599</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP30">
-        <v>103.86927587105613</v>
+        <v>56.43597346825765</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10589,16 +10589,16 @@
         <v>647</v>
       </c>
       <c r="BA30" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="BB30" t="s">
-        <v>683</v>
+        <v>429</v>
       </c>
       <c r="BC30">
-        <v>0.99229811324031303</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD30">
-        <v>141.20125726092687</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10663,16 +10663,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99565105035038126</v>
+        <v>0.99681605507557702</v>
       </c>
       <c r="AB31">
-        <v>79.730743576343073</v>
+        <v>58.372323614420687</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10705,10 +10705,10 @@
         <v>568</v>
       </c>
       <c r="AO31">
-        <v>0.99165427860211908</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP31">
-        <v>153.00489229448431</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10773,16 +10773,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99341896335341162</v>
+        <v>0.99590798933590385</v>
       </c>
       <c r="AB32">
-        <v>120.65233852078616</v>
+        <v>75.020195508429936</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10815,10 +10815,10 @@
         <v>570</v>
       </c>
       <c r="AO32">
-        <v>0.99572967547870339</v>
+        <v>0.99606896061575723</v>
       </c>
       <c r="AP32">
-        <v>78.289282890438841</v>
+        <v>72.069055377783442</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10883,16 +10883,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>305</v>
+        <v>270</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99315245009067388</v>
+        <v>0.99588491419783987</v>
       </c>
       <c r="AB33">
-        <v>125.5384150043114</v>
+        <v>75.443239706269793</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10925,10 +10925,10 @@
         <v>572</v>
       </c>
       <c r="AO33">
-        <v>0.99620690928326405</v>
+        <v>0.99415308404615776</v>
       </c>
       <c r="AP33">
-        <v>69.53999647349201</v>
+        <v>107.19345915377383</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10993,16 +10993,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99299045119957896</v>
+        <v>0.99021378007306371</v>
       </c>
       <c r="AB34">
-        <v>128.50839467438524</v>
+        <v>179.41403199383166</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11035,10 +11035,10 @@
         <v>574</v>
       </c>
       <c r="AO34">
-        <v>0.99830579859179591</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP34">
-        <v>31.060359150407386</v>
+        <v>77.236409972479407</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11103,16 +11103,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99495781957805363</v>
+        <v>0.99315447263323475</v>
       </c>
       <c r="AB35">
-        <v>92.439974402351027</v>
+        <v>125.50133505736341</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11145,10 +11145,10 @@
         <v>576</v>
       </c>
       <c r="AO35">
-        <v>0.9951764810877296</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP35">
-        <v>88.431180058290352</v>
+        <v>29.627234098515917</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11213,16 +11213,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99672872587342576</v>
+        <v>0.99649986768340049</v>
       </c>
       <c r="AB36">
-        <v>59.973358987194473</v>
+        <v>64.16909247099106</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11255,10 +11255,10 @@
         <v>578</v>
       </c>
       <c r="AO36">
-        <v>0.99509878714312805</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP36">
-        <v>89.85556904265141</v>
+        <v>37.384485603890518</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11323,16 +11323,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99528373638972145</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB37">
-        <v>86.464832855106309</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11365,10 +11365,10 @@
         <v>580</v>
       </c>
       <c r="AO37">
-        <v>0.99178008656222316</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP37">
-        <v>150.6984130259078</v>
+        <v>83.095996952896456</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11433,16 +11433,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99197366299435197</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB38">
-        <v>147.14951177021345</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11475,10 +11475,10 @@
         <v>582</v>
       </c>
       <c r="AO38">
-        <v>0.99398790580290575</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP38">
-        <v>110.2217269467279</v>
+        <v>75.626528315847352</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11543,16 +11543,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99536059527709431</v>
+        <v>0.99315245009067388</v>
       </c>
       <c r="AB39">
-        <v>85.055753253270055</v>
+        <v>125.5384150043114</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11585,10 +11585,10 @@
         <v>584</v>
       </c>
       <c r="AO39">
-        <v>0.99646273950702013</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP39">
-        <v>64.84977570462992</v>
+        <v>100.63855719912947</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11653,16 +11653,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99695083910621241</v>
+        <v>0.99399085439572143</v>
       </c>
       <c r="AB40">
-        <v>55.901283052772143</v>
+        <v>110.16766941177411</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11692,13 +11692,13 @@
         <v>585</v>
       </c>
       <c r="AN40" t="s">
-        <v>418</v>
+        <v>586</v>
       </c>
       <c r="AO40">
-        <v>0.99599400380931946</v>
+        <v>0.99509878714312805</v>
       </c>
       <c r="AP40">
-        <v>73.443263495810669</v>
+        <v>89.85556904265141</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11763,16 +11763,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99464845307754257</v>
+        <v>0.99601337563103476</v>
       </c>
       <c r="AB41">
-        <v>98.111693578387175</v>
+        <v>73.088113431029612</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11799,16 +11799,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN41" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AO41">
-        <v>0.99788320682147802</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP41">
-        <v>38.807874939569167</v>
+        <v>150.6984130259078</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11873,16 +11873,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.9951066982538278</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB42">
-        <v>89.710532013157362</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11909,16 +11909,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AN42" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO42">
-        <v>0.99505112170813059</v>
+        <v>0.99398790580290575</v>
       </c>
       <c r="AP42">
-        <v>90.729435350939028</v>
+        <v>110.2217269467279</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11983,16 +11983,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99590798933590385</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB43">
-        <v>75.020195508429936</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12019,16 +12019,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AN43" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO43">
-        <v>0.9979252881755144</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP43">
-        <v>38.036383448902463</v>
+        <v>64.84977570462992</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12093,16 +12093,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99588491419783987</v>
+        <v>0.99635213764962971</v>
       </c>
       <c r="AB44">
-        <v>75.443239706269793</v>
+        <v>66.877476423454894</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12129,16 +12129,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AN44" t="s">
-        <v>593</v>
+        <v>409</v>
       </c>
       <c r="AO44">
-        <v>0.99676762792199902</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP44">
-        <v>59.260154763351615</v>
+        <v>73.443263495810669</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12203,16 +12203,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99021378007306371</v>
+        <v>0.99331818519922233</v>
       </c>
       <c r="AB45">
-        <v>179.41403199383166</v>
+        <v>122.49993801425808</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12245,10 +12245,10 @@
         <v>595</v>
       </c>
       <c r="AO45">
-        <v>0.9960576359591049</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP45">
-        <v>72.276674083075989</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12313,16 +12313,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99315447263323475</v>
+        <v>0.99849240016674334</v>
       </c>
       <c r="AB46">
-        <v>125.50133505736341</v>
+        <v>27.639330276371737</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12355,10 +12355,10 @@
         <v>597</v>
       </c>
       <c r="AO46">
-        <v>0.99514523900053742</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP46">
-        <v>89.003951656813172</v>
+        <v>90.729435350939028</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12423,16 +12423,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99649986768340049</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB47">
-        <v>64.16909247099106</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12465,10 +12465,10 @@
         <v>599</v>
       </c>
       <c r="AO47">
-        <v>0.99515836501188337</v>
+        <v>0.9979252881755144</v>
       </c>
       <c r="AP47">
-        <v>88.763308115471318</v>
+        <v>38.036383448902463</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12533,16 +12533,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99827081845920873</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB48">
-        <v>31.701661581174136</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12575,10 +12575,10 @@
         <v>601</v>
       </c>
       <c r="AO48">
-        <v>0.99399231910847008</v>
+        <v>0.99576958396989479</v>
       </c>
       <c r="AP48">
-        <v>110.14081634471604</v>
+        <v>77.557627218594661</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12643,16 +12643,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99297090277863642</v>
+        <v>0.99520836470773288</v>
       </c>
       <c r="AB49">
-        <v>128.86678239166531</v>
+        <v>87.846647024897322</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12682,13 +12682,13 @@
         <v>602</v>
       </c>
       <c r="AN49" t="s">
-        <v>603</v>
+        <v>413</v>
       </c>
       <c r="AO49">
-        <v>0.99504825389388352</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP49">
-        <v>90.782011945468795</v>
+        <v>92.557267939235231</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12753,16 +12753,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>301</v>
+        <v>269</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99726845868655478</v>
+        <v>0.99492063738174197</v>
       </c>
       <c r="AB50">
-        <v>50.078257413162468</v>
+        <v>93.121648001396338</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12789,16 +12789,16 @@
         <v>521</v>
       </c>
       <c r="AM50" t="s">
+        <v>603</v>
+      </c>
+      <c r="AN50" t="s">
         <v>604</v>
       </c>
-      <c r="AN50" t="s">
-        <v>605</v>
-      </c>
       <c r="AO50">
-        <v>0.99247550518926964</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP50">
-        <v>137.94907153005732</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12863,16 +12863,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99681605507557702</v>
+        <v>0.99698749491520611</v>
       </c>
       <c r="AB51">
-        <v>58.372323614420687</v>
+        <v>55.229259887887068</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12899,16 +12899,16 @@
         <v>523</v>
       </c>
       <c r="AM51" t="s">
+        <v>605</v>
+      </c>
+      <c r="AN51" t="s">
         <v>606</v>
       </c>
-      <c r="AN51" t="s">
-        <v>607</v>
-      </c>
       <c r="AO51">
-        <v>0.99576958396989479</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP51">
-        <v>77.557627218594661</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12973,16 +12973,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99466941924265306</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB52">
-        <v>97.727313884694652</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13009,16 +13009,16 @@
         <v>525</v>
       </c>
       <c r="AM52" t="s">
+        <v>607</v>
+      </c>
+      <c r="AN52" t="s">
         <v>608</v>
       </c>
-      <c r="AN52" t="s">
-        <v>420</v>
-      </c>
       <c r="AO52">
-        <v>0.99495142174876894</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP52">
-        <v>92.557267939235231</v>
+        <v>77.611856892252987</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13083,16 +13083,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99599691424900794</v>
+        <v>0.99567492323161799</v>
       </c>
       <c r="AB53">
-        <v>73.389905434855194</v>
+        <v>79.293074087003873</v>
       </c>
     </row>
   </sheetData>
@@ -13101,7 +13101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23B27809-3719-48DF-B819-A835FE7203A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA204E96-72D3-4208-8875-BACCCB53D2B6}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13213,7 +13213,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13246,7 +13246,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13281,7 +13281,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>600</v>
+        <v>543</v>
       </c>
       <c r="L12">
         <v>41.625170147271362</v>
@@ -13349,7 +13349,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>596</v>
+        <v>539</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13382,7 +13382,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13417,7 +13417,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>545</v>
+        <v>581</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13450,7 +13450,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13485,7 +13485,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>537</v>
+        <v>571</v>
       </c>
       <c r="L15">
         <v>14.248215224493222</v>
@@ -13518,7 +13518,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>677</v>
+        <v>652</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13553,7 +13553,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="L16">
         <v>60.246276232111249</v>
@@ -13586,7 +13586,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>652</v>
+        <v>666</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13621,7 +13621,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13654,7 +13654,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>678</v>
+        <v>653</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13689,7 +13689,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>592</v>
+        <v>527</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13722,7 +13722,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13757,7 +13757,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="L19">
         <v>15.921767829784981</v>
@@ -13790,7 +13790,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>663</v>
+        <v>649</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13825,7 +13825,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13858,7 +13858,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13893,7 +13893,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>590</v>
+        <v>598</v>
       </c>
       <c r="L21">
         <v>11.156586435503245</v>
@@ -13926,7 +13926,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>671</v>
+        <v>659</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13961,7 +13961,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="L22">
         <v>6.3773535033999496</v>
@@ -13994,7 +13994,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>680</v>
+        <v>655</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14029,7 +14029,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>598</v>
+        <v>541</v>
       </c>
       <c r="L23">
         <v>4.8861340927283274</v>
@@ -14062,7 +14062,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14097,7 +14097,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="L24">
         <v>13.571087213989722</v>
@@ -14130,7 +14130,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14165,7 +14165,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>563</v>
+        <v>531</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14233,7 +14233,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14266,7 +14266,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>653</v>
+        <v>667</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14301,7 +14301,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14334,7 +14334,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>651</v>
+        <v>683</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14369,7 +14369,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14402,7 +14402,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14437,7 +14437,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14470,7 +14470,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14505,7 +14505,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14538,7 +14538,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>682</v>
+        <v>650</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14573,7 +14573,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14608,7 +14608,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14643,7 +14643,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14678,7 +14678,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>533</v>
+        <v>607</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14713,7 +14713,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14748,7 +14748,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>531</v>
+        <v>579</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14783,7 +14783,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14818,7 +14818,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14853,7 +14853,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="L39">
         <v>26.32580391715549</v>
@@ -14888,7 +14888,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14923,7 +14923,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14958,7 +14958,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>553</v>
+        <v>561</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14993,7 +14993,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>579</v>
+        <v>587</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15028,7 +15028,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>547</v>
+        <v>583</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15063,7 +15063,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>535</v>
+        <v>569</v>
       </c>
       <c r="L45">
         <v>11.262860315683808</v>
@@ -15098,7 +15098,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>594</v>
+        <v>537</v>
       </c>
       <c r="L46">
         <v>34.610640160809844</v>
@@ -15133,7 +15133,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15168,7 +15168,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>549</v>
+        <v>557</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15203,7 +15203,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="L49">
         <v>63.11239557797159</v>
@@ -15238,7 +15238,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>581</v>
+        <v>589</v>
       </c>
       <c r="L50">
         <v>38.222782480143309</v>
@@ -15273,7 +15273,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>561</v>
+        <v>529</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15308,7 +15308,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>551</v>
+        <v>559</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15323,7 +15323,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCB57C0B-8F62-4875-AD09-B39D723ADD42}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E17B74-F65C-4A1A-A217-54499849938A}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17140,7 +17140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75F9577A-6611-466A-914F-46AEDD88A9BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3612096E-0783-4ABB-9A3E-6CB6CF345C3C}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{888C9B7D-BC79-4146-8DE4-02217DE4D6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{263EE554-5FEE-40EC-A7AF-FDC0D80CC64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
     <t>ele</t>
   </si>
   <si>
-    <t>e_spv_001</t>
+    <t>e_spv_ZAF_001</t>
   </si>
   <si>
     <t>solar resource in cluster 1</t>
@@ -661,253 +661,253 @@
     <t>no</t>
   </si>
   <si>
-    <t>e_spv_002</t>
+    <t>e_spv_ZAF_002</t>
   </si>
   <si>
     <t>solar resource in cluster 2</t>
   </si>
   <si>
-    <t>e_spv_003</t>
+    <t>e_spv_ZAF_003</t>
   </si>
   <si>
     <t>solar resource in cluster 3</t>
   </si>
   <si>
-    <t>e_spv_004</t>
+    <t>e_spv_ZAF_004</t>
   </si>
   <si>
     <t>solar resource in cluster 4</t>
   </si>
   <si>
-    <t>e_spv_005</t>
+    <t>e_spv_ZAF_005</t>
   </si>
   <si>
     <t>solar resource in cluster 5</t>
   </si>
   <si>
-    <t>e_spv_006</t>
+    <t>e_spv_ZAF_006</t>
   </si>
   <si>
     <t>solar resource in cluster 6</t>
   </si>
   <si>
-    <t>e_spv_007</t>
+    <t>e_spv_ZAF_007</t>
   </si>
   <si>
     <t>solar resource in cluster 7</t>
   </si>
   <si>
-    <t>e_spv_008</t>
+    <t>e_spv_ZAF_008</t>
   </si>
   <si>
     <t>solar resource in cluster 8</t>
   </si>
   <si>
-    <t>e_spv_009</t>
+    <t>e_spv_ZAF_009</t>
   </si>
   <si>
     <t>solar resource in cluster 9</t>
   </si>
   <si>
-    <t>e_spv_010</t>
+    <t>e_spv_ZAF_010</t>
   </si>
   <si>
     <t>solar resource in cluster 10</t>
   </si>
   <si>
-    <t>e_spv_011</t>
+    <t>e_spv_ZAF_011</t>
   </si>
   <si>
     <t>solar resource in cluster 11</t>
   </si>
   <si>
-    <t>e_spv_012</t>
+    <t>e_spv_ZAF_012</t>
   </si>
   <si>
     <t>solar resource in cluster 12</t>
   </si>
   <si>
-    <t>e_spv_013</t>
+    <t>e_spv_ZAF_013</t>
   </si>
   <si>
     <t>solar resource in cluster 13</t>
   </si>
   <si>
-    <t>e_spv_014</t>
+    <t>e_spv_ZAF_014</t>
   </si>
   <si>
     <t>solar resource in cluster 14</t>
   </si>
   <si>
-    <t>e_spv_015</t>
+    <t>e_spv_ZAF_015</t>
   </si>
   <si>
     <t>solar resource in cluster 15</t>
   </si>
   <si>
-    <t>e_spv_016</t>
+    <t>e_spv_ZAF_016</t>
   </si>
   <si>
     <t>solar resource in cluster 16</t>
   </si>
   <si>
-    <t>e_spv_017</t>
+    <t>e_spv_ZAF_017</t>
   </si>
   <si>
     <t>solar resource in cluster 17</t>
   </si>
   <si>
-    <t>e_spv_018</t>
+    <t>e_spv_ZAF_018</t>
   </si>
   <si>
     <t>solar resource in cluster 18</t>
   </si>
   <si>
-    <t>e_spv_019</t>
+    <t>e_spv_ZAF_019</t>
   </si>
   <si>
     <t>solar resource in cluster 19</t>
   </si>
   <si>
-    <t>e_spv_020</t>
+    <t>e_spv_ZAF_020</t>
   </si>
   <si>
     <t>solar resource in cluster 20</t>
   </si>
   <si>
-    <t>e_spv_021</t>
+    <t>e_spv_ZAF_021</t>
   </si>
   <si>
     <t>solar resource in cluster 21</t>
   </si>
   <si>
-    <t>e_spv_022</t>
+    <t>e_spv_ZAF_022</t>
   </si>
   <si>
     <t>solar resource in cluster 22</t>
   </si>
   <si>
-    <t>e_spv_023</t>
+    <t>e_spv_ZAF_023</t>
   </si>
   <si>
     <t>solar resource in cluster 23</t>
   </si>
   <si>
-    <t>e_spv_024</t>
+    <t>e_spv_ZAF_024</t>
   </si>
   <si>
     <t>solar resource in cluster 24</t>
   </si>
   <si>
-    <t>e_spv_025</t>
+    <t>e_spv_ZAF_025</t>
   </si>
   <si>
     <t>solar resource in cluster 25</t>
   </si>
   <si>
-    <t>e_spv_026</t>
+    <t>e_spv_ZAF_026</t>
   </si>
   <si>
     <t>solar resource in cluster 26</t>
   </si>
   <si>
-    <t>e_spv_027</t>
+    <t>e_spv_ZAF_027</t>
   </si>
   <si>
     <t>solar resource in cluster 27</t>
   </si>
   <si>
-    <t>e_spv_028</t>
+    <t>e_spv_ZAF_028</t>
   </si>
   <si>
     <t>solar resource in cluster 28</t>
   </si>
   <si>
-    <t>e_spv_029</t>
+    <t>e_spv_ZAF_029</t>
   </si>
   <si>
     <t>solar resource in cluster 29</t>
   </si>
   <si>
-    <t>e_spv_030</t>
+    <t>e_spv_ZAF_030</t>
   </si>
   <si>
     <t>solar resource in cluster 30</t>
   </si>
   <si>
-    <t>e_spv_031</t>
+    <t>e_spv_ZAF_031</t>
   </si>
   <si>
     <t>solar resource in cluster 31</t>
   </si>
   <si>
-    <t>e_spv_032</t>
+    <t>e_spv_ZAF_032</t>
   </si>
   <si>
     <t>solar resource in cluster 32</t>
   </si>
   <si>
-    <t>e_spv_033</t>
+    <t>e_spv_ZAF_033</t>
   </si>
   <si>
     <t>solar resource in cluster 33</t>
   </si>
   <si>
-    <t>e_spv_034</t>
+    <t>e_spv_ZAF_034</t>
   </si>
   <si>
     <t>solar resource in cluster 34</t>
   </si>
   <si>
-    <t>e_spv_035</t>
+    <t>e_spv_ZAF_035</t>
   </si>
   <si>
     <t>solar resource in cluster 35</t>
   </si>
   <si>
-    <t>e_spv_036</t>
+    <t>e_spv_ZAF_036</t>
   </si>
   <si>
     <t>solar resource in cluster 36</t>
   </si>
   <si>
-    <t>e_spv_037</t>
+    <t>e_spv_ZAF_037</t>
   </si>
   <si>
     <t>solar resource in cluster 37</t>
   </si>
   <si>
-    <t>e_spv_038</t>
+    <t>e_spv_ZAF_038</t>
   </si>
   <si>
     <t>solar resource in cluster 38</t>
   </si>
   <si>
-    <t>e_spv_039</t>
+    <t>e_spv_ZAF_039</t>
   </si>
   <si>
     <t>solar resource in cluster 39</t>
   </si>
   <si>
-    <t>e_spv_040</t>
+    <t>e_spv_ZAF_040</t>
   </si>
   <si>
     <t>solar resource in cluster 40</t>
   </si>
   <si>
-    <t>e_spv_041</t>
+    <t>e_spv_ZAF_041</t>
   </si>
   <si>
     <t>solar resource in cluster 41</t>
   </si>
   <si>
-    <t>e_spv_042</t>
+    <t>e_spv_ZAF_042</t>
   </si>
   <si>
     <t>solar resource in cluster 42</t>
   </si>
   <si>
-    <t>e_spv_043</t>
+    <t>e_spv_ZAF_043</t>
   </si>
   <si>
     <t>solar resource in cluster 43</t>
@@ -925,133 +925,133 @@
     <t>af~fx</t>
   </si>
   <si>
-    <t>elc_spv_001</t>
-  </si>
-  <si>
-    <t>elc_spv_002</t>
-  </si>
-  <si>
-    <t>elc_spv_003</t>
-  </si>
-  <si>
-    <t>elc_spv_004</t>
-  </si>
-  <si>
-    <t>elc_spv_005</t>
-  </si>
-  <si>
-    <t>elc_spv_006</t>
-  </si>
-  <si>
-    <t>elc_spv_007</t>
-  </si>
-  <si>
-    <t>elc_spv_008</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_010</t>
-  </si>
-  <si>
-    <t>elc_spv_011</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_014</t>
-  </si>
-  <si>
-    <t>elc_spv_015</t>
-  </si>
-  <si>
-    <t>elc_spv_016</t>
-  </si>
-  <si>
-    <t>elc_spv_017</t>
-  </si>
-  <si>
-    <t>elc_spv_018</t>
-  </si>
-  <si>
-    <t>elc_spv_019</t>
-  </si>
-  <si>
-    <t>elc_spv_020</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_022</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_024</t>
-  </si>
-  <si>
-    <t>elc_spv_025</t>
-  </si>
-  <si>
-    <t>elc_spv_026</t>
-  </si>
-  <si>
-    <t>elc_spv_027</t>
-  </si>
-  <si>
-    <t>elc_spv_028</t>
-  </si>
-  <si>
-    <t>elc_spv_029</t>
-  </si>
-  <si>
-    <t>elc_spv_030</t>
-  </si>
-  <si>
-    <t>elc_spv_031</t>
-  </si>
-  <si>
-    <t>elc_spv_032</t>
-  </si>
-  <si>
-    <t>elc_spv_033</t>
-  </si>
-  <si>
-    <t>elc_spv_034</t>
-  </si>
-  <si>
-    <t>elc_spv_035</t>
-  </si>
-  <si>
-    <t>elc_spv_036</t>
-  </si>
-  <si>
-    <t>elc_spv_037</t>
-  </si>
-  <si>
-    <t>elc_spv_038</t>
-  </si>
-  <si>
-    <t>elc_spv_039</t>
-  </si>
-  <si>
-    <t>elc_spv_040</t>
-  </si>
-  <si>
-    <t>elc_spv_041</t>
-  </si>
-  <si>
-    <t>elc_spv_042</t>
-  </si>
-  <si>
-    <t>elc_spv_043</t>
+    <t>elc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_014</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_021</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_040</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>elc_spv_ZAF_043</t>
   </si>
   <si>
     <t>primarycg</t>
@@ -1060,1495 +1060,1495 @@
     <t>pre</t>
   </si>
   <si>
-    <t>distr_solelc_spv_007</t>
+    <t>distr_solelc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_007</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_021</t>
+    <t>distr_solelc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_021</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_solelc_spv_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_043</t>
+    <t>distr_solelc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_043</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
-    <t>e_w125754107-400,e_ZA39-400,e_w125769921-400,e_w167590549-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_w934819484-400,e_w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w167540668-400,e_w103079596-400,e_w693869805-400,e_w184201271-400,e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w87434264-400,e_ZA24-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w162871098-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400,e_w105759402-400,e_ZA31-400</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_ZA24-400,e_w105759402-400,e_w98231311-400,e_ZA26-400,e_w179136373-400,e_w178968761-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400,e_w200757306-400</t>
-  </si>
-  <si>
-    <t>e_ZA25-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w193977981-765,e_w183402339-400,e_ZA38-765,e_w142414070-400</t>
-  </si>
-  <si>
-    <t>e_w167648085-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_r17287657-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400,e_w156418705-400,e_ZA7-400</t>
-  </si>
-  <si>
-    <t>e_w836844162-400,e_w107431792-400,e_w545652232-400,e_ZA43-400,e_w182042518-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_w586032034-400,e_w934819484-400,e_w586032034-765,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>e_w208749745-400,e_ZA7-400,e_w156418705-400</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400,e_w142414070-765,e_w181366662-400</t>
-  </si>
-  <si>
-    <t>e_ZA3-400,e_w182408147-400,e_ZA2-400</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_w125754107-400,e_ZA25-400,e_w125769921-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400,e_w693869805-400,e_w230551819-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w142414070-400,e_w107937167-400,e_ZA28-765</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w87404898-400,e_w184201271-400,e_w359805008-400,e_w184581460-400,e_ZA14-400,e_w170672051-400,e_w1146812331-400</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_w104080393-400,e_w213181313-400,e_w167648085-400,e_w183759046-400,e_w238322344-400</t>
-  </si>
-  <si>
-    <t>e_w167590549-400,e_w89173873-400,e_w90454383-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>e_w107937167-400,e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w200223220-400,e_w631673098-400,e_w105759402-400</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>e_w107391770-400,e_w120941269-400,e_w219596295-400</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400,e_w586032034-765</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w167590549-400</t>
-  </si>
-  <si>
-    <t>e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
-  </si>
-  <si>
-    <t>e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>e_w156418705-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_ZA39-400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_ZA28-765,e_w496302277-400,e_w92348290-765,e_w181366662-765</t>
-  </si>
-  <si>
-    <t>e_w685294883-400,e_w1146812331-400,e_ZA4-400,e_w1146878078-400,e_w184560833-400,e_w184552955-400,e_w156418705-400,e_ZA7-400</t>
-  </si>
-  <si>
-    <t>e_w176362710-400,e_ZA33-400,e_ZA31-400,e_ZA30-400,e_w107391770-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>e_ZA23-400,e_w260486370-400,e_w156418705-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_008</t>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_008</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
-    <t>distr_wonelc_won_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_015</t>
+    <t>distr_wonelc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_015</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>elc_won_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400,e_ZA26-400,e_w179136373-400,e_w104080393-400,e_w213181313-400</t>
-  </si>
-  <si>
-    <t>elc_won_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400,e_ZA25-400,e_w125769921-400,e_w663042845-400,e_w663042849-400,e_w183402339-400</t>
-  </si>
-  <si>
-    <t>elc_won_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765,e_w200757306-400,e_ZA28-765,e_w181366662-400,e_w92348290-765,e_w181366662-765</t>
-  </si>
-  <si>
-    <t>elc_won_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765,e_w92348290-765,e_w102925909-400,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>elc_won_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w162871098-400,e_w125754107-400</t>
-  </si>
-  <si>
-    <t>elc_won_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_ZA39-400,e_w193978748-400</t>
-  </si>
-  <si>
-    <t>elc_won_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400,e_w89637370-400,e_w142414070-400,e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_won_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400,e_w125769921-400,e_ZA39-400,e_w167590549-400,e_w183402339-400,e_w193977981-765,e_ZA38-765</t>
-  </si>
-  <si>
-    <t>elc_won_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w167590549-400,e_w90454383-400,e_w169647963-400</t>
-  </si>
-  <si>
-    <t>elc_won_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w92348290-765</t>
-  </si>
-  <si>
-    <t>elc_won_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400,e_w631673098-400,e_w207991752-400,e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_won_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400,e_ZA14-400,e_w178968761-400,e_w179140081-400,e_w185497473-400,e_w179136373-765,e_w209365700-400,e_w209976655-400,e_ZA20-400,e_w238322344-400,e_w260486370-400</t>
-  </si>
-  <si>
-    <t>elc_won_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w219596295-400,e_w131625968-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400</t>
-  </si>
-  <si>
-    <t>elc_won_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400,e_w663042845-400</t>
-  </si>
-  <si>
-    <t>elc_won_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w496302277-400,e_w103079596-400</t>
-  </si>
-  <si>
-    <t>elc_won_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400,e_w127585817-400</t>
-  </si>
-  <si>
-    <t>elc_won_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400,e_w207991752-400</t>
-  </si>
-  <si>
-    <t>elc_won_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400,e_w181284049-400,e_w167648085-400</t>
-  </si>
-  <si>
-    <t>elc_won_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w193978748-400,e_w62218063-400,e_w836844162-400,e_w107431792-400,e_w102682082-400,e_w545652232-400,e_ZA43-400,e_w182042518-400</t>
-  </si>
-  <si>
-    <t>elc_won_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w89173873-400,e_w89637370-400</t>
-  </si>
-  <si>
-    <t>elc_won_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400,e_w200223220-400,e_w167540668-765,e_w178240552-400,e_w105759402-400,e_ZA24-400</t>
-  </si>
-  <si>
-    <t>elc_won_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w87404898-400,e_w184201271-400,e_w230551819-400,e_w359805008-400</t>
-  </si>
-  <si>
-    <t>elc_won_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400,e_ZA4-400,e_w184560833-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400,e_w230551819-400,e_ZA2-400,e_ZA14-400,e_w685294883-400,e_w170672051-400</t>
-  </si>
-  <si>
-    <t>elc_won_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w586032034-400,e_w586032034-765,e_w934819484-400,e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_won_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400,e_w183402339-400,e_w496302277-400</t>
-  </si>
-  <si>
-    <t>elc_won_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765,e_ZA39-400,e_w934819484-400,e_w167590549-400,e_w89173873-400</t>
-  </si>
-  <si>
-    <t>elc_won_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400</t>
-  </si>
-  <si>
-    <t>elc_won_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400,e_ZA38-765,e_w142414070-400,e_w142414070-765,e_w107937167-400</t>
-  </si>
-  <si>
-    <t>elc_won_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400,e_w103079596-400,e_w200223220-400,e_w167540668-400,e_w693869805-400,e_w184201271-400,e_w87434264-400,e_w105811523-400</t>
-  </si>
-  <si>
-    <t>elc_won_001</t>
-  </si>
-  <si>
-    <t>elc_won_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400,e_w176362710-400,e_ZA33-400,e_ZA36-400,e_w107391770-400</t>
-  </si>
-  <si>
-    <t>elc_won_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400,e_w685294883-400,e_ZA1-400,e_w208749745-400,e_w184552955-400</t>
-  </si>
-  <si>
-    <t>elc_won_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400,e_ZA26-400,e_ZA30-400,e_w167648085-400,e_w183759046-400,e_w104080393-400,e_w183757901-400,e_ZA23-400</t>
-  </si>
-  <si>
-    <t>elc_won_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400,e_w89637370-400,e_r17287657-400,e_w107937167-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_won_020</t>
-  </si>
-  <si>
-    <t>elc_won_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w125754107-400</t>
-  </si>
-  <si>
-    <t>elc_won_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400,e_w156418705-400,e_ZA7-400,e_w208749745-400</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400,e_w230551819-400,e_ZA3-400,e_w182408147-400</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_009</t>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_009</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_020</t>
+    <t>distr_wofelc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_020</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_007</t>
+    <t>distr_wofelc_wof_ZAF_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_011</t>
+    <t>distr_wofelc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_011</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_003</t>
+    <t>distr_wofelc_wof_ZAF_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>elc_wof_009</t>
-  </si>
-  <si>
-    <t>elc_wof_020</t>
-  </si>
-  <si>
-    <t>e_w934819484-400,e_w169789536-400,e_w90454383-400</t>
-  </si>
-  <si>
-    <t>elc_wof_005</t>
-  </si>
-  <si>
-    <t>elc_wof_007</t>
-  </si>
-  <si>
-    <t>e_r17287657-400,e_w631673098-400</t>
-  </si>
-  <si>
-    <t>elc_wof_012</t>
-  </si>
-  <si>
-    <t>e_ZA36-400,e_w107391770-400,e_w120941269-400,e_w131625968-400</t>
-  </si>
-  <si>
-    <t>elc_wof_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400,e_w169647963-400,e_r17287657-400</t>
-  </si>
-  <si>
-    <t>elc_wof_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400</t>
-  </si>
-  <si>
-    <t>elc_wof_004</t>
-  </si>
-  <si>
-    <t>elc_wof_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_006</t>
-  </si>
-  <si>
-    <t>elc_wof_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400,e_w102682082-400</t>
-  </si>
-  <si>
-    <t>elc_wof_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400</t>
-  </si>
-  <si>
-    <t>elc_wof_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400,e_ZA23-400,e_ZA11-400</t>
-  </si>
-  <si>
-    <t>elc_wof_002</t>
-  </si>
-  <si>
-    <t>e_w193465369-400,e_w107431792-400,e_w193978748-400,e_w836844162-400</t>
-  </si>
-  <si>
-    <t>elc_wof_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400,e_w177800991-400,e_w934819484-400</t>
-  </si>
-  <si>
-    <t>elc_wof_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400,e_w836844162-400,e_w62218063-400</t>
-  </si>
-  <si>
-    <t>elc_wof_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400,e_w193465369-400,e_w107431792-400</t>
-  </si>
-  <si>
-    <t>elc_wof_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400</t>
-  </si>
-  <si>
-    <t>elc_wof_017</t>
-  </si>
-  <si>
-    <t>e_won_001</t>
+    <t>elc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_won_ZAF_001</t>
   </si>
   <si>
     <t>wind resource in cluster 1</t>
   </si>
   <si>
-    <t>e_won_002</t>
+    <t>e_won_ZAF_002</t>
   </si>
   <si>
     <t>wind resource in cluster 2</t>
   </si>
   <si>
-    <t>e_won_003</t>
+    <t>e_won_ZAF_003</t>
   </si>
   <si>
     <t>wind resource in cluster 3</t>
   </si>
   <si>
-    <t>e_won_004</t>
+    <t>e_won_ZAF_004</t>
   </si>
   <si>
     <t>wind resource in cluster 4</t>
   </si>
   <si>
-    <t>e_won_005</t>
+    <t>e_won_ZAF_005</t>
   </si>
   <si>
     <t>wind resource in cluster 5</t>
   </si>
   <si>
-    <t>e_won_006</t>
+    <t>e_won_ZAF_006</t>
   </si>
   <si>
     <t>wind resource in cluster 6</t>
   </si>
   <si>
-    <t>e_won_007</t>
+    <t>e_won_ZAF_007</t>
   </si>
   <si>
     <t>wind resource in cluster 7</t>
   </si>
   <si>
-    <t>e_won_008</t>
+    <t>e_won_ZAF_008</t>
   </si>
   <si>
     <t>wind resource in cluster 8</t>
   </si>
   <si>
-    <t>e_won_009</t>
+    <t>e_won_ZAF_009</t>
   </si>
   <si>
     <t>wind resource in cluster 9</t>
   </si>
   <si>
-    <t>e_won_010</t>
+    <t>e_won_ZAF_010</t>
   </si>
   <si>
     <t>wind resource in cluster 10</t>
   </si>
   <si>
-    <t>e_won_011</t>
+    <t>e_won_ZAF_011</t>
   </si>
   <si>
     <t>wind resource in cluster 11</t>
   </si>
   <si>
-    <t>e_won_012</t>
+    <t>e_won_ZAF_012</t>
   </si>
   <si>
     <t>wind resource in cluster 12</t>
   </si>
   <si>
-    <t>e_won_013</t>
+    <t>e_won_ZAF_013</t>
   </si>
   <si>
     <t>wind resource in cluster 13</t>
   </si>
   <si>
-    <t>e_won_014</t>
+    <t>e_won_ZAF_014</t>
   </si>
   <si>
     <t>wind resource in cluster 14</t>
   </si>
   <si>
-    <t>e_won_015</t>
+    <t>e_won_ZAF_015</t>
   </si>
   <si>
     <t>wind resource in cluster 15</t>
   </si>
   <si>
-    <t>e_won_016</t>
+    <t>e_won_ZAF_016</t>
   </si>
   <si>
     <t>wind resource in cluster 16</t>
   </si>
   <si>
-    <t>e_won_017</t>
+    <t>e_won_ZAF_017</t>
   </si>
   <si>
     <t>wind resource in cluster 17</t>
   </si>
   <si>
-    <t>e_won_018</t>
+    <t>e_won_ZAF_018</t>
   </si>
   <si>
     <t>wind resource in cluster 18</t>
   </si>
   <si>
-    <t>e_won_019</t>
+    <t>e_won_ZAF_019</t>
   </si>
   <si>
     <t>wind resource in cluster 19</t>
   </si>
   <si>
-    <t>e_won_020</t>
+    <t>e_won_ZAF_020</t>
   </si>
   <si>
     <t>wind resource in cluster 20</t>
   </si>
   <si>
-    <t>e_won_021</t>
+    <t>e_won_ZAF_021</t>
   </si>
   <si>
     <t>wind resource in cluster 21</t>
   </si>
   <si>
-    <t>e_won_022</t>
+    <t>e_won_ZAF_022</t>
   </si>
   <si>
     <t>wind resource in cluster 22</t>
   </si>
   <si>
-    <t>e_won_023</t>
+    <t>e_won_ZAF_023</t>
   </si>
   <si>
     <t>wind resource in cluster 23</t>
   </si>
   <si>
-    <t>e_won_024</t>
+    <t>e_won_ZAF_024</t>
   </si>
   <si>
     <t>wind resource in cluster 24</t>
   </si>
   <si>
-    <t>e_won_025</t>
+    <t>e_won_ZAF_025</t>
   </si>
   <si>
     <t>wind resource in cluster 25</t>
   </si>
   <si>
-    <t>e_won_026</t>
+    <t>e_won_ZAF_026</t>
   </si>
   <si>
     <t>wind resource in cluster 26</t>
   </si>
   <si>
-    <t>e_won_027</t>
+    <t>e_won_ZAF_027</t>
   </si>
   <si>
     <t>wind resource in cluster 27</t>
   </si>
   <si>
-    <t>e_won_028</t>
+    <t>e_won_ZAF_028</t>
   </si>
   <si>
     <t>wind resource in cluster 28</t>
   </si>
   <si>
-    <t>e_won_029</t>
+    <t>e_won_ZAF_029</t>
   </si>
   <si>
     <t>wind resource in cluster 29</t>
   </si>
   <si>
-    <t>e_won_030</t>
+    <t>e_won_ZAF_030</t>
   </si>
   <si>
     <t>wind resource in cluster 30</t>
   </si>
   <si>
-    <t>e_won_031</t>
+    <t>e_won_ZAF_031</t>
   </si>
   <si>
     <t>wind resource in cluster 31</t>
   </si>
   <si>
-    <t>e_won_032</t>
+    <t>e_won_ZAF_032</t>
   </si>
   <si>
     <t>wind resource in cluster 32</t>
   </si>
   <si>
-    <t>e_won_033</t>
+    <t>e_won_ZAF_033</t>
   </si>
   <si>
     <t>wind resource in cluster 33</t>
   </si>
   <si>
-    <t>e_won_034</t>
+    <t>e_won_ZAF_034</t>
   </si>
   <si>
     <t>wind resource in cluster 34</t>
   </si>
   <si>
-    <t>e_won_035</t>
+    <t>e_won_ZAF_035</t>
   </si>
   <si>
     <t>wind resource in cluster 35</t>
   </si>
   <si>
-    <t>e_won_036</t>
+    <t>e_won_ZAF_036</t>
   </si>
   <si>
     <t>wind resource in cluster 36</t>
   </si>
   <si>
-    <t>e_won_037</t>
+    <t>e_won_ZAF_037</t>
   </si>
   <si>
     <t>wind resource in cluster 37</t>
   </si>
   <si>
-    <t>e_won_038</t>
+    <t>e_won_ZAF_038</t>
   </si>
   <si>
     <t>wind resource in cluster 38</t>
   </si>
   <si>
-    <t>e_won_039</t>
+    <t>e_won_ZAF_039</t>
   </si>
   <si>
     <t>wind resource in cluster 39</t>
   </si>
   <si>
-    <t>e_won_040</t>
+    <t>e_won_ZAF_040</t>
   </si>
   <si>
     <t>wind resource in cluster 40</t>
   </si>
   <si>
-    <t>e_won_041</t>
+    <t>e_won_ZAF_041</t>
   </si>
   <si>
     <t>wind resource in cluster 41</t>
   </si>
   <si>
-    <t>e_won_042</t>
+    <t>e_won_ZAF_042</t>
   </si>
   <si>
     <t>wind resource in cluster 42</t>
   </si>
   <si>
-    <t>e_wof_001</t>
+    <t>e_wof_ZAF_001</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 1</t>
   </si>
   <si>
-    <t>e_wof_002</t>
+    <t>e_wof_ZAF_002</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 2</t>
   </si>
   <si>
-    <t>e_wof_003</t>
+    <t>e_wof_ZAF_003</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 3</t>
   </si>
   <si>
-    <t>e_wof_004</t>
+    <t>e_wof_ZAF_004</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 4</t>
   </si>
   <si>
-    <t>e_wof_005</t>
+    <t>e_wof_ZAF_005</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 5</t>
   </si>
   <si>
-    <t>e_wof_006</t>
+    <t>e_wof_ZAF_006</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 6</t>
   </si>
   <si>
-    <t>e_wof_007</t>
+    <t>e_wof_ZAF_007</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 7</t>
   </si>
   <si>
-    <t>e_wof_008</t>
+    <t>e_wof_ZAF_008</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 8</t>
   </si>
   <si>
-    <t>e_wof_009</t>
+    <t>e_wof_ZAF_009</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 9</t>
   </si>
   <si>
-    <t>e_wof_010</t>
+    <t>e_wof_ZAF_010</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 10</t>
   </si>
   <si>
-    <t>e_wof_011</t>
+    <t>e_wof_ZAF_011</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 11</t>
   </si>
   <si>
-    <t>e_wof_012</t>
+    <t>e_wof_ZAF_012</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 12</t>
   </si>
   <si>
-    <t>e_wof_013</t>
+    <t>e_wof_ZAF_013</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 13</t>
   </si>
   <si>
-    <t>e_wof_014</t>
+    <t>e_wof_ZAF_014</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 14</t>
   </si>
   <si>
-    <t>e_wof_015</t>
+    <t>e_wof_ZAF_015</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 15</t>
   </si>
   <si>
-    <t>e_wof_016</t>
+    <t>e_wof_ZAF_016</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 16</t>
   </si>
   <si>
-    <t>e_wof_017</t>
+    <t>e_wof_ZAF_017</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 17</t>
   </si>
   <si>
-    <t>e_wof_018</t>
+    <t>e_wof_ZAF_018</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 18</t>
   </si>
   <si>
-    <t>e_wof_019</t>
+    <t>e_wof_ZAF_019</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 19</t>
   </si>
   <si>
-    <t>e_wof_020</t>
+    <t>e_wof_ZAF_020</t>
   </si>
   <si>
     <t>wind offshore resource in cluster 20</t>
@@ -2623,100 +2623,100 @@
     <t>yes</t>
   </si>
   <si>
-    <t>stepdown_w142414070_765to400</t>
-  </si>
-  <si>
-    <t>e_w142414070-765</t>
-  </si>
-  <si>
-    <t>e_w142414070-400</t>
-  </si>
-  <si>
-    <t>stepup_w142414070_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w167540668_765to400</t>
-  </si>
-  <si>
-    <t>e_w167540668-765</t>
-  </si>
-  <si>
-    <t>e_w167540668-400</t>
-  </si>
-  <si>
-    <t>stepup_w167540668_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w178968761_765to400</t>
-  </si>
-  <si>
-    <t>e_w178968761-765</t>
-  </si>
-  <si>
-    <t>e_w178968761-400</t>
-  </si>
-  <si>
-    <t>stepup_w178968761_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w179136373_765to400</t>
-  </si>
-  <si>
-    <t>e_w179136373-765</t>
-  </si>
-  <si>
-    <t>e_w179136373-400</t>
-  </si>
-  <si>
-    <t>stepup_w179136373_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w181366662_765to400</t>
-  </si>
-  <si>
-    <t>e_w181366662-765</t>
-  </si>
-  <si>
-    <t>e_w181366662-400</t>
-  </si>
-  <si>
-    <t>stepup_w181366662_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w219384657_765to400</t>
-  </si>
-  <si>
-    <t>e_w219384657-765</t>
-  </si>
-  <si>
-    <t>e_w219384657-400</t>
-  </si>
-  <si>
-    <t>stepup_w219384657_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w586032034_765to400</t>
-  </si>
-  <si>
-    <t>e_w586032034-765</t>
-  </si>
-  <si>
-    <t>e_w586032034-400</t>
-  </si>
-  <si>
-    <t>stepup_w586032034_400to765</t>
-  </si>
-  <si>
-    <t>stepdown_w92348290_765to400</t>
-  </si>
-  <si>
-    <t>e_w92348290-765</t>
-  </si>
-  <si>
-    <t>e_w92348290-400</t>
-  </si>
-  <si>
-    <t>stepup_w92348290_400to765</t>
+    <t>stepdown_w142414070_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w142414070_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w167540668_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w167540668-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w167540668_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w178968761_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w178968761-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w178968761_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w179136373_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w179136373-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179136373-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w179136373_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w181366662_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w181366662_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w219384657_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w219384657-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219384657-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w219384657_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w586032034_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w586032034_ZAF_400to765</t>
+  </si>
+  <si>
+    <t>stepdown_w92348290_ZAF_765to400</t>
+  </si>
+  <si>
+    <t>e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w92348290-400_ZAF</t>
+  </si>
+  <si>
+    <t>stepup_w92348290_ZAF_400to765</t>
   </si>
   <si>
     <t>activityunit</t>
@@ -2725,55 +2725,55 @@
     <t>capacityunit</t>
   </si>
   <si>
-    <t>Transformer: e_w142414070-765 → e_w142414070-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w142414070-400 → e_w142414070-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w167540668-765 → e_w167540668-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w167540668-400 → e_w167540668-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w178968761-765 → e_w178968761-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w178968761-400 → e_w178968761-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w179136373-765 → e_w179136373-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w179136373-400 → e_w179136373-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w181366662-765 → e_w181366662-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w181366662-400 → e_w181366662-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w219384657-765 → e_w219384657-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w219384657-400 → e_w219384657-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w586032034-765 → e_w586032034-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w586032034-400 → e_w586032034-765</t>
-  </si>
-  <si>
-    <t>Transformer: e_w92348290-765 → e_w92348290-400</t>
-  </si>
-  <si>
-    <t>Transformer: e_w92348290-400 → e_w92348290-765</t>
-  </si>
-  <si>
-    <t>e_ZA11-400,e_ZA40-400,e_ZA41-400,e_ZA44-400,e_w120941269-400,e_w169647963-400,e_w169789536-400,e_w182042518-400,e_w219384657-400,e_w219384657-765,e_w545652232-400,e_w62193952-400,e_w62218063-400,e_w836844162-400,e_w90454383-400</t>
+    <t>Transformer: e_w142414070-765_ZAF → e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w142414070-400_ZAF → e_w142414070-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w167540668-765_ZAF → e_w167540668-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w167540668-400_ZAF → e_w167540668-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w178968761-765_ZAF → e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w178968761-400_ZAF → e_w178968761-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w179136373-765_ZAF → e_w179136373-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w179136373-400_ZAF → e_w179136373-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w181366662-765_ZAF → e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w181366662-400_ZAF → e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w219384657-765_ZAF → e_w219384657-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w219384657-400_ZAF → e_w219384657-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w586032034-765_ZAF → e_w586032034-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w586032034-400_ZAF → e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w92348290-765_ZAF → e_w92348290-400_ZAF</t>
+  </si>
+  <si>
+    <t>Transformer: e_w92348290-400_ZAF → e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</t>
   </si>
 </sst>
 </file>
@@ -3727,6 +3727,9 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover"/>
       <sheetName val="ELC_Lists"/>
@@ -4667,7 +4670,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_ZA11-400,e_ZA40-400,e_ZA41-400,e_ZA44-400,e_w120941269-400,e_w169647963-400,e_w169789536-400,e_w182042518-400,e_w219384657-400,e_w219384657-765,e_w545652232-400,e_w62193952-400,e_w62218063-400,e_w836844162-400,e_w90454383-400</v>
+        <v>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4689,7 +4692,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_ZA11-400,e_ZA40-400,e_ZA41-400,e_ZA44-400,e_w120941269-400,e_w169647963-400,e_w169789536-400,e_w182042518-400,e_w219384657-400,e_w219384657-765,e_w545652232-400,e_w62193952-400,e_w62218063-400,e_w836844162-400,e_w90454383-400</v>
+        <v>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -7505,7 +7508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55544942-4C2D-43AE-807F-081B3263B226}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA5A8EA2-AC97-4E8A-9C6C-5DD0716DB4BF}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7710,10 +7713,10 @@
         <v>265</v>
       </c>
       <c r="L11">
-        <v>56.429478435887411</v>
+        <v>56.354478435887408</v>
       </c>
       <c r="M11">
-        <v>0.25207647823266571</v>
+        <v>0.25208959618772531</v>
       </c>
       <c r="O11" t="s">
         <v>309</v>
@@ -7743,16 +7746,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99299045119957896</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB11">
-        <v>128.50839467438524</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7785,10 +7788,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99676762792199902</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP11">
-        <v>59.260154763351615</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7818,13 +7821,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>566</v>
+        <v>650</v>
       </c>
       <c r="BC11">
-        <v>0.99507162964364948</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD11">
-        <v>90.353456533092867</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7856,10 +7859,10 @@
         <v>266</v>
       </c>
       <c r="L12">
-        <v>97.940509255758968</v>
+        <v>97.153409255758959</v>
       </c>
       <c r="M12">
-        <v>0.26109049573058718</v>
+        <v>0.26107416062241862</v>
       </c>
       <c r="O12" t="s">
         <v>309</v>
@@ -7889,16 +7892,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99495781957805363</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB12">
-        <v>92.439974402351027</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7931,10 +7934,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99606892759117205</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP12">
-        <v>72.069660828511601</v>
+        <v>110.17470964763046</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7961,16 +7964,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BB12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="BC12">
-        <v>0.99229811324031303</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD12">
-        <v>141.20125726092687</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8002,10 +8005,10 @@
         <v>267</v>
       </c>
       <c r="L13">
-        <v>40.535152029925861</v>
+        <v>40.328452029925863</v>
       </c>
       <c r="M13">
-        <v>0.25990698994338879</v>
+        <v>0.2599120182920357</v>
       </c>
       <c r="O13" t="s">
         <v>309</v>
@@ -8035,16 +8038,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99672872587342576</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB13">
-        <v>59.973358987194473</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8077,10 +8080,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99824683646529189</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP13">
-        <v>32.141331469648897</v>
+        <v>64.84977570462992</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8107,10 +8110,10 @@
         <v>613</v>
       </c>
       <c r="BA13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BB13" t="s">
-        <v>558</v>
+        <v>528</v>
       </c>
       <c r="BC13">
         <v>0.99581145929743231</v>
@@ -8148,10 +8151,10 @@
         <v>268</v>
       </c>
       <c r="L14">
-        <v>42.823197842342175</v>
+        <v>41.897697842342176</v>
       </c>
       <c r="M14">
-        <v>0.2553457994494347</v>
+        <v>0.25525242245654889</v>
       </c>
       <c r="O14" t="s">
         <v>309</v>
@@ -8181,16 +8184,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99464845307754257</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB14">
-        <v>98.111693578387175</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8223,10 +8226,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.99333523291287673</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP14">
-        <v>122.18739659725948</v>
+        <v>77.236409972479407</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8253,16 +8256,16 @@
         <v>615</v>
       </c>
       <c r="BA14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BB14" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BC14">
-        <v>0.99582070241731502</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD14">
-        <v>76.620455682557321</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8294,10 +8297,10 @@
         <v>269</v>
       </c>
       <c r="L15">
-        <v>38.657737868310825</v>
+        <v>38.204737868310822</v>
       </c>
       <c r="M15">
-        <v>0.25368717475149188</v>
+        <v>0.2536874619803503</v>
       </c>
       <c r="O15" t="s">
         <v>309</v>
@@ -8327,16 +8330,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.9951066982538278</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB15">
-        <v>89.710532013157362</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8366,13 +8369,13 @@
         <v>535</v>
       </c>
       <c r="AN15" t="s">
-        <v>536</v>
+        <v>421</v>
       </c>
       <c r="AO15">
-        <v>0.99201650479533909</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP15">
-        <v>146.36407875211563</v>
+        <v>73.443263495810669</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8399,16 +8402,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="BC15">
-        <v>0.99501631001524238</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD15">
-        <v>91.367649720556983</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8440,10 +8443,10 @@
         <v>270</v>
       </c>
       <c r="L16">
-        <v>44.158408061296171</v>
+        <v>43.812908061296163</v>
       </c>
       <c r="M16">
-        <v>0.26700187736591419</v>
+        <v>0.26697566246182752</v>
       </c>
       <c r="O16" t="s">
         <v>309</v>
@@ -8473,16 +8476,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99466941924265306</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB16">
-        <v>97.727313884694652</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8509,16 +8512,16 @@
         <v>453</v>
       </c>
       <c r="AM16" t="s">
+        <v>536</v>
+      </c>
+      <c r="AN16" t="s">
         <v>537</v>
       </c>
-      <c r="AN16" t="s">
-        <v>538</v>
-      </c>
       <c r="AO16">
-        <v>0.9960576359591049</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP16">
-        <v>72.276674083075989</v>
+        <v>38.251429847691753</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8545,16 +8548,16 @@
         <v>619</v>
       </c>
       <c r="BA16" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="BB16" t="s">
-        <v>658</v>
+        <v>528</v>
       </c>
       <c r="BC16">
-        <v>0.99462081464868646</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD16">
-        <v>98.618398107414592</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8619,16 +8622,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>307</v>
+        <v>266</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99599691424900794</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB17">
-        <v>73.389905434855194</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8655,16 +8658,16 @@
         <v>455</v>
       </c>
       <c r="AM17" t="s">
+        <v>538</v>
+      </c>
+      <c r="AN17" t="s">
         <v>539</v>
       </c>
-      <c r="AN17" t="s">
-        <v>540</v>
-      </c>
       <c r="AO17">
-        <v>0.99514523900053742</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP17">
-        <v>89.003951656813172</v>
+        <v>72.069660828511601</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8697,10 +8700,10 @@
         <v>660</v>
       </c>
       <c r="BC17">
-        <v>0.99447517161328947</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD17">
-        <v>101.28852042302684</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8765,16 +8768,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99450846292949968</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB18">
-        <v>100.67817962584009</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8801,16 +8804,16 @@
         <v>457</v>
       </c>
       <c r="AM18" t="s">
+        <v>540</v>
+      </c>
+      <c r="AN18" t="s">
         <v>541</v>
       </c>
-      <c r="AN18" t="s">
-        <v>542</v>
-      </c>
       <c r="AO18">
-        <v>0.99515836501188337</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP18">
-        <v>88.763308115471318</v>
+        <v>89.511926450871471</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,13 +8843,13 @@
         <v>661</v>
       </c>
       <c r="BB18" t="s">
-        <v>421</v>
+        <v>600</v>
       </c>
       <c r="BC18">
-        <v>0.98830355217046739</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD18">
-        <v>214.43487687476414</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8878,10 +8881,10 @@
         <v>273</v>
       </c>
       <c r="L19">
-        <v>105.97700341595768</v>
+        <v>104.55610341595768</v>
       </c>
       <c r="M19">
-        <v>0.26626360775868613</v>
+        <v>0.26627156085778991</v>
       </c>
       <c r="O19" t="s">
         <v>309</v>
@@ -8911,16 +8914,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.98298990306503153</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB19">
-        <v>311.85177714108931</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8947,16 +8950,16 @@
         <v>459</v>
       </c>
       <c r="AM19" t="s">
+        <v>542</v>
+      </c>
+      <c r="AN19" t="s">
         <v>543</v>
       </c>
-      <c r="AN19" t="s">
-        <v>544</v>
-      </c>
       <c r="AO19">
-        <v>0.99399231910847008</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP19">
-        <v>110.14081634471604</v>
+        <v>100.63855719912947</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8989,10 +8992,10 @@
         <v>663</v>
       </c>
       <c r="BC19">
-        <v>0.98743040674179927</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD19">
-        <v>230.44254306701379</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9024,10 +9027,10 @@
         <v>274</v>
       </c>
       <c r="L20">
-        <v>2.3952801575716864</v>
+        <v>2.3740801575716861</v>
       </c>
       <c r="M20">
-        <v>0.23745087287451869</v>
+        <v>0.2374475117546864</v>
       </c>
       <c r="O20" t="s">
         <v>309</v>
@@ -9057,16 +9060,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99493070276109996</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB20">
-        <v>92.937116046500407</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9093,16 +9096,16 @@
         <v>461</v>
       </c>
       <c r="AM20" t="s">
+        <v>544</v>
+      </c>
+      <c r="AN20" t="s">
         <v>545</v>
       </c>
-      <c r="AN20" t="s">
-        <v>546</v>
-      </c>
       <c r="AO20">
-        <v>0.99433440313430599</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP20">
-        <v>103.86927587105613</v>
+        <v>154.37346914756148</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9135,10 +9138,10 @@
         <v>665</v>
       </c>
       <c r="BC20">
-        <v>0.99279657608325511</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD20">
-        <v>132.06277180699064</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9170,10 +9173,10 @@
         <v>275</v>
       </c>
       <c r="L21">
-        <v>12.904824068159623</v>
+        <v>12.520224068159623</v>
       </c>
       <c r="M21">
-        <v>0.2451476227155413</v>
+        <v>0.24512325744256841</v>
       </c>
       <c r="O21" t="s">
         <v>309</v>
@@ -9203,16 +9206,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99536059527709431</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB21">
-        <v>85.055753253270055</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9239,16 +9242,16 @@
         <v>463</v>
       </c>
       <c r="AM21" t="s">
+        <v>546</v>
+      </c>
+      <c r="AN21" t="s">
         <v>547</v>
       </c>
-      <c r="AN21" t="s">
-        <v>548</v>
-      </c>
       <c r="AO21">
-        <v>0.99165427860211908</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP21">
-        <v>153.00489229448431</v>
+        <v>111.02977673354209</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,13 +9281,13 @@
         <v>666</v>
       </c>
       <c r="BB21" t="s">
-        <v>558</v>
+        <v>430</v>
       </c>
       <c r="BC21">
-        <v>0.99223220184557481</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD21">
-        <v>142.40963283112865</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9316,10 +9319,10 @@
         <v>276</v>
       </c>
       <c r="L22">
-        <v>29.31230018687852</v>
+        <v>29.302100186878523</v>
       </c>
       <c r="M22">
-        <v>0.2488724719138711</v>
+        <v>0.24887404635798621</v>
       </c>
       <c r="O22" t="s">
         <v>309</v>
@@ -9349,16 +9352,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99695083910621241</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB22">
-        <v>55.901283052772143</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9385,16 +9388,16 @@
         <v>465</v>
       </c>
       <c r="AM22" t="s">
+        <v>548</v>
+      </c>
+      <c r="AN22" t="s">
         <v>549</v>
       </c>
-      <c r="AN22" t="s">
-        <v>550</v>
-      </c>
       <c r="AO22">
-        <v>0.99572967547870339</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP22">
-        <v>78.289282890438841</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9427,10 +9430,10 @@
         <v>668</v>
       </c>
       <c r="BC22">
-        <v>0.99429876975975018</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD22">
-        <v>104.52255440457925</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9462,10 +9465,10 @@
         <v>277</v>
       </c>
       <c r="L23">
-        <v>22.214470816241736</v>
+        <v>22.128470816241737</v>
       </c>
       <c r="M23">
-        <v>0.25603972465784708</v>
+        <v>0.25603328475412201</v>
       </c>
       <c r="O23" t="s">
         <v>309</v>
@@ -9495,16 +9498,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>298</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99615584710269711</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB23">
-        <v>70.476136450553028</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9531,16 +9534,16 @@
         <v>467</v>
       </c>
       <c r="AM23" t="s">
+        <v>550</v>
+      </c>
+      <c r="AN23" t="s">
         <v>551</v>
       </c>
-      <c r="AN23" t="s">
-        <v>552</v>
-      </c>
       <c r="AO23">
-        <v>0.99620690928326405</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP23">
-        <v>69.53999647349201</v>
+        <v>150.6984130259078</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9573,10 +9576,10 @@
         <v>670</v>
       </c>
       <c r="BC23">
-        <v>0.99672758029478525</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD23">
-        <v>59.994361262269514</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9641,16 +9644,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99565105035038126</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB24">
-        <v>79.730743576343073</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9677,16 +9680,16 @@
         <v>469</v>
       </c>
       <c r="AM24" t="s">
+        <v>552</v>
+      </c>
+      <c r="AN24" t="s">
         <v>553</v>
       </c>
-      <c r="AN24" t="s">
-        <v>554</v>
-      </c>
       <c r="AO24">
-        <v>0.99830579859179591</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP24">
-        <v>31.060359150407386</v>
+        <v>78.445591424369994</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9719,10 +9722,10 @@
         <v>672</v>
       </c>
       <c r="BC24">
-        <v>0.98805842341846151</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD24">
-        <v>218.92890399487229</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9754,10 +9757,10 @@
         <v>279</v>
       </c>
       <c r="L25">
-        <v>2.3538967711813057</v>
+        <v>2.3487967711813051</v>
       </c>
       <c r="M25">
-        <v>0.21199843631213611</v>
+        <v>0.2120030875174293</v>
       </c>
       <c r="O25" t="s">
         <v>309</v>
@@ -9787,16 +9790,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99715230385125297</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB25">
-        <v>52.207762727027884</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9823,16 +9826,16 @@
         <v>471</v>
       </c>
       <c r="AM25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN25" t="s">
         <v>555</v>
       </c>
-      <c r="AN25" t="s">
-        <v>556</v>
-      </c>
       <c r="AO25">
-        <v>0.9951764810877296</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP25">
-        <v>88.431180058290352</v>
+        <v>72.473564293852363</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9865,10 +9868,10 @@
         <v>674</v>
       </c>
       <c r="BC25">
-        <v>0.991900752046595</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD25">
-        <v>148.48621247909063</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9939,10 +9942,10 @@
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99545552704228712</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB26">
-        <v>83.315337558069643</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9969,16 +9972,16 @@
         <v>473</v>
       </c>
       <c r="AM26" t="s">
+        <v>556</v>
+      </c>
+      <c r="AN26" t="s">
         <v>557</v>
       </c>
-      <c r="AN26" t="s">
-        <v>558</v>
-      </c>
       <c r="AO26">
-        <v>0.99468222901836267</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP26">
-        <v>97.492467996683757</v>
+        <v>153.25643118471478</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10011,10 +10014,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.99231435496704667</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD26">
-        <v>140.90349227081035</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10079,16 +10082,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.9895807450862778</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB27">
-        <v>191.01967341824059</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10115,16 +10118,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
+        <v>558</v>
+      </c>
+      <c r="AN27" t="s">
         <v>559</v>
       </c>
-      <c r="AN27" t="s">
-        <v>560</v>
-      </c>
       <c r="AO27">
-        <v>0.98687966194564902</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP27">
-        <v>240.53953099643502</v>
+        <v>75.626528315847352</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10157,10 +10160,10 @@
         <v>678</v>
       </c>
       <c r="BC27">
-        <v>0.99481516601444531</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD27">
-        <v>95.055289735168813</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10225,16 +10228,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99528373638972145</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB28">
-        <v>86.464832855106309</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10261,16 +10264,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
+        <v>560</v>
+      </c>
+      <c r="AN28" t="s">
         <v>561</v>
       </c>
-      <c r="AN28" t="s">
-        <v>562</v>
-      </c>
       <c r="AO28">
-        <v>0.98860885963065015</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP28">
-        <v>208.83757343808102</v>
+        <v>78.289282890438841</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10300,13 +10303,13 @@
         <v>679</v>
       </c>
       <c r="BB28" t="s">
-        <v>680</v>
+        <v>410</v>
       </c>
       <c r="BC28">
-        <v>0.99545422785121029</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD28">
-        <v>83.33915606114418</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10338,10 +10341,10 @@
         <v>283</v>
       </c>
       <c r="L29">
-        <v>6.780535686435802</v>
+        <v>6.779335686435803</v>
       </c>
       <c r="M29">
-        <v>0.2232796212133317</v>
+        <v>0.2232809215219326</v>
       </c>
       <c r="O29" t="s">
         <v>309</v>
@@ -10371,16 +10374,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>266</v>
+        <v>302</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99297090277863642</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB29">
-        <v>128.86678239166531</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10407,16 +10410,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
+        <v>562</v>
+      </c>
+      <c r="AN29" t="s">
         <v>563</v>
       </c>
-      <c r="AN29" t="s">
-        <v>564</v>
-      </c>
       <c r="AO29">
-        <v>0.99164055829901554</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP29">
-        <v>153.25643118471478</v>
+        <v>73.025825491381909</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10443,16 +10446,16 @@
         <v>645</v>
       </c>
       <c r="BA29" t="s">
+        <v>680</v>
+      </c>
+      <c r="BB29" t="s">
         <v>681</v>
       </c>
-      <c r="BB29" t="s">
-        <v>682</v>
-      </c>
       <c r="BC29">
-        <v>0.98843991010136767</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD29">
-        <v>211.93498147492642</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10484,10 +10487,10 @@
         <v>284</v>
       </c>
       <c r="L30">
-        <v>4.354279652922429</v>
+        <v>4.3507796529224292</v>
       </c>
       <c r="M30">
-        <v>0.2273175886369857</v>
+        <v>0.2273195455779386</v>
       </c>
       <c r="O30" t="s">
         <v>309</v>
@@ -10517,16 +10520,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99726845868655478</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB30">
-        <v>50.078257413162468</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10553,16 +10556,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
+        <v>564</v>
+      </c>
+      <c r="AN30" t="s">
         <v>565</v>
       </c>
-      <c r="AN30" t="s">
-        <v>566</v>
-      </c>
       <c r="AO30">
-        <v>0.99692167417445865</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP30">
-        <v>56.43597346825765</v>
+        <v>69.53999647349201</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10589,16 +10592,16 @@
         <v>647</v>
       </c>
       <c r="BA30" t="s">
+        <v>682</v>
+      </c>
+      <c r="BB30" t="s">
         <v>683</v>
       </c>
-      <c r="BB30" t="s">
-        <v>429</v>
-      </c>
       <c r="BC30">
-        <v>0.99010219056094972</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD30">
-        <v>181.45983971592244</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10663,16 +10666,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99681605507557702</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB31">
-        <v>58.372323614420687</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10699,16 +10702,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AN31" t="s">
-        <v>568</v>
+        <v>435</v>
       </c>
       <c r="AO31">
-        <v>0.99677069953771458</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP31">
-        <v>59.203841808565592</v>
+        <v>92.557267939235231</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10773,16 +10776,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99590798933590385</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB32">
-        <v>75.020195508429936</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10809,16 +10812,16 @@
         <v>485</v>
       </c>
       <c r="AM32" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AN32" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="AO32">
-        <v>0.99606896061575723</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP32">
-        <v>72.069055377783442</v>
+        <v>88.42284494294006</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10850,10 +10853,10 @@
         <v>287</v>
       </c>
       <c r="L33">
-        <v>10.151636249684735</v>
+        <v>10.147336249684731</v>
       </c>
       <c r="M33">
-        <v>0.18815941777915471</v>
+        <v>0.188156077225243</v>
       </c>
       <c r="O33" t="s">
         <v>309</v>
@@ -10883,16 +10886,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99588491419783987</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB33">
-        <v>75.443239706269793</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10919,16 +10922,16 @@
         <v>487</v>
       </c>
       <c r="AM33" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="AN33" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="AO33">
-        <v>0.99415308404615776</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP33">
-        <v>107.19345915377383</v>
+        <v>29.627234098515917</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10960,10 +10963,10 @@
         <v>288</v>
       </c>
       <c r="L34">
-        <v>16.998068135490481</v>
+        <v>16.99686813549048</v>
       </c>
       <c r="M34">
-        <v>0.19477093059803541</v>
+        <v>0.19477049371676591</v>
       </c>
       <c r="O34" t="s">
         <v>309</v>
@@ -10993,16 +10996,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99021378007306371</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB34">
-        <v>179.41403199383166</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11029,16 +11032,16 @@
         <v>489</v>
       </c>
       <c r="AM34" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="AN34" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="AO34">
-        <v>0.99578710491059208</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP34">
-        <v>77.236409972479407</v>
+        <v>83.095996952896456</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11070,10 +11073,10 @@
         <v>289</v>
       </c>
       <c r="L35">
-        <v>20.691784306073561</v>
+        <v>20.543784306073562</v>
       </c>
       <c r="M35">
-        <v>0.2073770682577383</v>
+        <v>0.20737376047649481</v>
       </c>
       <c r="O35" t="s">
         <v>309</v>
@@ -11103,16 +11106,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99315447263323475</v>
+        <v>0.99446824002516876</v>
       </c>
       <c r="AB35">
-        <v>125.50133505736341</v>
+        <v>101.41559953857198</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11139,16 +11142,16 @@
         <v>491</v>
       </c>
       <c r="AM35" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AN35" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="AO35">
-        <v>0.99838396904917182</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP35">
-        <v>29.627234098515917</v>
+        <v>59.260154763351615</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11180,10 +11183,10 @@
         <v>290</v>
       </c>
       <c r="L36">
-        <v>14.371597679532691</v>
+        <v>14.36889767953269</v>
       </c>
       <c r="M36">
-        <v>0.22194550173217681</v>
+        <v>0.22194579047261079</v>
       </c>
       <c r="O36" t="s">
         <v>309</v>
@@ -11213,16 +11216,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99649986768340049</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB36">
-        <v>64.16909247099106</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11249,16 +11252,16 @@
         <v>493</v>
       </c>
       <c r="AM36" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="AN36" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="AO36">
-        <v>0.99796084623978776</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP36">
-        <v>37.384485603890518</v>
+        <v>208.83757343808102</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11323,16 +11326,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99827081845920873</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB37">
-        <v>31.701661581174136</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11359,16 +11362,16 @@
         <v>495</v>
       </c>
       <c r="AM37" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="AN37" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="AO37">
-        <v>0.99546749107529653</v>
+        <v>0.99333075340694588</v>
       </c>
       <c r="AP37">
-        <v>83.095996952896456</v>
+        <v>122.26952087265865</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11433,16 +11436,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99341896335341162</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB38">
-        <v>120.65233852078616</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11469,16 +11472,16 @@
         <v>497</v>
       </c>
       <c r="AM38" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="AN38" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AO38">
-        <v>0.99587491663731742</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP38">
-        <v>75.626528315847352</v>
+        <v>146.36407875211563</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11543,16 +11546,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99315245009067388</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB39">
-        <v>125.5384150043114</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11579,16 +11582,16 @@
         <v>499</v>
       </c>
       <c r="AM39" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="AN39" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="AO39">
-        <v>0.9945106241527748</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP39">
-        <v>100.63855719912947</v>
+        <v>88.431180058290352</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11653,16 +11656,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99399085439572143</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB40">
-        <v>110.16766941177411</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11689,16 +11692,16 @@
         <v>501</v>
       </c>
       <c r="AM40" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AN40" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="AO40">
-        <v>0.99509878714312805</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP40">
-        <v>89.85556904265141</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11763,16 +11766,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99601337563103476</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB41">
-        <v>73.088113431029612</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11799,16 +11802,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="AN41" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AO41">
-        <v>0.99178008656222316</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP41">
-        <v>150.6984130259078</v>
+        <v>111.10955342049355</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11840,10 +11843,10 @@
         <v>296</v>
       </c>
       <c r="L42">
-        <v>1.6388504698729149</v>
+        <v>1.6357504698729151</v>
       </c>
       <c r="M42">
-        <v>0.18266247456258269</v>
+        <v>0.18265086375731221</v>
       </c>
       <c r="O42" t="s">
         <v>309</v>
@@ -11873,16 +11876,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99758018972146978</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB42">
-        <v>44.363188439721</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11909,16 +11912,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="AN42" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AO42">
-        <v>0.99398790580290575</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP42">
-        <v>110.2217269467279</v>
+        <v>77.611856892252987</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11983,16 +11986,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99456731509164431</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB43">
-        <v>99.599223319854588</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12019,16 +12022,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="AN43" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AO43">
-        <v>0.99646273950702013</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP43">
-        <v>64.84977570462992</v>
+        <v>37.384485603890518</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12093,16 +12096,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99635213764962971</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB44">
-        <v>66.877476423454894</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12129,16 +12132,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="AN44" t="s">
-        <v>409</v>
+        <v>592</v>
       </c>
       <c r="AO44">
-        <v>0.99599400380931946</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP44">
-        <v>73.443263495810669</v>
+        <v>90.729435350939028</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12170,10 +12173,10 @@
         <v>299</v>
       </c>
       <c r="L45">
-        <v>10.303329586985814</v>
+        <v>10.300829586985813</v>
       </c>
       <c r="M45">
-        <v>0.23437547258180519</v>
+        <v>0.23438031305128909</v>
       </c>
       <c r="O45" t="s">
         <v>309</v>
@@ -12203,16 +12206,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99331818519922233</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB45">
-        <v>122.49993801425808</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12239,16 +12242,16 @@
         <v>511</v>
       </c>
       <c r="AM45" t="s">
+        <v>593</v>
+      </c>
+      <c r="AN45" t="s">
         <v>594</v>
       </c>
-      <c r="AN45" t="s">
-        <v>595</v>
-      </c>
       <c r="AO45">
-        <v>0.99788320682147802</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP45">
-        <v>38.807874939569167</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12280,10 +12283,10 @@
         <v>300</v>
       </c>
       <c r="L46">
-        <v>2.6360968796725124</v>
+        <v>2.634896879672513</v>
       </c>
       <c r="M46">
-        <v>0.2042826035183809</v>
+        <v>0.2042854491814535</v>
       </c>
       <c r="O46" t="s">
         <v>309</v>
@@ -12313,16 +12316,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99849240016674334</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB46">
-        <v>27.639330276371737</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12349,16 +12352,16 @@
         <v>513</v>
       </c>
       <c r="AM46" t="s">
+        <v>595</v>
+      </c>
+      <c r="AN46" t="s">
         <v>596</v>
       </c>
-      <c r="AN46" t="s">
-        <v>597</v>
-      </c>
       <c r="AO46">
-        <v>0.99505112170813059</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP46">
-        <v>90.729435350939028</v>
+        <v>240.53953099643502</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12423,16 +12426,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99484635552608569</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB47">
-        <v>94.483482021761333</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12459,16 +12462,16 @@
         <v>515</v>
       </c>
       <c r="AM47" t="s">
+        <v>597</v>
+      </c>
+      <c r="AN47" t="s">
         <v>598</v>
       </c>
-      <c r="AN47" t="s">
-        <v>599</v>
-      </c>
       <c r="AO47">
-        <v>0.9979252881755144</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP47">
-        <v>38.036383448902463</v>
+        <v>104.26406003195649</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12500,10 +12503,10 @@
         <v>302</v>
       </c>
       <c r="L48">
-        <v>63.720446576087795</v>
+        <v>63.412446576087802</v>
       </c>
       <c r="M48">
-        <v>0.23318065257061349</v>
+        <v>0.23317134732857389</v>
       </c>
       <c r="O48" t="s">
         <v>309</v>
@@ -12533,16 +12536,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99197366299435197</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB48">
-        <v>147.14951177021345</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12569,16 +12572,16 @@
         <v>517</v>
       </c>
       <c r="AM48" t="s">
+        <v>599</v>
+      </c>
+      <c r="AN48" t="s">
         <v>600</v>
       </c>
-      <c r="AN48" t="s">
-        <v>601</v>
-      </c>
       <c r="AO48">
-        <v>0.99576958396989479</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP48">
-        <v>77.557627218594661</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12610,10 +12613,10 @@
         <v>303</v>
       </c>
       <c r="L49">
-        <v>29.239068847577361</v>
+        <v>29.13576884757736</v>
       </c>
       <c r="M49">
-        <v>0.22460706804417219</v>
+        <v>0.2246012823477575</v>
       </c>
       <c r="O49" t="s">
         <v>309</v>
@@ -12643,16 +12646,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99520836470773288</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB49">
-        <v>87.846647024897322</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12679,16 +12682,16 @@
         <v>519</v>
       </c>
       <c r="AM49" t="s">
+        <v>601</v>
+      </c>
+      <c r="AN49" t="s">
         <v>602</v>
       </c>
-      <c r="AN49" t="s">
-        <v>413</v>
-      </c>
       <c r="AO49">
-        <v>0.99495142174876894</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP49">
-        <v>92.557267939235231</v>
+        <v>31.154905747485419</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12720,10 +12723,10 @@
         <v>304</v>
       </c>
       <c r="L50">
-        <v>19.549817854653909</v>
+        <v>19.489217854653909</v>
       </c>
       <c r="M50">
-        <v>0.2287196564423056</v>
+        <v>0.2287280726107829</v>
       </c>
       <c r="O50" t="s">
         <v>309</v>
@@ -12753,16 +12756,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99492063738174197</v>
+        <v>0.99331672850632224</v>
       </c>
       <c r="AB50">
-        <v>93.121648001396338</v>
+        <v>122.52664405075954</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12795,10 +12798,10 @@
         <v>604</v>
       </c>
       <c r="AO50">
-        <v>0.99504825389388352</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP50">
-        <v>90.782011945468795</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12830,10 +12833,10 @@
         <v>305</v>
       </c>
       <c r="L51">
-        <v>28.757070855030403</v>
+        <v>28.273574477569518</v>
       </c>
       <c r="M51">
-        <v>0.24859980825566219</v>
+        <v>0.24860198280857571</v>
       </c>
       <c r="O51" t="s">
         <v>309</v>
@@ -12869,10 +12872,10 @@
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99698749491520611</v>
+        <v>0.99698458324869177</v>
       </c>
       <c r="AB51">
-        <v>55.229259887887068</v>
+        <v>55.282640440651299</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12905,10 +12908,10 @@
         <v>606</v>
       </c>
       <c r="AO51">
-        <v>0.99247550518926964</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP51">
-        <v>137.94907153005732</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12940,10 +12943,10 @@
         <v>306</v>
       </c>
       <c r="L52">
-        <v>25.892135224655235</v>
+        <v>25.472835224655235</v>
       </c>
       <c r="M52">
-        <v>0.24134502600928109</v>
+        <v>0.24128363316485779</v>
       </c>
       <c r="O52" t="s">
         <v>309</v>
@@ -12973,16 +12976,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99766238113026029</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB52">
-        <v>42.856345945228725</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13015,10 +13018,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99576662598769528</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP52">
-        <v>77.611856892252987</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13050,10 +13053,10 @@
         <v>307</v>
       </c>
       <c r="L53">
-        <v>21.239563863148575</v>
+        <v>21.226063863148575</v>
       </c>
       <c r="M53">
-        <v>0.23194852600613919</v>
+        <v>0.2319501736913773</v>
       </c>
       <c r="O53" t="s">
         <v>309</v>
@@ -13083,16 +13086,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99567492323161799</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB53">
-        <v>79.293074087003873</v>
+        <v>73.421601000514329</v>
       </c>
     </row>
   </sheetData>
@@ -13101,7 +13104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA204E96-72D3-4208-8875-BACCCB53D2B6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0A35BE-0E6F-4AF3-B9E5-869202DAEC41}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13213,13 +13216,13 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>593</v>
+        <v>535</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
       </c>
       <c r="M11">
-        <v>0.1843319915380067</v>
+        <v>0.18433199254240021</v>
       </c>
       <c r="O11" t="s">
         <v>172</v>
@@ -13246,7 +13249,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>677</v>
+        <v>664</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13281,13 +13284,13 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
       <c r="L12">
-        <v>41.625170147271362</v>
+        <v>41.38517014727136</v>
       </c>
       <c r="M12">
-        <v>0.2641821193468662</v>
+        <v>0.2638323307979224</v>
       </c>
       <c r="O12" t="s">
         <v>172</v>
@@ -13314,7 +13317,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>673</v>
+        <v>651</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13349,13 +13352,13 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
       </c>
       <c r="M13">
-        <v>0.1448045738501898</v>
+        <v>0.1448045754986462</v>
       </c>
       <c r="O13" t="s">
         <v>172</v>
@@ -13382,7 +13385,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13417,13 +13420,13 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>581</v>
+        <v>558</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
       </c>
       <c r="M14">
-        <v>0.14724526375320399</v>
+        <v>0.1472452646883205</v>
       </c>
       <c r="O14" t="s">
         <v>172</v>
@@ -13450,7 +13453,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>661</v>
+        <v>679</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13485,13 +13488,13 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>571</v>
+        <v>546</v>
       </c>
       <c r="L15">
-        <v>14.248215224493222</v>
+        <v>13.570215224493221</v>
       </c>
       <c r="M15">
-        <v>0.2270019606139384</v>
+        <v>0.2275446266892821</v>
       </c>
       <c r="O15" t="s">
         <v>172</v>
@@ -13518,7 +13521,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13553,13 +13556,13 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>585</v>
+        <v>540</v>
       </c>
       <c r="L16">
-        <v>60.246276232111249</v>
+        <v>59.282276232111244</v>
       </c>
       <c r="M16">
-        <v>0.29796998234161798</v>
+        <v>0.29757266403047927</v>
       </c>
       <c r="O16" t="s">
         <v>172</v>
@@ -13586,7 +13589,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>666</v>
+        <v>658</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13621,13 +13624,13 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
       </c>
       <c r="M17">
-        <v>0.1016094115504282</v>
+        <v>0.10160941375580169</v>
       </c>
       <c r="O17" t="s">
         <v>172</v>
@@ -13654,7 +13657,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13689,13 +13692,13 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>527</v>
+        <v>573</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
       </c>
       <c r="M18">
-        <v>0.20062430489929889</v>
+        <v>0.2006243063465184</v>
       </c>
       <c r="O18" t="s">
         <v>172</v>
@@ -13722,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13757,13 +13760,13 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>553</v>
+        <v>601</v>
       </c>
       <c r="L19">
-        <v>15.921767829784981</v>
+        <v>15.766767829784982</v>
       </c>
       <c r="M19">
-        <v>0.2098918338026157</v>
+        <v>0.2093672016716305</v>
       </c>
       <c r="O19" t="s">
         <v>172</v>
@@ -13790,7 +13793,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13825,13 +13828,13 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>567</v>
+        <v>605</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
       </c>
       <c r="M20">
-        <v>8.5955872642622402E-2</v>
+        <v>8.5955873032015601E-2</v>
       </c>
       <c r="O20" t="s">
         <v>172</v>
@@ -13858,7 +13861,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13893,13 +13896,13 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>598</v>
+        <v>536</v>
       </c>
       <c r="L21">
-        <v>11.156586435503245</v>
+        <v>11.016586435503244</v>
       </c>
       <c r="M21">
-        <v>0.1458988949348993</v>
+        <v>0.14608853294175</v>
       </c>
       <c r="O21" t="s">
         <v>172</v>
@@ -13926,7 +13929,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>659</v>
+        <v>680</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13961,13 +13964,13 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>600</v>
+        <v>552</v>
       </c>
       <c r="L22">
-        <v>6.3773535033999496</v>
+        <v>6.1733535033999489</v>
       </c>
       <c r="M22">
-        <v>0.26612703444830588</v>
+        <v>0.26562209869187098</v>
       </c>
       <c r="O22" t="s">
         <v>172</v>
@@ -13994,7 +13997,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14029,13 +14032,13 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>541</v>
+        <v>567</v>
       </c>
       <c r="L23">
-        <v>4.8861340927283274</v>
+        <v>4.8541340927283274</v>
       </c>
       <c r="M23">
-        <v>0.30360257079112291</v>
+        <v>0.30315144838934321</v>
       </c>
       <c r="O23" t="s">
         <v>172</v>
@@ -14062,7 +14065,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14097,13 +14100,13 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="L24">
-        <v>13.571087213989722</v>
+        <v>13.114783900591691</v>
       </c>
       <c r="M24">
-        <v>0.19929607412876171</v>
+        <v>0.1930178375150288</v>
       </c>
       <c r="O24" t="s">
         <v>172</v>
@@ -14130,7 +14133,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14165,13 +14168,13 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
       </c>
       <c r="M25">
-        <v>0.11880817254789069</v>
+        <v>0.1188081729625151</v>
       </c>
       <c r="O25" t="s">
         <v>172</v>
@@ -14198,7 +14201,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14233,13 +14236,13 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>555</v>
+        <v>581</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
       </c>
       <c r="M26">
-        <v>0.26308084673963789</v>
+        <v>0.2630808486393762</v>
       </c>
       <c r="O26" t="s">
         <v>172</v>
@@ -14266,7 +14269,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14301,13 +14304,13 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>565</v>
+        <v>599</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
       </c>
       <c r="M27">
-        <v>9.3570387474760999E-2</v>
+        <v>9.3570388278180705E-2</v>
       </c>
       <c r="O27" t="s">
         <v>172</v>
@@ -14334,7 +14337,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14369,13 +14372,13 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
       </c>
       <c r="M28">
-        <v>0.32076749760644679</v>
+        <v>0.32076749874204119</v>
       </c>
       <c r="O28" t="s">
         <v>172</v>
@@ -14402,7 +14405,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14437,13 +14440,13 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
       </c>
       <c r="M29">
-        <v>0.14789509056852229</v>
+        <v>0.1478950901773681</v>
       </c>
       <c r="O29" t="s">
         <v>172</v>
@@ -14470,7 +14473,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14505,13 +14508,13 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>602</v>
+        <v>566</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
       </c>
       <c r="M30">
-        <v>0.17149549523455249</v>
+        <v>0.17149549876626999</v>
       </c>
       <c r="O30" t="s">
         <v>172</v>
@@ -14538,7 +14541,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>650</v>
+        <v>671</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14573,13 +14576,13 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
       </c>
       <c r="M31">
-        <v>0.2166175963211332</v>
+        <v>0.2166175972934255</v>
       </c>
     </row>
     <row r="32" spans="2:26">
@@ -14608,13 +14611,13 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
       </c>
       <c r="M32">
-        <v>0.10417096817583441</v>
+        <v>0.104170969653659</v>
       </c>
     </row>
     <row r="33" spans="2:13">
@@ -14643,13 +14646,13 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
       </c>
       <c r="M33">
-        <v>0.2050393536459105</v>
+        <v>0.2050393593730995</v>
       </c>
     </row>
     <row r="34" spans="2:13">
@@ -14678,13 +14681,13 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
       </c>
       <c r="M34">
-        <v>0.21608568854715859</v>
+        <v>0.21608569331385249</v>
       </c>
     </row>
     <row r="35" spans="2:13">
@@ -14713,13 +14716,13 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
       </c>
       <c r="M35">
-        <v>0.143845838858737</v>
+        <v>0.1438458406474295</v>
       </c>
     </row>
     <row r="36" spans="2:13">
@@ -14748,13 +14751,13 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
       </c>
       <c r="M36">
-        <v>0.1070354092669597</v>
+        <v>0.10703541144568141</v>
       </c>
     </row>
     <row r="37" spans="2:13">
@@ -14783,13 +14786,13 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>573</v>
+        <v>533</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
       </c>
       <c r="M37">
-        <v>0.22472775896605149</v>
+        <v>0.2247277620360586</v>
       </c>
     </row>
     <row r="38" spans="2:13">
@@ -14818,13 +14821,13 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>591</v>
+        <v>531</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
       </c>
       <c r="M38">
-        <v>0.23523818012163661</v>
+        <v>0.23523818252810319</v>
       </c>
     </row>
     <row r="39" spans="2:13">
@@ -14853,13 +14856,13 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>533</v>
+        <v>577</v>
       </c>
       <c r="L39">
-        <v>26.32580391715549</v>
+        <v>26.291803917155487</v>
       </c>
       <c r="M39">
-        <v>0.28020228387492641</v>
+        <v>0.28021487518392479</v>
       </c>
     </row>
     <row r="40" spans="2:13">
@@ -14888,13 +14891,13 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>535</v>
+        <v>579</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
       </c>
       <c r="M40">
-        <v>0.23411117543992219</v>
+        <v>0.23411117506850479</v>
       </c>
     </row>
     <row r="41" spans="2:13">
@@ -14923,13 +14926,13 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
       </c>
       <c r="M41">
-        <v>0.2721920265122556</v>
+        <v>0.27219202668797271</v>
       </c>
     </row>
     <row r="42" spans="2:13">
@@ -14958,13 +14961,13 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
       </c>
       <c r="M42">
-        <v>0.28623389287532353</v>
+        <v>0.28623388974188912</v>
       </c>
     </row>
     <row r="43" spans="2:13">
@@ -14993,13 +14996,13 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>587</v>
+        <v>550</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
       </c>
       <c r="M43">
-        <v>0.3484200860985141</v>
+        <v>0.348420078803785</v>
       </c>
     </row>
     <row r="44" spans="2:13">
@@ -15028,13 +15031,13 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>583</v>
+        <v>542</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
       </c>
       <c r="M44">
-        <v>0.29648623812476937</v>
+        <v>0.2964862404499255</v>
       </c>
     </row>
     <row r="45" spans="2:13">
@@ -15063,13 +15066,13 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="L45">
-        <v>11.262860315683808</v>
+        <v>10.919135648131764</v>
       </c>
       <c r="M45">
-        <v>0.370916188296673</v>
+        <v>0.36891972512195198</v>
       </c>
     </row>
     <row r="46" spans="2:13">
@@ -15098,13 +15101,13 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>537</v>
+        <v>554</v>
       </c>
       <c r="L46">
-        <v>34.610640160809844</v>
+        <v>33.912640160809843</v>
       </c>
       <c r="M46">
-        <v>0.31938677936207349</v>
+        <v>0.31815403336967979</v>
       </c>
     </row>
     <row r="47" spans="2:13">
@@ -15133,13 +15136,13 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
       </c>
       <c r="M47">
-        <v>0.23211275790412131</v>
+        <v>0.23211276252305649</v>
       </c>
     </row>
     <row r="48" spans="2:13">
@@ -15168,13 +15171,13 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>557</v>
+        <v>527</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
       </c>
       <c r="M48">
-        <v>0.18932181859163921</v>
+        <v>0.18932182375750431</v>
       </c>
     </row>
     <row r="49" spans="2:13">
@@ -15203,13 +15206,13 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>545</v>
+        <v>597</v>
       </c>
       <c r="L49">
-        <v>63.11239557797159</v>
+        <v>62.791395577971592</v>
       </c>
       <c r="M49">
-        <v>0.40984504679108119</v>
+        <v>0.40980925718823819</v>
       </c>
     </row>
     <row r="50" spans="2:13">
@@ -15238,13 +15241,13 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="L50">
-        <v>38.222782480143309</v>
+        <v>37.678782480143312</v>
       </c>
       <c r="M50">
-        <v>0.33995720411689029</v>
+        <v>0.33908004774906758</v>
       </c>
     </row>
     <row r="51" spans="2:13">
@@ -15273,13 +15276,13 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
       </c>
       <c r="M51">
-        <v>0.33623081374544261</v>
+        <v>0.33623081279274131</v>
       </c>
     </row>
     <row r="52" spans="2:13">
@@ -15308,13 +15311,13 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>559</v>
+        <v>595</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
       </c>
       <c r="M52">
-        <v>0.31961940066535188</v>
+        <v>0.31961939788339488</v>
       </c>
     </row>
   </sheetData>
@@ -15323,7 +15326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11E17B74-F65C-4A1A-A217-54499849938A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72363F4-7B83-467B-A90E-486DDED2ACAA}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17140,7 +17143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3612096E-0783-4ABB-9A3E-6CB6CF345C3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD27DDF0-5A7D-4072-83E4-F503CB98AE83}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{263EE554-5FEE-40EC-A7AF-FDC0D80CC64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{669ADC9E-6FF1-4BE7-9D8B-2186D9F2373E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,18 +1060,72 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_018</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_016</t>
   </si>
   <si>
@@ -1102,6 +1156,30 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_002</t>
   </si>
   <si>
@@ -1126,6 +1204,60 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_012</t>
   </si>
   <si>
@@ -1138,58 +1270,46 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
     <t>distr_solelc_spv_ZAF_035</t>
@@ -1204,132 +1324,39 @@
     <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+  </si>
+  <si>
     <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
   </si>
   <si>
@@ -1348,6 +1375,18 @@
     <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
   </si>
   <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
   </si>
   <si>
@@ -1360,37 +1399,58 @@
     <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
   </si>
   <si>
+    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
   </si>
   <si>
     <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
   </si>
   <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
     <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
@@ -1399,64 +1459,106 @@
     <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
   </si>
   <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+    <t>distr_wonelc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_038</t>
@@ -1477,22 +1579,70 @@
     <t>connecting wind onshore to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
+    <t>distr_wonelc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_041</t>
@@ -1525,34 +1675,22 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>distr_wonelc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_004</t>
@@ -1567,148 +1705,106 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ZAF_037</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>elc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_038</t>
@@ -1729,19 +1825,70 @@
     <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_041</t>
@@ -1774,34 +1921,22 @@
     <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_004</t>
@@ -1816,145 +1951,124 @@
     <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_won_ZAF_037</t>
   </si>
   <si>
     <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+    <t>distr_wofelc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_012</t>
@@ -1963,223 +2077,109 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
+    <t>elc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_012</t>
   </si>
   <si>
     <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_005</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
   </si>
   <si>
     <t>e_won_ZAF_001</t>
@@ -7508,7 +7508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA5A8EA2-AC97-4E8A-9C6C-5DD0716DB4BF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{826B3F18-CA90-45FF-A352-E256C39428C1}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7746,16 +7746,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99456731509164431</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB11">
-        <v>99.599223319854588</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7788,10 +7788,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99468222901836267</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP11">
-        <v>97.492467996683757</v>
+        <v>73.025825491381909</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7821,13 +7821,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>650</v>
+        <v>560</v>
       </c>
       <c r="BC11">
-        <v>0.99501631001524238</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD11">
-        <v>91.367649720556983</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7892,16 +7892,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99466941924265306</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB12">
-        <v>97.727313884694652</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7934,10 +7934,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99399047038285648</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP12">
-        <v>110.17470964763046</v>
+        <v>69.53999647349201</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7964,16 +7964,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
+        <v>650</v>
+      </c>
+      <c r="BB12" t="s">
         <v>651</v>
       </c>
-      <c r="BB12" t="s">
-        <v>652</v>
-      </c>
       <c r="BC12">
-        <v>0.991900752046595</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD12">
-        <v>148.48621247909063</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8038,16 +8038,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99527761530085967</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB13">
-        <v>86.577052817573119</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8077,13 +8077,13 @@
         <v>531</v>
       </c>
       <c r="AN13" t="s">
-        <v>532</v>
+        <v>440</v>
       </c>
       <c r="AO13">
-        <v>0.99646273950702013</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP13">
-        <v>64.84977570462992</v>
+        <v>92.557267939235231</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8110,16 +8110,16 @@
         <v>613</v>
       </c>
       <c r="BA13" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="BB13" t="s">
-        <v>528</v>
+        <v>578</v>
       </c>
       <c r="BC13">
-        <v>0.99581145929743231</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD13">
-        <v>76.789912880408167</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8184,16 +8184,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.9951066982538278</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB14">
-        <v>89.710532013157362</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8220,16 +8220,16 @@
         <v>449</v>
       </c>
       <c r="AM14" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AN14" t="s">
-        <v>534</v>
+        <v>441</v>
       </c>
       <c r="AO14">
-        <v>0.99578710491059208</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP14">
-        <v>77.236409972479407</v>
+        <v>73.443263495810669</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8256,16 +8256,16 @@
         <v>615</v>
       </c>
       <c r="BA14" t="s">
+        <v>653</v>
+      </c>
+      <c r="BB14" t="s">
         <v>654</v>
       </c>
-      <c r="BB14" t="s">
-        <v>655</v>
-      </c>
       <c r="BC14">
-        <v>0.99429876975975018</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD14">
-        <v>104.52255440457925</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8330,16 +8330,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99681791473814529</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB15">
-        <v>58.33822980066963</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8366,16 +8366,16 @@
         <v>451</v>
       </c>
       <c r="AM15" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="AN15" t="s">
-        <v>421</v>
+        <v>534</v>
       </c>
       <c r="AO15">
-        <v>0.99599400380931946</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP15">
-        <v>73.443263495810669</v>
+        <v>38.251429847691753</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8402,16 +8402,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
+        <v>655</v>
+      </c>
+      <c r="BB15" t="s">
         <v>656</v>
       </c>
-      <c r="BB15" t="s">
-        <v>657</v>
-      </c>
       <c r="BC15">
-        <v>0.98743040674179927</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD15">
-        <v>230.44254306701379</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8476,16 +8476,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.98958063849079669</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB16">
-        <v>191.02162766872783</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8512,16 +8512,16 @@
         <v>453</v>
       </c>
       <c r="AM16" t="s">
+        <v>535</v>
+      </c>
+      <c r="AN16" t="s">
         <v>536</v>
       </c>
-      <c r="AN16" t="s">
-        <v>537</v>
-      </c>
       <c r="AO16">
-        <v>0.99791355837194406</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP16">
-        <v>38.251429847691753</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8548,16 +8548,16 @@
         <v>619</v>
       </c>
       <c r="BA16" t="s">
+        <v>657</v>
+      </c>
+      <c r="BB16" t="s">
         <v>658</v>
       </c>
-      <c r="BB16" t="s">
-        <v>528</v>
-      </c>
       <c r="BC16">
-        <v>0.99223220184557481</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD16">
-        <v>142.40963283112865</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8622,16 +8622,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99294071263677341</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB17">
-        <v>129.42026832582172</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8658,16 +8658,16 @@
         <v>455</v>
       </c>
       <c r="AM17" t="s">
+        <v>537</v>
+      </c>
+      <c r="AN17" t="s">
         <v>538</v>
       </c>
-      <c r="AN17" t="s">
-        <v>539</v>
-      </c>
       <c r="AO17">
-        <v>0.99606892759117205</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP17">
-        <v>72.069660828511601</v>
+        <v>150.6984130259078</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8697,13 +8697,13 @@
         <v>659</v>
       </c>
       <c r="BB17" t="s">
-        <v>660</v>
+        <v>432</v>
       </c>
       <c r="BC17">
-        <v>0.99462081464868646</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD17">
-        <v>98.618398107414592</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8768,16 +8768,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99535442409010222</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB18">
-        <v>85.168891681458845</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8804,16 +8804,16 @@
         <v>457</v>
       </c>
       <c r="AM18" t="s">
+        <v>539</v>
+      </c>
+      <c r="AN18" t="s">
         <v>540</v>
       </c>
-      <c r="AN18" t="s">
-        <v>541</v>
-      </c>
       <c r="AO18">
-        <v>0.99511753128449787</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP18">
-        <v>89.511926450871471</v>
+        <v>78.445591424369994</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,16 +8840,16 @@
         <v>623</v>
       </c>
       <c r="BA18" t="s">
+        <v>660</v>
+      </c>
+      <c r="BB18" t="s">
         <v>661</v>
       </c>
-      <c r="BB18" t="s">
-        <v>600</v>
-      </c>
       <c r="BC18">
-        <v>0.99507162964364948</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD18">
-        <v>90.353456533092867</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8914,16 +8914,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>305</v>
+        <v>268</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99309463181702251</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB19">
-        <v>126.5984166879211</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8950,16 +8950,16 @@
         <v>459</v>
       </c>
       <c r="AM19" t="s">
+        <v>541</v>
+      </c>
+      <c r="AN19" t="s">
         <v>542</v>
       </c>
-      <c r="AN19" t="s">
-        <v>543</v>
-      </c>
       <c r="AO19">
-        <v>0.9945106241527748</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP19">
-        <v>100.63855719912947</v>
+        <v>90.729435350939028</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8989,13 +8989,13 @@
         <v>662</v>
       </c>
       <c r="BB19" t="s">
-        <v>663</v>
+        <v>405</v>
       </c>
       <c r="BC19">
-        <v>0.98805842341846151</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD19">
-        <v>218.92890399487229</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9060,16 +9060,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99827081845920873</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB20">
-        <v>31.701661581174136</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9096,16 +9096,16 @@
         <v>461</v>
       </c>
       <c r="AM20" t="s">
+        <v>543</v>
+      </c>
+      <c r="AN20" t="s">
         <v>544</v>
       </c>
-      <c r="AN20" t="s">
-        <v>545</v>
-      </c>
       <c r="AO20">
-        <v>0.9915796289555876</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP20">
-        <v>154.37346914756148</v>
+        <v>208.83757343808102</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9132,16 +9132,16 @@
         <v>627</v>
       </c>
       <c r="BA20" t="s">
+        <v>663</v>
+      </c>
+      <c r="BB20" t="s">
         <v>664</v>
       </c>
-      <c r="BB20" t="s">
-        <v>665</v>
-      </c>
       <c r="BC20">
-        <v>0.99481516601444531</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD20">
-        <v>95.055289735168813</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9206,16 +9206,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99590738174919524</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB21">
-        <v>75.031334598088264</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9242,16 +9242,16 @@
         <v>463</v>
       </c>
       <c r="AM21" t="s">
+        <v>545</v>
+      </c>
+      <c r="AN21" t="s">
         <v>546</v>
       </c>
-      <c r="AN21" t="s">
-        <v>547</v>
-      </c>
       <c r="AO21">
-        <v>0.99394383035998857</v>
+        <v>0.99333075340694588</v>
       </c>
       <c r="AP21">
-        <v>111.02977673354209</v>
+        <v>122.26952087265865</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,16 +9278,16 @@
         <v>629</v>
       </c>
       <c r="BA21" t="s">
+        <v>665</v>
+      </c>
+      <c r="BB21" t="s">
         <v>666</v>
       </c>
-      <c r="BB21" t="s">
-        <v>430</v>
-      </c>
       <c r="BC21">
-        <v>0.99010219056094972</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD21">
-        <v>181.45983971592244</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9352,16 +9352,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>271</v>
+        <v>303</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99299045119957896</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB22">
-        <v>128.50839467438524</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9388,16 +9388,16 @@
         <v>465</v>
       </c>
       <c r="AM22" t="s">
+        <v>547</v>
+      </c>
+      <c r="AN22" t="s">
         <v>548</v>
       </c>
-      <c r="AN22" t="s">
-        <v>549</v>
-      </c>
       <c r="AO22">
-        <v>0.99514523900053742</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP22">
-        <v>89.003951656813172</v>
+        <v>146.36407875211563</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9430,10 +9430,10 @@
         <v>668</v>
       </c>
       <c r="BC22">
-        <v>0.99672758029478525</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD22">
-        <v>59.994361262269514</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9498,16 +9498,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>265</v>
+        <v>297</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99021255380204343</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB23">
-        <v>179.43651362920434</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9534,16 +9534,16 @@
         <v>467</v>
       </c>
       <c r="AM23" t="s">
+        <v>549</v>
+      </c>
+      <c r="AN23" t="s">
         <v>550</v>
       </c>
-      <c r="AN23" t="s">
-        <v>551</v>
-      </c>
       <c r="AO23">
-        <v>0.99178008656222316</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP23">
-        <v>150.6984130259078</v>
+        <v>88.431180058290352</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9576,10 +9576,10 @@
         <v>670</v>
       </c>
       <c r="BC23">
-        <v>0.99231435496704667</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD23">
-        <v>140.90349227081035</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9644,16 +9644,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99766238113026029</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB24">
-        <v>42.856345945228725</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9680,16 +9680,16 @@
         <v>469</v>
       </c>
       <c r="AM24" t="s">
+        <v>551</v>
+      </c>
+      <c r="AN24" t="s">
         <v>552</v>
       </c>
-      <c r="AN24" t="s">
-        <v>553</v>
-      </c>
       <c r="AO24">
-        <v>0.99572114955867075</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP24">
-        <v>78.445591424369994</v>
+        <v>137.94907153005732</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9722,10 +9722,10 @@
         <v>672</v>
       </c>
       <c r="BC24">
-        <v>0.99229811324031303</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD24">
-        <v>141.20125726092687</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9790,16 +9790,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99588759895151135</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB25">
-        <v>75.394019222291774</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9826,16 +9826,16 @@
         <v>471</v>
       </c>
       <c r="AM25" t="s">
+        <v>553</v>
+      </c>
+      <c r="AN25" t="s">
         <v>554</v>
       </c>
-      <c r="AN25" t="s">
-        <v>555</v>
-      </c>
       <c r="AO25">
-        <v>0.99604689649306255</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP25">
-        <v>72.473564293852363</v>
+        <v>77.236409972479407</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9868,10 +9868,10 @@
         <v>674</v>
       </c>
       <c r="BC25">
-        <v>0.99582070241731502</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD25">
-        <v>76.620455682557321</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9936,16 +9936,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99545581573707076</v>
+        <v>0.99331672850632224</v>
       </c>
       <c r="AB26">
-        <v>83.310044820369185</v>
+        <v>122.52664405075954</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9972,16 +9972,16 @@
         <v>473</v>
       </c>
       <c r="AM26" t="s">
+        <v>555</v>
+      </c>
+      <c r="AN26" t="s">
         <v>556</v>
       </c>
-      <c r="AN26" t="s">
-        <v>557</v>
-      </c>
       <c r="AO26">
-        <v>0.99164055829901554</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP26">
-        <v>153.25643118471478</v>
+        <v>72.473564293852363</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10011,13 +10011,13 @@
         <v>675</v>
       </c>
       <c r="BB26" t="s">
-        <v>676</v>
+        <v>560</v>
       </c>
       <c r="BC26">
-        <v>0.99279657608325511</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD26">
-        <v>132.06277180699064</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10082,16 +10082,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>269</v>
+        <v>304</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99491802052597356</v>
+        <v>0.99698458324869177</v>
       </c>
       <c r="AB27">
-        <v>93.169623690484769</v>
+        <v>55.282640440651299</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10118,16 +10118,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
+        <v>557</v>
+      </c>
+      <c r="AN27" t="s">
         <v>558</v>
       </c>
-      <c r="AN27" t="s">
-        <v>559</v>
-      </c>
       <c r="AO27">
-        <v>0.99587491663731742</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP27">
-        <v>75.626528315847352</v>
+        <v>153.25643118471478</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10154,16 +10154,16 @@
         <v>641</v>
       </c>
       <c r="BA27" t="s">
+        <v>676</v>
+      </c>
+      <c r="BB27" t="s">
         <v>677</v>
       </c>
-      <c r="BB27" t="s">
-        <v>678</v>
-      </c>
       <c r="BC27">
-        <v>0.98843991010136767</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD27">
-        <v>211.93498147492642</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10228,16 +10228,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.9967349730525964</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB28">
-        <v>59.858827369067072</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10264,16 +10264,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
+        <v>559</v>
+      </c>
+      <c r="AN28" t="s">
         <v>560</v>
       </c>
-      <c r="AN28" t="s">
-        <v>561</v>
-      </c>
       <c r="AO28">
-        <v>0.99572967547870339</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP28">
-        <v>78.289282890438841</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10300,16 +10300,16 @@
         <v>643</v>
       </c>
       <c r="BA28" t="s">
+        <v>678</v>
+      </c>
+      <c r="BB28" t="s">
         <v>679</v>
       </c>
-      <c r="BB28" t="s">
-        <v>410</v>
-      </c>
       <c r="BC28">
-        <v>0.98830355217046739</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD28">
-        <v>214.43487687476414</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10374,16 +10374,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99648891019904884</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB29">
-        <v>64.369979684103896</v>
+        <v>73.421601000514329</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10410,16 +10410,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
+        <v>561</v>
+      </c>
+      <c r="AN29" t="s">
         <v>562</v>
       </c>
-      <c r="AN29" t="s">
-        <v>563</v>
-      </c>
       <c r="AO29">
-        <v>0.99601677315501558</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP29">
-        <v>73.025825491381909</v>
+        <v>110.17470964763046</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10452,10 +10452,10 @@
         <v>681</v>
       </c>
       <c r="BC29">
-        <v>0.99447517161328947</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD29">
-        <v>101.28852042302684</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10520,16 +10520,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99849249864903489</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB30">
-        <v>27.63752476769432</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10556,16 +10556,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
+        <v>563</v>
+      </c>
+      <c r="AN30" t="s">
         <v>564</v>
       </c>
-      <c r="AN30" t="s">
-        <v>565</v>
-      </c>
       <c r="AO30">
-        <v>0.99620690928326405</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP30">
-        <v>69.53999647349201</v>
+        <v>64.84977570462992</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10598,10 +10598,10 @@
         <v>683</v>
       </c>
       <c r="BC30">
-        <v>0.99545422785121029</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD30">
-        <v>83.33915606114418</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10666,16 +10666,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>295</v>
+        <v>267</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99484635552608569</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB31">
-        <v>94.483482021761333</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10702,16 +10702,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
+        <v>565</v>
+      </c>
+      <c r="AN31" t="s">
         <v>566</v>
       </c>
-      <c r="AN31" t="s">
-        <v>435</v>
-      </c>
       <c r="AO31">
-        <v>0.99495142174876894</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP31">
-        <v>92.557267939235231</v>
+        <v>83.095996952896456</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10776,16 +10776,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99492995157662933</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB32">
-        <v>92.95088776179594</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10818,10 +10818,10 @@
         <v>568</v>
       </c>
       <c r="AO32">
-        <v>0.99517693573038513</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP32">
-        <v>88.42284494294006</v>
+        <v>59.260154763351615</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10886,16 +10886,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99197366299435197</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB33">
-        <v>147.14951177021345</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10928,10 +10928,10 @@
         <v>570</v>
       </c>
       <c r="AO33">
-        <v>0.99838396904917182</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP33">
-        <v>29.627234098515917</v>
+        <v>88.42284494294006</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10996,16 +10996,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99464845307754257</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB34">
-        <v>98.111693578387175</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11038,10 +11038,10 @@
         <v>572</v>
       </c>
       <c r="AO34">
-        <v>0.99546749107529653</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP34">
-        <v>83.095996952896456</v>
+        <v>29.627234098515917</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11106,16 +11106,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99446824002516876</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB35">
-        <v>101.41559953857198</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11148,10 +11148,10 @@
         <v>574</v>
       </c>
       <c r="AO35">
-        <v>0.99676762792199902</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP35">
-        <v>59.260154763351615</v>
+        <v>240.53953099643502</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11216,16 +11216,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99715332943801627</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB36">
-        <v>52.188960303034925</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11258,10 +11258,10 @@
         <v>576</v>
       </c>
       <c r="AO36">
-        <v>0.98860885963065015</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP36">
-        <v>208.83757343808102</v>
+        <v>104.26406003195649</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11326,16 +11326,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99341896335341162</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB37">
-        <v>120.65233852078616</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11368,10 +11368,10 @@
         <v>578</v>
       </c>
       <c r="AO37">
-        <v>0.99333075340694588</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP37">
-        <v>122.26952087265865</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11436,16 +11436,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99601318900739955</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB38">
-        <v>73.091534864341</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11478,10 +11478,10 @@
         <v>580</v>
       </c>
       <c r="AO38">
-        <v>0.99201650479533909</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP38">
-        <v>146.36407875211563</v>
+        <v>31.154905747485419</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11546,16 +11546,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99695083910621241</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB39">
-        <v>55.901283052772143</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11588,10 +11588,10 @@
         <v>582</v>
       </c>
       <c r="AO39">
-        <v>0.9951764810877296</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP39">
-        <v>88.431180058290352</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11656,16 +11656,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99758018972146978</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB40">
-        <v>44.363188439721</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11698,10 +11698,10 @@
         <v>584</v>
       </c>
       <c r="AO40">
-        <v>0.99247550518926964</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP40">
-        <v>137.94907153005732</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11766,16 +11766,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99398571695284077</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB41">
-        <v>110.2618558645854</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11808,10 +11808,10 @@
         <v>586</v>
       </c>
       <c r="AO41">
-        <v>0.99393947890433676</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP41">
-        <v>111.10955342049355</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11876,16 +11876,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99726845868655478</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB42">
-        <v>50.078257413162468</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11918,10 +11918,10 @@
         <v>588</v>
       </c>
       <c r="AO42">
-        <v>0.99576662598769528</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP42">
-        <v>77.611856892252987</v>
+        <v>72.069660828511601</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11986,16 +11986,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99519943077301054</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB43">
-        <v>88.010435828140345</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12028,10 +12028,10 @@
         <v>590</v>
       </c>
       <c r="AO43">
-        <v>0.99796084623978776</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP43">
-        <v>37.384485603890518</v>
+        <v>89.511926450871471</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12096,16 +12096,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.98298990306503153</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB44">
-        <v>311.85177714108931</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12138,10 +12138,10 @@
         <v>592</v>
       </c>
       <c r="AO44">
-        <v>0.99505112170813059</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP44">
-        <v>90.729435350939028</v>
+        <v>100.63855719912947</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12206,16 +12206,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99495781957805363</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB45">
-        <v>92.439974402351027</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12248,10 +12248,10 @@
         <v>594</v>
       </c>
       <c r="AO45">
-        <v>0.99504825389388352</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP45">
-        <v>90.782011945468795</v>
+        <v>154.37346914756148</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12316,16 +12316,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99564550658027606</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB46">
-        <v>79.832379361605149</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12358,10 +12358,10 @@
         <v>596</v>
       </c>
       <c r="AO46">
-        <v>0.98687966194564902</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP46">
-        <v>240.53953099643502</v>
+        <v>111.02977673354209</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12426,16 +12426,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99567500995545699</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB47">
-        <v>79.29148414995565</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12468,10 +12468,10 @@
         <v>598</v>
       </c>
       <c r="AO47">
-        <v>0.99431286945280239</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP47">
-        <v>104.26406003195649</v>
+        <v>111.10955342049355</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12536,16 +12536,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99635918407512603</v>
+        <v>0.99446824002516876</v>
       </c>
       <c r="AB48">
-        <v>66.748291956023195</v>
+        <v>101.41559953857198</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12578,10 +12578,10 @@
         <v>600</v>
       </c>
       <c r="AO48">
-        <v>0.99692167417445865</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP48">
-        <v>56.43597346825765</v>
+        <v>77.611856892252987</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12646,16 +12646,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99305283137490208</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB49">
-        <v>127.36475812679497</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12688,10 +12688,10 @@
         <v>602</v>
       </c>
       <c r="AO49">
-        <v>0.99830064150468256</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP49">
-        <v>31.154905747485419</v>
+        <v>37.384485603890518</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12756,16 +12756,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99331672850632224</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB50">
-        <v>122.52664405075954</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12798,10 +12798,10 @@
         <v>604</v>
       </c>
       <c r="AO50">
-        <v>0.99788320682147802</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP50">
-        <v>38.807874939569167</v>
+        <v>75.626528315847352</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12866,16 +12866,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99698458324869177</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB51">
-        <v>55.282640440651299</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12908,10 +12908,10 @@
         <v>606</v>
       </c>
       <c r="AO51">
-        <v>0.99677069953771458</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP51">
-        <v>59.203841808565592</v>
+        <v>78.289282890438841</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12976,16 +12976,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99615584710269711</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB52">
-        <v>70.476136450553028</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13018,10 +13018,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99824683646529189</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP52">
-        <v>32.141331469648897</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13086,16 +13086,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99599518539997189</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB53">
-        <v>73.421601000514329</v>
+        <v>147.14951177021345</v>
       </c>
     </row>
   </sheetData>
@@ -13104,7 +13104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0A35BE-0E6F-4AF3-B9E5-869202DAEC41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660CE2A7-B8E4-44C2-AE00-78E98CC4E4AB}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13216,7 +13216,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13249,7 +13249,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13284,7 +13284,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>529</v>
+        <v>561</v>
       </c>
       <c r="L12">
         <v>41.38517014727136</v>
@@ -13317,7 +13317,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>651</v>
+        <v>673</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13352,7 +13352,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>548</v>
+        <v>535</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13385,7 +13385,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>682</v>
+        <v>663</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13420,7 +13420,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>558</v>
+        <v>603</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13453,7 +13453,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>679</v>
+        <v>659</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13488,7 +13488,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>546</v>
+        <v>595</v>
       </c>
       <c r="L15">
         <v>13.570215224493221</v>
@@ -13521,7 +13521,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>653</v>
+        <v>675</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13556,7 +13556,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>540</v>
+        <v>589</v>
       </c>
       <c r="L16">
         <v>59.282276232111244</v>
@@ -13589,7 +13589,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13624,7 +13624,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13657,7 +13657,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13692,7 +13692,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13725,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>667</v>
+        <v>657</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13760,7 +13760,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="L19">
         <v>15.766767829784982</v>
@@ -13793,7 +13793,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13828,7 +13828,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13861,7 +13861,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13896,7 +13896,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="L21">
         <v>11.016586435503244</v>
@@ -13929,7 +13929,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>680</v>
+        <v>660</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13964,7 +13964,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>552</v>
+        <v>539</v>
       </c>
       <c r="L22">
         <v>6.1733535033999489</v>
@@ -13997,7 +13997,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>649</v>
+        <v>682</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14032,7 +14032,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="L23">
         <v>4.8541340927283274</v>
@@ -14065,7 +14065,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14100,7 +14100,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>544</v>
+        <v>593</v>
       </c>
       <c r="L24">
         <v>13.114783900591691</v>
@@ -14133,7 +14133,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>656</v>
+        <v>678</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14168,7 +14168,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14201,7 +14201,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14236,7 +14236,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14269,7 +14269,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>654</v>
+        <v>676</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14304,7 +14304,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14337,7 +14337,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14372,7 +14372,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>564</v>
+        <v>529</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14405,7 +14405,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14440,7 +14440,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14473,7 +14473,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14508,7 +14508,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>566</v>
+        <v>531</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14541,7 +14541,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14576,7 +14576,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>583</v>
+        <v>551</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14611,7 +14611,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14646,7 +14646,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>591</v>
+        <v>541</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14681,7 +14681,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14716,7 +14716,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14751,7 +14751,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14786,7 +14786,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14821,7 +14821,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>531</v>
+        <v>563</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14856,7 +14856,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>577</v>
+        <v>545</v>
       </c>
       <c r="L39">
         <v>26.291803917155487</v>
@@ -14891,7 +14891,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>579</v>
+        <v>547</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14926,7 +14926,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>560</v>
+        <v>605</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14961,7 +14961,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>575</v>
+        <v>543</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14996,7 +14996,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>550</v>
+        <v>537</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15031,7 +15031,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>542</v>
+        <v>591</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15066,7 +15066,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>562</v>
+        <v>527</v>
       </c>
       <c r="L45">
         <v>10.919135648131764</v>
@@ -15101,7 +15101,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="L46">
         <v>33.912640160809843</v>
@@ -15136,7 +15136,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15171,7 +15171,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>527</v>
+        <v>559</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15206,7 +15206,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="L49">
         <v>62.791395577971592</v>
@@ -15241,7 +15241,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="L50">
         <v>37.678782480143312</v>
@@ -15276,7 +15276,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>538</v>
+        <v>587</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15311,7 +15311,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15326,7 +15326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E72363F4-7B83-467B-A90E-486DDED2ACAA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{597A53D0-05B5-4D83-92EB-74457EEE808C}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17143,7 +17143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD27DDF0-5A7D-4072-83E4-F503CB98AE83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D64F5-8155-4337-ACA5-F89A63C9B015}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{669ADC9E-6FF1-4BE7-9D8B-2186D9F2373E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{52DBE018-BA45-456A-813D-82F8B29C883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,18 +1060,30 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_017</t>
   </si>
   <si>
@@ -1096,6 +1108,72 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_015</t>
   </si>
   <si>
@@ -1108,6 +1186,60 @@
     <t>connecting solar to buses in cluster 37</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_011</t>
   </si>
   <si>
@@ -1120,40 +1252,46 @@
     <t>connecting solar to buses in cluster 4</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
     <t>distr_solelc_spv_ZAF_020</t>
@@ -1168,114 +1306,6 @@
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_013</t>
   </si>
   <si>
@@ -1294,42 +1324,18 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
   </si>
   <si>
@@ -1345,34 +1351,97 @@
     <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
   </si>
   <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
   </si>
   <si>
     <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
   </si>
   <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
   </si>
   <si>
     <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
   </si>
   <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
     <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
@@ -1381,60 +1450,6 @@
     <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
-    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
     <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
   </si>
   <si>
@@ -1444,19 +1459,196 @@
     <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
   </si>
   <si>
-    <t>e_ZA25-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+    <t>distr_wonelc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_035</t>
@@ -1477,132 +1669,6 @@
     <t>connecting wind onshore to buses in cluster 20</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ZAF_042</t>
   </si>
   <si>
@@ -1645,70 +1711,193 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_035</t>
@@ -1726,129 +1915,6 @@
     <t>elc_won_ZAF_020</t>
   </si>
   <si>
-    <t>elc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_won_ZAF_042</t>
   </si>
   <si>
@@ -1891,70 +1957,40 @@
     <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
+    <t>distr_wofelc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_006</t>
@@ -1981,16 +2017,28 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_ZAF_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
+    <t>distr_wofelc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_004</t>
@@ -2005,42 +2053,6 @@
     <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ZAF_002</t>
   </si>
   <si>
@@ -2065,16 +2077,37 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
+    <t>elc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_006</t>
@@ -2095,16 +2128,28 @@
     <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
   </si>
   <si>
+    <t>elc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_wof_ZAF_001</t>
   </si>
   <si>
     <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF</t>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_004</t>
@@ -2116,39 +2161,6 @@
     <t>e_w131625968-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_wof_ZAF_002</t>
   </si>
   <si>
@@ -2168,18 +2180,6 @@
   </si>
   <si>
     <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
   </si>
   <si>
     <t>e_won_ZAF_001</t>
@@ -7508,7 +7508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{826B3F18-CA90-45FF-A352-E256C39428C1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC09FD0D-C778-40D2-BE76-21E6D23980CB}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7746,16 +7746,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>274</v>
+        <v>299</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99715332943801627</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB11">
-        <v>52.188960303034925</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7788,10 +7788,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99601677315501558</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP11">
-        <v>73.025825491381909</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7821,13 +7821,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>560</v>
+        <v>418</v>
       </c>
       <c r="BC11">
-        <v>0.99223220184557481</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD11">
-        <v>142.40963283112865</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7892,16 +7892,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99341896335341162</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB12">
-        <v>120.65233852078616</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7934,10 +7934,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99620690928326405</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP12">
-        <v>69.53999647349201</v>
+        <v>150.6984130259078</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7970,10 +7970,10 @@
         <v>651</v>
       </c>
       <c r="BC12">
-        <v>0.99462081464868646</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD12">
-        <v>98.618398107414592</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8038,16 +8038,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99601318900739955</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB13">
-        <v>73.091534864341</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8077,13 +8077,13 @@
         <v>531</v>
       </c>
       <c r="AN13" t="s">
-        <v>440</v>
+        <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99495142174876894</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP13">
-        <v>92.557267939235231</v>
+        <v>78.445591424369994</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8113,13 +8113,13 @@
         <v>652</v>
       </c>
       <c r="BB13" t="s">
-        <v>578</v>
+        <v>653</v>
       </c>
       <c r="BC13">
-        <v>0.99507162964364948</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD13">
-        <v>90.353456533092867</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8184,16 +8184,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99695083910621241</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB14">
-        <v>55.901283052772143</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8220,16 +8220,16 @@
         <v>449</v>
       </c>
       <c r="AM14" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AN14" t="s">
-        <v>441</v>
+        <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.99599400380931946</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP14">
-        <v>73.443263495810669</v>
+        <v>90.782011945468795</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8256,16 +8256,16 @@
         <v>615</v>
       </c>
       <c r="BA14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BB14" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="BC14">
-        <v>0.98805842341846151</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD14">
-        <v>218.92890399487229</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8330,16 +8330,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99758018972146978</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB15">
-        <v>44.363188439721</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8366,16 +8366,16 @@
         <v>451</v>
       </c>
       <c r="AM15" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AN15" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.99791355837194406</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP15">
-        <v>38.251429847691753</v>
+        <v>83.095996952896456</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8402,16 +8402,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB15" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="BC15">
-        <v>0.99481516601444531</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD15">
-        <v>95.055289735168813</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8476,16 +8476,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99398571695284077</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB16">
-        <v>110.2618558645854</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8512,16 +8512,16 @@
         <v>453</v>
       </c>
       <c r="AM16" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AN16" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AO16">
-        <v>0.99514523900053742</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP16">
-        <v>89.003951656813172</v>
+        <v>59.260154763351615</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8548,16 +8548,16 @@
         <v>619</v>
       </c>
       <c r="BA16" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="BB16" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="BC16">
-        <v>0.99672758029478525</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD16">
-        <v>59.994361262269514</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8622,16 +8622,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99726845868655478</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB17">
-        <v>50.078257413162468</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8658,16 +8658,16 @@
         <v>455</v>
       </c>
       <c r="AM17" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AN17" t="s">
-        <v>538</v>
+        <v>400</v>
       </c>
       <c r="AO17">
-        <v>0.99178008656222316</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP17">
-        <v>150.6984130259078</v>
+        <v>73.443263495810669</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8694,16 +8694,16 @@
         <v>621</v>
       </c>
       <c r="BA17" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="BB17" t="s">
-        <v>432</v>
+        <v>547</v>
       </c>
       <c r="BC17">
-        <v>0.98830355217046739</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD17">
-        <v>214.43487687476414</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8768,16 +8768,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99635918407512603</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB18">
-        <v>66.748291956023195</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8804,16 +8804,16 @@
         <v>457</v>
       </c>
       <c r="AM18" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AN18" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AO18">
-        <v>0.99572114955867075</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP18">
-        <v>78.445591424369994</v>
+        <v>38.251429847691753</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,16 +8840,16 @@
         <v>623</v>
       </c>
       <c r="BA18" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="BB18" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="BC18">
-        <v>0.99447517161328947</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD18">
-        <v>101.28852042302684</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8914,16 +8914,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99305283137490208</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB19">
-        <v>127.36475812679497</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8950,16 +8950,16 @@
         <v>459</v>
       </c>
       <c r="AM19" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AO19">
-        <v>0.99505112170813059</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP19">
-        <v>90.729435350939028</v>
+        <v>75.626528315847352</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8986,16 +8986,16 @@
         <v>625</v>
       </c>
       <c r="BA19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="BB19" t="s">
-        <v>405</v>
+        <v>600</v>
       </c>
       <c r="BC19">
-        <v>0.99010219056094972</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD19">
-        <v>181.45983971592244</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9060,16 +9060,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>282</v>
+        <v>266</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99456731509164431</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB20">
-        <v>99.599223319854588</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9096,16 +9096,16 @@
         <v>461</v>
       </c>
       <c r="AM20" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AN20" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AO20">
-        <v>0.98860885963065015</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP20">
-        <v>208.83757343808102</v>
+        <v>78.289282890438841</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9132,16 +9132,16 @@
         <v>627</v>
       </c>
       <c r="BA20" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="BB20" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="BC20">
-        <v>0.99545422785121029</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD20">
-        <v>83.33915606114418</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9206,16 +9206,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99466941924265306</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB21">
-        <v>97.727313884694652</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9242,16 +9242,16 @@
         <v>463</v>
       </c>
       <c r="AM21" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AN21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AO21">
-        <v>0.99333075340694588</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP21">
-        <v>122.26952087265865</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,16 +9278,16 @@
         <v>629</v>
       </c>
       <c r="BA21" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="BB21" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="BC21">
-        <v>0.99279657608325511</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD21">
-        <v>132.06277180699064</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9352,16 +9352,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99527761530085967</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB22">
-        <v>86.577052817573119</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9388,16 +9388,16 @@
         <v>465</v>
       </c>
       <c r="AM22" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN22" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO22">
-        <v>0.99201650479533909</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP22">
-        <v>146.36407875211563</v>
+        <v>110.17470964763046</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9424,16 +9424,16 @@
         <v>631</v>
       </c>
       <c r="BA22" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="BB22" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="BC22">
-        <v>0.99231435496704667</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD22">
-        <v>140.90349227081035</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9498,16 +9498,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.9951066982538278</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB23">
-        <v>89.710532013157362</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9534,16 +9534,16 @@
         <v>467</v>
       </c>
       <c r="AM23" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN23" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AO23">
-        <v>0.9951764810877296</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP23">
-        <v>88.431180058290352</v>
+        <v>64.84977570462992</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9570,16 +9570,16 @@
         <v>633</v>
       </c>
       <c r="BA23" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="BB23" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="BC23">
-        <v>0.99229811324031303</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD23">
-        <v>141.20125726092687</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9644,16 +9644,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99681791473814529</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB24">
-        <v>58.33822980066963</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9680,16 +9680,16 @@
         <v>469</v>
       </c>
       <c r="AM24" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AN24" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AO24">
-        <v>0.99247550518926964</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP24">
-        <v>137.94907153005732</v>
+        <v>90.729435350939028</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9716,16 +9716,16 @@
         <v>635</v>
       </c>
       <c r="BA24" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="BB24" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="BC24">
-        <v>0.99582070241731502</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD24">
-        <v>76.620455682557321</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9790,16 +9790,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.98958063849079669</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB25">
-        <v>191.02162766872783</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9826,10 +9826,10 @@
         <v>471</v>
       </c>
       <c r="AM25" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN25" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO25">
         <v>0.99578710491059208</v>
@@ -9862,16 +9862,16 @@
         <v>637</v>
       </c>
       <c r="BA25" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="BB25" t="s">
-        <v>674</v>
+        <v>414</v>
       </c>
       <c r="BC25">
-        <v>0.991900752046595</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD25">
-        <v>148.48621247909063</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9936,16 +9936,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99331672850632224</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB26">
-        <v>122.52664405075954</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9972,16 +9972,16 @@
         <v>473</v>
       </c>
       <c r="AM26" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN26" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO26">
-        <v>0.99604689649306255</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP26">
-        <v>72.473564293852363</v>
+        <v>111.10955342049355</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10011,13 +10011,13 @@
         <v>675</v>
       </c>
       <c r="BB26" t="s">
-        <v>560</v>
+        <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.99581145929743231</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD26">
-        <v>76.789912880408167</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10082,16 +10082,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99698458324869177</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB27">
-        <v>55.282640440651299</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10118,16 +10118,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN27" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO27">
-        <v>0.99164055829901554</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP27">
-        <v>153.25643118471478</v>
+        <v>77.611856892252987</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10154,16 +10154,16 @@
         <v>641</v>
       </c>
       <c r="BA27" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="BC27">
-        <v>0.99429876975975018</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD27">
-        <v>104.52255440457925</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10228,16 +10228,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99615584710269711</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB28">
-        <v>70.476136450553028</v>
+        <v>73.421601000514329</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10264,16 +10264,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN28" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO28">
-        <v>0.99468222901836267</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP28">
-        <v>97.492467996683757</v>
+        <v>37.384485603890518</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10300,16 +10300,16 @@
         <v>643</v>
       </c>
       <c r="BA28" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="BB28" t="s">
-        <v>679</v>
+        <v>547</v>
       </c>
       <c r="BC28">
-        <v>0.98743040674179927</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD28">
-        <v>230.44254306701379</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10374,16 +10374,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>307</v>
+        <v>279</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99599518539997189</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB29">
-        <v>73.421601000514329</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10410,16 +10410,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN29" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO29">
-        <v>0.99399047038285648</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP29">
-        <v>110.17470964763046</v>
+        <v>208.83757343808102</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10452,10 +10452,10 @@
         <v>681</v>
       </c>
       <c r="BC29">
-        <v>0.98843991010136767</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD29">
-        <v>211.93498147492642</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10520,16 +10520,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99294071263677341</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB30">
-        <v>129.42026832582172</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10556,16 +10556,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN30" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO30">
-        <v>0.99646273950702013</v>
+        <v>0.99333075340694588</v>
       </c>
       <c r="AP30">
-        <v>64.84977570462992</v>
+        <v>122.26952087265865</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10598,10 +10598,10 @@
         <v>683</v>
       </c>
       <c r="BC30">
-        <v>0.99501631001524238</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD30">
-        <v>91.367649720556983</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10666,16 +10666,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99535442409010222</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB31">
-        <v>85.168891681458845</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10702,16 +10702,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AN31" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO31">
-        <v>0.99546749107529653</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP31">
-        <v>83.095996952896456</v>
+        <v>146.36407875211563</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10776,16 +10776,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>305</v>
+        <v>280</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99309463181702251</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB32">
-        <v>126.5984166879211</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10812,16 +10812,16 @@
         <v>485</v>
       </c>
       <c r="AM32" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN32" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO32">
-        <v>0.99676762792199902</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP32">
-        <v>59.260154763351615</v>
+        <v>88.431180058290352</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10886,16 +10886,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99827081845920873</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB33">
-        <v>31.701661581174136</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10922,16 +10922,16 @@
         <v>487</v>
       </c>
       <c r="AM33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO33">
-        <v>0.99517693573038513</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP33">
-        <v>88.42284494294006</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10996,16 +10996,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99588759895151135</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB34">
-        <v>75.394019222291774</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11032,16 +11032,16 @@
         <v>489</v>
       </c>
       <c r="AM34" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN34" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO34">
-        <v>0.99838396904917182</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP34">
-        <v>29.627234098515917</v>
+        <v>88.42284494294006</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11106,16 +11106,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99545581573707076</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB35">
-        <v>83.310044820369185</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11142,16 +11142,16 @@
         <v>491</v>
       </c>
       <c r="AM35" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN35" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO35">
-        <v>0.98687966194564902</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP35">
-        <v>240.53953099643502</v>
+        <v>29.627234098515917</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11216,16 +11216,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99491802052597356</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB36">
-        <v>93.169623690484769</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11252,16 +11252,16 @@
         <v>493</v>
       </c>
       <c r="AM36" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN36" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO36">
-        <v>0.99431286945280239</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP36">
-        <v>104.26406003195649</v>
+        <v>72.473564293852363</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11326,16 +11326,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>306</v>
+        <v>272</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.9967349730525964</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB37">
-        <v>59.858827369067072</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11362,16 +11362,16 @@
         <v>495</v>
       </c>
       <c r="AM37" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN37" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO37">
-        <v>0.99692167417445865</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP37">
-        <v>56.43597346825765</v>
+        <v>153.25643118471478</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11436,16 +11436,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99648891019904884</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB38">
-        <v>64.369979684103896</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11472,16 +11472,16 @@
         <v>497</v>
       </c>
       <c r="AM38" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN38" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO38">
-        <v>0.99830064150468256</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP38">
-        <v>31.154905747485419</v>
+        <v>72.069660828511601</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11546,16 +11546,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99849249864903489</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB39">
-        <v>27.63752476769432</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11582,16 +11582,16 @@
         <v>499</v>
       </c>
       <c r="AM39" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN39" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO39">
-        <v>0.99788320682147802</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP39">
-        <v>38.807874939569167</v>
+        <v>89.511926450871471</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11656,16 +11656,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99484635552608569</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB40">
-        <v>94.483482021761333</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11692,16 +11692,16 @@
         <v>501</v>
       </c>
       <c r="AM40" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN40" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO40">
-        <v>0.99677069953771458</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP40">
-        <v>59.203841808565592</v>
+        <v>100.63855719912947</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11766,16 +11766,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99021255380204343</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB41">
-        <v>179.43651362920434</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11802,16 +11802,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN41" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO41">
-        <v>0.99824683646529189</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP41">
-        <v>32.141331469648897</v>
+        <v>154.37346914756148</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11876,16 +11876,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>293</v>
+        <v>270</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99766238113026029</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB42">
-        <v>42.856345945228725</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11912,16 +11912,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN42" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO42">
-        <v>0.99606892759117205</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP42">
-        <v>72.069660828511601</v>
+        <v>111.02977673354209</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11986,16 +11986,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99590738174919524</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB43">
-        <v>75.031334598088264</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12022,16 +12022,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AN43" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO43">
-        <v>0.99511753128449787</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP43">
-        <v>89.511926450871471</v>
+        <v>73.025825491381909</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12096,16 +12096,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99299045119957896</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB44">
-        <v>128.50839467438524</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12132,16 +12132,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN44" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO44">
-        <v>0.9945106241527748</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP44">
-        <v>100.63855719912947</v>
+        <v>69.53999647349201</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12206,16 +12206,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99567500995545699</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB45">
-        <v>79.29148414995565</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12242,16 +12242,16 @@
         <v>511</v>
       </c>
       <c r="AM45" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN45" t="s">
-        <v>594</v>
+        <v>428</v>
       </c>
       <c r="AO45">
-        <v>0.9915796289555876</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP45">
-        <v>154.37346914756148</v>
+        <v>92.557267939235231</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12316,16 +12316,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99519943077301054</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB46">
-        <v>88.010435828140345</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12358,10 +12358,10 @@
         <v>596</v>
       </c>
       <c r="AO46">
-        <v>0.99394383035998857</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP46">
-        <v>111.02977673354209</v>
+        <v>240.53953099643502</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12426,16 +12426,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99464845307754257</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB47">
-        <v>98.111693578387175</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12468,10 +12468,10 @@
         <v>598</v>
       </c>
       <c r="AO47">
-        <v>0.99393947890433676</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP47">
-        <v>111.10955342049355</v>
+        <v>104.26406003195649</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12536,16 +12536,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99446824002516876</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB48">
-        <v>101.41559953857198</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12578,10 +12578,10 @@
         <v>600</v>
       </c>
       <c r="AO48">
-        <v>0.99576662598769528</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP48">
-        <v>77.611856892252987</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12646,16 +12646,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.98298990306503153</v>
+        <v>0.99331672850632224</v>
       </c>
       <c r="AB49">
-        <v>311.85177714108931</v>
+        <v>122.52664405075954</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12688,10 +12688,10 @@
         <v>602</v>
       </c>
       <c r="AO49">
-        <v>0.99796084623978776</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP49">
-        <v>37.384485603890518</v>
+        <v>31.154905747485419</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12756,16 +12756,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99495781957805363</v>
+        <v>0.99698458324869177</v>
       </c>
       <c r="AB50">
-        <v>92.439974402351027</v>
+        <v>55.282640440651299</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12798,10 +12798,10 @@
         <v>604</v>
       </c>
       <c r="AO50">
-        <v>0.99587491663731742</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP50">
-        <v>75.626528315847352</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12866,16 +12866,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99564550658027606</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB51">
-        <v>79.832379361605149</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12908,10 +12908,10 @@
         <v>606</v>
       </c>
       <c r="AO51">
-        <v>0.99572967547870339</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP51">
-        <v>78.289282890438841</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12976,16 +12976,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99492995157662933</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB52">
-        <v>92.95088776179594</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13018,10 +13018,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99504825389388352</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP52">
-        <v>90.782011945468795</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13086,16 +13086,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99197366299435197</v>
+        <v>0.99446824002516876</v>
       </c>
       <c r="AB53">
-        <v>147.14951177021345</v>
+        <v>101.41559953857198</v>
       </c>
     </row>
   </sheetData>
@@ -13104,7 +13104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{660CE2A7-B8E4-44C2-AE00-78E98CC4E4AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8901FD1-355D-45B3-9BD2-ACC269CAEA3D}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13216,7 +13216,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13249,7 +13249,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>655</v>
+        <v>670</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13284,7 +13284,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="L12">
         <v>41.38517014727136</v>
@@ -13317,7 +13317,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13352,7 +13352,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13385,7 +13385,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13420,7 +13420,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>603</v>
+        <v>542</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13453,7 +13453,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>659</v>
+        <v>674</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13488,7 +13488,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="L15">
         <v>13.570215224493221</v>
@@ -13521,7 +13521,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13556,7 +13556,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="L16">
         <v>59.282276232111244</v>
@@ -13589,7 +13589,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13624,7 +13624,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13657,7 +13657,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>671</v>
+        <v>656</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13692,7 +13692,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>567</v>
+        <v>537</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13725,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13760,7 +13760,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>579</v>
+        <v>601</v>
       </c>
       <c r="L19">
         <v>15.766767829784982</v>
@@ -13793,7 +13793,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13828,7 +13828,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13861,7 +13861,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13896,7 +13896,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="L21">
         <v>11.016586435503244</v>
@@ -13929,7 +13929,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>660</v>
+        <v>675</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13964,7 +13964,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L22">
         <v>6.1733535033999489</v>
@@ -13997,7 +13997,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>682</v>
+        <v>668</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14032,7 +14032,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="L23">
         <v>4.8541340927283274</v>
@@ -14065,7 +14065,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>680</v>
+        <v>658</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14100,7 +14100,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="L24">
         <v>13.114783900591691</v>
@@ -14133,7 +14133,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14168,7 +14168,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14201,7 +14201,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>667</v>
+        <v>652</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14236,7 +14236,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>549</v>
+        <v>568</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14269,7 +14269,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14304,7 +14304,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>577</v>
+        <v>599</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14337,7 +14337,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>662</v>
+        <v>649</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14372,7 +14372,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>529</v>
+        <v>592</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14405,7 +14405,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14440,7 +14440,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>581</v>
+        <v>603</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14473,7 +14473,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14508,7 +14508,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>531</v>
+        <v>594</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14541,7 +14541,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14576,7 +14576,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>551</v>
+        <v>570</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14611,7 +14611,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>601</v>
+        <v>560</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14646,7 +14646,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14681,7 +14681,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>599</v>
+        <v>558</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14716,7 +14716,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14751,7 +14751,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>565</v>
+        <v>535</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14786,7 +14786,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14821,7 +14821,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>563</v>
+        <v>550</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14856,7 +14856,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c r="L39">
         <v>26.291803917155487</v>
@@ -14891,7 +14891,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14926,7 +14926,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>605</v>
+        <v>544</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14961,7 +14961,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14996,7 +14996,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15031,7 +15031,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15066,7 +15066,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>527</v>
+        <v>590</v>
       </c>
       <c r="L45">
         <v>10.919135648131764</v>
@@ -15101,7 +15101,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="L46">
         <v>33.912640160809843</v>
@@ -15136,7 +15136,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>607</v>
+        <v>533</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15171,7 +15171,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>559</v>
+        <v>546</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15206,7 +15206,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>575</v>
+        <v>597</v>
       </c>
       <c r="L49">
         <v>62.791395577971592</v>
@@ -15241,7 +15241,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>597</v>
+        <v>556</v>
       </c>
       <c r="L50">
         <v>37.678782480143312</v>
@@ -15276,7 +15276,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15311,7 +15311,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>573</v>
+        <v>595</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15326,7 +15326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{597A53D0-05B5-4D83-92EB-74457EEE808C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15104F78-0452-444E-9766-4B46327404BD}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17143,7 +17143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949D64F5-8155-4337-ACA5-F89A63C9B015}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E767D8-42FC-4D46-8CCB-A7B7A63E3A7D}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52DBE018-BA45-456A-813D-82F8B29C883E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{964117AE-6809-498B-A7F9-B2CBC532E18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,52 +1060,214 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_035</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 35</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_022</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
+    <t>distr_solelc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
     <t>distr_solelc_spv_ZAF_001</t>
@@ -1120,106 +1282,16 @@
     <t>connecting solar to buses in cluster 29</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
+    <t>distr_solelc_spv_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
     <t>distr_solelc_spv_ZAF_008</t>
@@ -1240,78 +1312,6 @@
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_014</t>
   </si>
   <si>
@@ -1330,25 +1330,106 @@
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
   </si>
   <si>
     <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
   </si>
   <si>
-    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
   </si>
   <si>
     <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
@@ -1357,55 +1438,10 @@
     <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
   </si>
   <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
     <t>e_ZA25-400_ZAF</t>
@@ -1417,48 +1453,84 @@
     <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
-  </si>
-  <si>
     <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
   </si>
   <si>
     <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ZAF_003</t>
   </si>
   <si>
@@ -1477,22 +1549,154 @@
     <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>distr_wonelc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_001</t>
@@ -1507,208 +1711,73 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
+    <t>elc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_003</t>
@@ -1729,22 +1798,154 @@
     <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+    <t>elc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_001</t>
@@ -1756,205 +1957,16 @@
     <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+    <t>distr_wofelc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_017</t>
@@ -1963,6 +1975,48 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_ZAF_008</t>
   </si>
   <si>
@@ -1993,66 +2047,12 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ZAF_003</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ZAF_002</t>
   </si>
   <si>
@@ -2077,9 +2077,54 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
+    <t>elc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_wof_ZAF_017</t>
   </si>
   <si>
+    <t>elc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_wof_ZAF_008</t>
   </si>
   <si>
@@ -2110,55 +2155,10 @@
     <t>e_w169789536-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_wof_ZAF_003</t>
   </si>
   <si>
     <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_002</t>
@@ -7508,7 +7508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC09FD0D-C778-40D2-BE76-21E6D23980CB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6349821-E822-47D3-B720-A5ADB53547C8}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7746,16 +7746,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99492995157662933</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB11">
-        <v>92.95088776179594</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7788,10 +7788,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99514523900053742</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP11">
-        <v>89.003951656813172</v>
+        <v>90.782011945468795</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7821,13 +7821,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>418</v>
+        <v>650</v>
       </c>
       <c r="BC11">
-        <v>0.99010219056094972</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD11">
-        <v>181.45983971592244</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7892,16 +7892,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99197366299435197</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB12">
-        <v>147.14951177021345</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7934,10 +7934,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99178008656222316</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP12">
-        <v>150.6984130259078</v>
+        <v>83.095996952896456</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7964,16 +7964,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BB12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="BC12">
-        <v>0.99672758029478525</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD12">
-        <v>59.994361262269514</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8038,16 +8038,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>274</v>
+        <v>303</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99715332943801627</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB13">
-        <v>52.188960303034925</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8080,10 +8080,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99572114955867075</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP13">
-        <v>78.445591424369994</v>
+        <v>59.260154763351615</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8110,16 +8110,16 @@
         <v>613</v>
       </c>
       <c r="BA13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BB13" t="s">
-        <v>653</v>
+        <v>426</v>
       </c>
       <c r="BC13">
-        <v>0.99231435496704667</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD13">
-        <v>140.90349227081035</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8184,16 +8184,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99341896335341162</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB14">
-        <v>120.65233852078616</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8226,10 +8226,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.99504825389388352</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP14">
-        <v>90.782011945468795</v>
+        <v>73.025825491381909</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8259,13 +8259,13 @@
         <v>654</v>
       </c>
       <c r="BB14" t="s">
-        <v>655</v>
+        <v>597</v>
       </c>
       <c r="BC14">
-        <v>0.99229811324031303</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD14">
-        <v>141.20125726092687</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8330,16 +8330,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99601318900739955</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB15">
-        <v>73.091534864341</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8372,10 +8372,10 @@
         <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.99546749107529653</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP15">
-        <v>83.095996952896456</v>
+        <v>69.53999647349201</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8402,16 +8402,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
+        <v>655</v>
+      </c>
+      <c r="BB15" t="s">
         <v>656</v>
       </c>
-      <c r="BB15" t="s">
-        <v>657</v>
-      </c>
       <c r="BC15">
-        <v>0.99582070241731502</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD15">
-        <v>76.620455682557321</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8476,16 +8476,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99695083910621241</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB16">
-        <v>55.901283052772143</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8515,13 +8515,13 @@
         <v>537</v>
       </c>
       <c r="AN16" t="s">
-        <v>538</v>
+        <v>440</v>
       </c>
       <c r="AO16">
-        <v>0.99676762792199902</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP16">
-        <v>59.260154763351615</v>
+        <v>92.557267939235231</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8548,16 +8548,16 @@
         <v>619</v>
       </c>
       <c r="BA16" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="BB16" t="s">
-        <v>659</v>
+        <v>581</v>
       </c>
       <c r="BC16">
-        <v>0.98843991010136767</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD16">
-        <v>211.93498147492642</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8622,16 +8622,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99758018972146978</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB17">
-        <v>44.363188439721</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8658,16 +8658,16 @@
         <v>455</v>
       </c>
       <c r="AM17" t="s">
+        <v>538</v>
+      </c>
+      <c r="AN17" t="s">
         <v>539</v>
       </c>
-      <c r="AN17" t="s">
-        <v>400</v>
-      </c>
       <c r="AO17">
-        <v>0.99599400380931946</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP17">
-        <v>73.443263495810669</v>
+        <v>111.10955342049355</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8694,16 +8694,16 @@
         <v>621</v>
       </c>
       <c r="BA17" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="BB17" t="s">
-        <v>547</v>
+        <v>659</v>
       </c>
       <c r="BC17">
-        <v>0.99223220184557481</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD17">
-        <v>142.40963283112865</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8768,16 +8768,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99021255380204343</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB18">
-        <v>179.43651362920434</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8810,10 +8810,10 @@
         <v>541</v>
       </c>
       <c r="AO18">
-        <v>0.99791355837194406</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP18">
-        <v>38.251429847691753</v>
+        <v>77.611856892252987</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,16 +8840,16 @@
         <v>623</v>
       </c>
       <c r="BA18" t="s">
+        <v>660</v>
+      </c>
+      <c r="BB18" t="s">
         <v>661</v>
       </c>
-      <c r="BB18" t="s">
-        <v>662</v>
-      </c>
       <c r="BC18">
-        <v>0.99462081464868646</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD18">
-        <v>98.618398107414592</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8914,16 +8914,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99766238113026029</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB19">
-        <v>42.856345945228725</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8956,10 +8956,10 @@
         <v>543</v>
       </c>
       <c r="AO19">
-        <v>0.99587491663731742</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP19">
-        <v>75.626528315847352</v>
+        <v>37.384485603890518</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8986,16 +8986,16 @@
         <v>625</v>
       </c>
       <c r="BA19" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="BB19" t="s">
-        <v>600</v>
+        <v>406</v>
       </c>
       <c r="BC19">
-        <v>0.99507162964364948</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD19">
-        <v>90.353456533092867</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9060,16 +9060,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99294071263677341</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB20">
-        <v>129.42026832582172</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9102,10 +9102,10 @@
         <v>545</v>
       </c>
       <c r="AO20">
-        <v>0.99572967547870339</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP20">
-        <v>78.289282890438841</v>
+        <v>88.42284494294006</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9132,16 +9132,16 @@
         <v>627</v>
       </c>
       <c r="BA20" t="s">
+        <v>663</v>
+      </c>
+      <c r="BB20" t="s">
         <v>664</v>
       </c>
-      <c r="BB20" t="s">
-        <v>665</v>
-      </c>
       <c r="BC20">
-        <v>0.98805842341846151</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD20">
-        <v>218.92890399487229</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9206,16 +9206,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>267</v>
+        <v>300</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99535442409010222</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB21">
-        <v>85.168891681458845</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9248,10 +9248,10 @@
         <v>547</v>
       </c>
       <c r="AO21">
-        <v>0.99468222901836267</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP21">
-        <v>97.492467996683757</v>
+        <v>29.627234098515917</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,16 +9278,16 @@
         <v>629</v>
       </c>
       <c r="BA21" t="s">
+        <v>665</v>
+      </c>
+      <c r="BB21" t="s">
         <v>666</v>
       </c>
-      <c r="BB21" t="s">
-        <v>667</v>
-      </c>
       <c r="BC21">
-        <v>0.99545422785121029</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD21">
-        <v>83.33915606114418</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9352,16 +9352,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99309463181702251</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB22">
-        <v>126.5984166879211</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9394,10 +9394,10 @@
         <v>549</v>
       </c>
       <c r="AO22">
-        <v>0.99399047038285648</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP22">
-        <v>110.17470964763046</v>
+        <v>77.236409972479407</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9424,16 +9424,16 @@
         <v>631</v>
       </c>
       <c r="BA22" t="s">
+        <v>667</v>
+      </c>
+      <c r="BB22" t="s">
         <v>668</v>
       </c>
-      <c r="BB22" t="s">
-        <v>669</v>
-      </c>
       <c r="BC22">
-        <v>0.99501631001524238</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD22">
-        <v>91.367649720556983</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9498,16 +9498,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99827081845920873</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB23">
-        <v>31.701661581174136</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9540,10 +9540,10 @@
         <v>551</v>
       </c>
       <c r="AO23">
-        <v>0.99646273950702013</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP23">
-        <v>64.84977570462992</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9570,16 +9570,16 @@
         <v>633</v>
       </c>
       <c r="BA23" t="s">
+        <v>669</v>
+      </c>
+      <c r="BB23" t="s">
         <v>670</v>
       </c>
-      <c r="BB23" t="s">
-        <v>671</v>
-      </c>
       <c r="BC23">
-        <v>0.99481516601444531</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD23">
-        <v>95.055289735168813</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9644,16 +9644,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99567500995545699</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB24">
-        <v>79.29148414995565</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9686,10 +9686,10 @@
         <v>553</v>
       </c>
       <c r="AO24">
-        <v>0.99505112170813059</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP24">
-        <v>90.729435350939028</v>
+        <v>150.6984130259078</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9716,16 +9716,16 @@
         <v>635</v>
       </c>
       <c r="BA24" t="s">
+        <v>671</v>
+      </c>
+      <c r="BB24" t="s">
         <v>672</v>
       </c>
-      <c r="BB24" t="s">
-        <v>673</v>
-      </c>
       <c r="BC24">
-        <v>0.99279657608325511</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD24">
-        <v>132.06277180699064</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9790,16 +9790,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99590738174919524</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB25">
-        <v>75.031334598088264</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9832,10 +9832,10 @@
         <v>555</v>
       </c>
       <c r="AO25">
-        <v>0.99578710491059208</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP25">
-        <v>77.236409972479407</v>
+        <v>78.445591424369994</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9862,16 +9862,16 @@
         <v>637</v>
       </c>
       <c r="BA25" t="s">
+        <v>673</v>
+      </c>
+      <c r="BB25" t="s">
         <v>674</v>
       </c>
-      <c r="BB25" t="s">
-        <v>414</v>
-      </c>
       <c r="BC25">
-        <v>0.98830355217046739</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD25">
-        <v>214.43487687476414</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9936,16 +9936,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99299045119957896</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB26">
-        <v>128.50839467438524</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9978,10 +9978,10 @@
         <v>557</v>
       </c>
       <c r="AO26">
-        <v>0.99393947890433676</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP26">
-        <v>111.10955342049355</v>
+        <v>72.069660828511601</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10014,10 +10014,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.99447517161328947</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD26">
-        <v>101.28852042302684</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10082,16 +10082,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99615584710269711</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB27">
-        <v>70.476136450553028</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10124,10 +10124,10 @@
         <v>559</v>
       </c>
       <c r="AO27">
-        <v>0.99576662598769528</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP27">
-        <v>77.611856892252987</v>
+        <v>89.511926450871471</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10228,16 +10228,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99599518539997189</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB28">
-        <v>73.421601000514329</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10270,10 +10270,10 @@
         <v>561</v>
       </c>
       <c r="AO28">
-        <v>0.99796084623978776</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP28">
-        <v>37.384485603890518</v>
+        <v>100.63855719912947</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10303,7 +10303,7 @@
         <v>679</v>
       </c>
       <c r="BB28" t="s">
-        <v>547</v>
+        <v>597</v>
       </c>
       <c r="BC28">
         <v>0.99581145929743231</v>
@@ -10374,16 +10374,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99398571695284077</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB29">
-        <v>110.2618558645854</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10416,10 +10416,10 @@
         <v>563</v>
       </c>
       <c r="AO29">
-        <v>0.98860885963065015</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP29">
-        <v>208.83757343808102</v>
+        <v>154.37346914756148</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10520,16 +10520,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99726845868655478</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB30">
-        <v>50.078257413162468</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10562,10 +10562,10 @@
         <v>565</v>
       </c>
       <c r="AO30">
-        <v>0.99333075340694588</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP30">
-        <v>122.26952087265865</v>
+        <v>111.02977673354209</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10666,16 +10666,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99456731509164431</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB31">
-        <v>99.599223319854588</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10708,10 +10708,10 @@
         <v>567</v>
       </c>
       <c r="AO31">
-        <v>0.99201650479533909</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP31">
-        <v>146.36407875211563</v>
+        <v>208.83757343808102</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10776,16 +10776,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99466941924265306</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB32">
-        <v>97.727313884694652</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10818,10 +10818,10 @@
         <v>569</v>
       </c>
       <c r="AO32">
-        <v>0.9951764810877296</v>
+        <v>0.99333075340694588</v>
       </c>
       <c r="AP32">
-        <v>88.431180058290352</v>
+        <v>122.26952087265865</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10886,16 +10886,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>303</v>
+        <v>275</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99527761530085967</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB33">
-        <v>86.577052817573119</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10928,10 +10928,10 @@
         <v>571</v>
       </c>
       <c r="AO33">
-        <v>0.99247550518926964</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP33">
-        <v>137.94907153005732</v>
+        <v>146.36407875211563</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10996,16 +10996,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.9951066982538278</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB34">
-        <v>89.710532013157362</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11038,10 +11038,10 @@
         <v>573</v>
       </c>
       <c r="AO34">
-        <v>0.99517693573038513</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP34">
-        <v>88.42284494294006</v>
+        <v>88.431180058290352</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11106,16 +11106,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99681791473814529</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB35">
-        <v>58.33822980066963</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11148,10 +11148,10 @@
         <v>575</v>
       </c>
       <c r="AO35">
-        <v>0.99838396904917182</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP35">
-        <v>29.627234098515917</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11216,16 +11216,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.98958063849079669</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB36">
-        <v>191.02162766872783</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11258,10 +11258,10 @@
         <v>577</v>
       </c>
       <c r="AO36">
-        <v>0.99604689649306255</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP36">
-        <v>72.473564293852363</v>
+        <v>240.53953099643502</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11326,16 +11326,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.98298990306503153</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB37">
-        <v>311.85177714108931</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11368,10 +11368,10 @@
         <v>579</v>
       </c>
       <c r="AO37">
-        <v>0.99164055829901554</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP37">
-        <v>153.25643118471478</v>
+        <v>104.26406003195649</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11436,16 +11436,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99495781957805363</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB38">
-        <v>92.439974402351027</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11478,10 +11478,10 @@
         <v>581</v>
       </c>
       <c r="AO38">
-        <v>0.99606892759117205</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP38">
-        <v>72.069660828511601</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11546,16 +11546,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99564550658027606</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB39">
-        <v>79.832379361605149</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11588,10 +11588,10 @@
         <v>583</v>
       </c>
       <c r="AO39">
-        <v>0.99511753128449787</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP39">
-        <v>89.511926450871471</v>
+        <v>31.154905747485419</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11656,16 +11656,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>275</v>
+        <v>307</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99635918407512603</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB40">
-        <v>66.748291956023195</v>
+        <v>73.421601000514329</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11698,10 +11698,10 @@
         <v>585</v>
       </c>
       <c r="AO40">
-        <v>0.9945106241527748</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP40">
-        <v>100.63855719912947</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11766,16 +11766,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99305283137490208</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB41">
-        <v>127.36475812679497</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11808,10 +11808,10 @@
         <v>587</v>
       </c>
       <c r="AO41">
-        <v>0.9915796289555876</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP41">
-        <v>154.37346914756148</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11876,16 +11876,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99588759895151135</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB42">
-        <v>75.394019222291774</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11918,10 +11918,10 @@
         <v>589</v>
       </c>
       <c r="AO42">
-        <v>0.99394383035998857</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP42">
-        <v>111.02977673354209</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11986,16 +11986,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99545581573707076</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB43">
-        <v>83.310044820369185</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12028,10 +12028,10 @@
         <v>591</v>
       </c>
       <c r="AO43">
-        <v>0.99601677315501558</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP43">
-        <v>73.025825491381909</v>
+        <v>75.626528315847352</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12096,16 +12096,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99491802052597356</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB44">
-        <v>93.169623690484769</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12138,10 +12138,10 @@
         <v>593</v>
       </c>
       <c r="AO44">
-        <v>0.99620690928326405</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP44">
-        <v>69.53999647349201</v>
+        <v>78.289282890438841</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12206,16 +12206,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>306</v>
+        <v>265</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.9967349730525964</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB45">
-        <v>59.858827369067072</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12245,13 +12245,13 @@
         <v>594</v>
       </c>
       <c r="AN45" t="s">
-        <v>428</v>
+        <v>595</v>
       </c>
       <c r="AO45">
-        <v>0.99495142174876894</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP45">
-        <v>92.557267939235231</v>
+        <v>90.729435350939028</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12316,16 +12316,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99648891019904884</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB46">
-        <v>64.369979684103896</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12352,16 +12352,16 @@
         <v>513</v>
       </c>
       <c r="AM46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN46" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO46">
-        <v>0.98687966194564902</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP46">
-        <v>240.53953099643502</v>
+        <v>97.492467996683757</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12426,16 +12426,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99849249864903489</v>
+        <v>0.99331672850632224</v>
       </c>
       <c r="AB47">
-        <v>27.63752476769432</v>
+        <v>122.52664405075954</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12462,16 +12462,16 @@
         <v>515</v>
       </c>
       <c r="AM47" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN47" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO47">
-        <v>0.99431286945280239</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP47">
-        <v>104.26406003195649</v>
+        <v>110.17470964763046</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12536,16 +12536,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99484635552608569</v>
+        <v>0.99698458324869177</v>
       </c>
       <c r="AB48">
-        <v>94.483482021761333</v>
+        <v>55.282640440651299</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12572,16 +12572,16 @@
         <v>517</v>
       </c>
       <c r="AM48" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO48">
-        <v>0.99692167417445865</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP48">
-        <v>56.43597346825765</v>
+        <v>64.84977570462992</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12646,16 +12646,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99331672850632224</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB49">
-        <v>122.52664405075954</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12682,16 +12682,16 @@
         <v>519</v>
       </c>
       <c r="AM49" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO49">
-        <v>0.99830064150468256</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP49">
-        <v>31.154905747485419</v>
+        <v>72.473564293852363</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12756,16 +12756,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99698458324869177</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB50">
-        <v>55.282640440651299</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12792,16 +12792,16 @@
         <v>521</v>
       </c>
       <c r="AM50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AN50" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO50">
-        <v>0.99788320682147802</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP50">
-        <v>38.807874939569167</v>
+        <v>153.25643118471478</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12866,16 +12866,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99519943077301054</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB51">
-        <v>88.010435828140345</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12902,16 +12902,16 @@
         <v>523</v>
       </c>
       <c r="AM51" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN51" t="s">
-        <v>606</v>
+        <v>420</v>
       </c>
       <c r="AO51">
-        <v>0.99677069953771458</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP51">
-        <v>59.203841808565592</v>
+        <v>73.443263495810669</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13018,10 +13018,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99824683646529189</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP52">
-        <v>32.141331469648897</v>
+        <v>38.251429847691753</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13104,7 +13104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8901FD1-355D-45B3-9BD2-ACC269CAEA3D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE2951F-9BD9-4E0B-A53B-FFC9678D92E4}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13216,7 +13216,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>539</v>
+        <v>606</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13249,7 +13249,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13284,7 +13284,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>548</v>
+        <v>598</v>
       </c>
       <c r="L12">
         <v>41.38517014727136</v>
@@ -13352,7 +13352,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>527</v>
+        <v>550</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13385,7 +13385,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13420,7 +13420,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>542</v>
+        <v>590</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13453,7 +13453,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>674</v>
+        <v>662</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13488,7 +13488,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>588</v>
+        <v>564</v>
       </c>
       <c r="L15">
         <v>13.570215224493221</v>
@@ -13556,7 +13556,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>582</v>
+        <v>558</v>
       </c>
       <c r="L16">
         <v>59.282276232111244</v>
@@ -13589,7 +13589,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13624,7 +13624,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>578</v>
+        <v>604</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13657,7 +13657,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>656</v>
+        <v>671</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13692,7 +13692,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13725,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>650</v>
+        <v>665</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13760,7 +13760,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>601</v>
+        <v>582</v>
       </c>
       <c r="L19">
         <v>15.766767829784982</v>
@@ -13793,7 +13793,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13828,7 +13828,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>605</v>
+        <v>586</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13861,7 +13861,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13896,7 +13896,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>540</v>
+        <v>607</v>
       </c>
       <c r="L21">
         <v>11.016586435503244</v>
@@ -13929,7 +13929,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>675</v>
+        <v>663</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13964,7 +13964,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>531</v>
+        <v>554</v>
       </c>
       <c r="L22">
         <v>6.1733535033999489</v>
@@ -13997,7 +13997,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>668</v>
+        <v>649</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14032,7 +14032,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>572</v>
+        <v>544</v>
       </c>
       <c r="L23">
         <v>4.8541340927283274</v>
@@ -14065,7 +14065,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>658</v>
+        <v>673</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14100,7 +14100,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>586</v>
+        <v>562</v>
       </c>
       <c r="L24">
         <v>13.114783900591691</v>
@@ -14168,7 +14168,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>607</v>
+        <v>588</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14201,7 +14201,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>652</v>
+        <v>667</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14236,7 +14236,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14304,7 +14304,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14337,7 +14337,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14372,7 +14372,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>592</v>
+        <v>535</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14405,7 +14405,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14440,7 +14440,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>603</v>
+        <v>584</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14473,7 +14473,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>672</v>
+        <v>651</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14508,7 +14508,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>594</v>
+        <v>537</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14541,7 +14541,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>654</v>
+        <v>669</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14576,7 +14576,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14611,7 +14611,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>560</v>
+        <v>542</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14646,7 +14646,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>552</v>
+        <v>594</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14681,7 +14681,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14716,7 +14716,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>574</v>
+        <v>546</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14751,7 +14751,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14786,7 +14786,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14821,7 +14821,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14856,7 +14856,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="L39">
         <v>26.291803917155487</v>
@@ -14891,7 +14891,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14926,7 +14926,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14961,7 +14961,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14996,7 +14996,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>529</v>
+        <v>552</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15031,7 +15031,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15066,7 +15066,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>590</v>
+        <v>533</v>
       </c>
       <c r="L45">
         <v>10.919135648131764</v>
@@ -15101,7 +15101,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>576</v>
+        <v>602</v>
       </c>
       <c r="L46">
         <v>33.912640160809843</v>
@@ -15136,7 +15136,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15171,7 +15171,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>546</v>
+        <v>596</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15206,7 +15206,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>597</v>
+        <v>578</v>
       </c>
       <c r="L49">
         <v>62.791395577971592</v>
@@ -15241,7 +15241,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>556</v>
+        <v>538</v>
       </c>
       <c r="L50">
         <v>37.678782480143312</v>
@@ -15276,7 +15276,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>580</v>
+        <v>556</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15311,7 +15311,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>595</v>
+        <v>576</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15326,7 +15326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15104F78-0452-444E-9766-4B46327404BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D8352A-7DB6-49F1-BAB5-47A58B4391A4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17143,7 +17143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09E767D8-42FC-4D46-8CCB-A7B7A63E3A7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978C7A1F-94A8-429F-A77B-D459C1490F03}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{964117AE-6809-498B-A7F9-B2CBC532E18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BC5E887-29A5-425A-B7F9-22FFF3A9DD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,18 +1060,210 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_018</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_016</t>
   </si>
   <si>
@@ -1102,18 +1294,6 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_010</t>
   </si>
   <si>
@@ -1144,192 +1324,108 @@
     <t>connecting solar to buses in cluster 28</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
   </si>
   <si>
@@ -1348,12 +1444,6 @@
     <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
   </si>
   <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
     <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
   </si>
   <si>
@@ -1369,94 +1459,148 @@
     <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
   </si>
   <si>
-    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
+    <t>distr_wonelc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_037</t>
@@ -1477,6 +1621,60 @@
     <t>connecting wind onshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ZAF_035</t>
   </si>
   <si>
@@ -1513,202 +1711,145 @@
     <t>connecting wind onshore to buses in cluster 22</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
+    <t>elc_won_ZAF_032</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_029</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_030</t>
+  </si>
+  <si>
+    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_021</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_037</t>
@@ -1729,6 +1870,60 @@
     <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
   </si>
   <si>
+    <t>elc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_won_ZAF_035</t>
   </si>
   <si>
@@ -1762,199 +1957,118 @@
     <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_032</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_029</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w200757306-400_ZAF,e_ZA28-765_ZAF,e_w181366662-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_030</t>
-  </si>
-  <si>
-    <t>e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_021</t>
-  </si>
-  <si>
-    <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+    <t>distr_wofelc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_012</t>
@@ -1963,223 +2077,109 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
+    <t>elc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_012</t>
   </si>
   <si>
     <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_005</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
   </si>
   <si>
     <t>e_won_ZAF_001</t>
@@ -7508,7 +7508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6349821-E822-47D3-B720-A5ADB53547C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF81764-647E-48B5-8A20-93D993B32ABF}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7746,16 +7746,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99456731509164431</v>
+        <v>0.99331672850632224</v>
       </c>
       <c r="AB11">
-        <v>99.599223319854588</v>
+        <v>122.52664405075954</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7788,10 +7788,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.99504825389388352</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP11">
-        <v>90.782011945468795</v>
+        <v>208.83757343808102</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7821,13 +7821,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>650</v>
+        <v>424</v>
       </c>
       <c r="BC11">
-        <v>0.99501631001524238</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD11">
-        <v>91.367649720556983</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7892,16 +7892,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>280</v>
+        <v>304</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99466941924265306</v>
+        <v>0.99698458324869177</v>
       </c>
       <c r="AB12">
-        <v>97.727313884694652</v>
+        <v>55.282640440651299</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7934,10 +7934,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99546749107529653</v>
+        <v>0.99333075340694588</v>
       </c>
       <c r="AP12">
-        <v>83.095996952896456</v>
+        <v>122.26952087265865</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7964,16 +7964,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
+        <v>650</v>
+      </c>
+      <c r="BB12" t="s">
         <v>651</v>
       </c>
-      <c r="BB12" t="s">
-        <v>652</v>
-      </c>
       <c r="BC12">
-        <v>0.99279657608325511</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD12">
-        <v>132.06277180699064</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8038,16 +8038,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99527761530085967</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB13">
-        <v>86.577052817573119</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8080,10 +8080,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99676762792199902</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP13">
-        <v>59.260154763351615</v>
+        <v>146.36407875211563</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8110,16 +8110,16 @@
         <v>613</v>
       </c>
       <c r="BA13" t="s">
+        <v>652</v>
+      </c>
+      <c r="BB13" t="s">
         <v>653</v>
       </c>
-      <c r="BB13" t="s">
-        <v>426</v>
-      </c>
       <c r="BC13">
-        <v>0.99010219056094972</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD13">
-        <v>181.45983971592244</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8184,16 +8184,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>297</v>
+        <v>267</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.9951066982538278</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB14">
-        <v>89.710532013157362</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8226,10 +8226,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.99601677315501558</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP14">
-        <v>73.025825491381909</v>
+        <v>88.431180058290352</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8259,13 +8259,13 @@
         <v>654</v>
       </c>
       <c r="BB14" t="s">
-        <v>597</v>
+        <v>655</v>
       </c>
       <c r="BC14">
-        <v>0.99223220184557481</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD14">
-        <v>142.40963283112865</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8330,16 +8330,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99681791473814529</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB15">
-        <v>58.33822980066963</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8372,10 +8372,10 @@
         <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.99620690928326405</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP15">
-        <v>69.53999647349201</v>
+        <v>137.94907153005732</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8402,16 +8402,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="BB15" t="s">
-        <v>656</v>
+        <v>569</v>
       </c>
       <c r="BC15">
-        <v>0.99462081464868646</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD15">
-        <v>98.618398107414592</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8476,16 +8476,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.98958063849079669</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB16">
-        <v>191.02162766872783</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8515,13 +8515,13 @@
         <v>537</v>
       </c>
       <c r="AN16" t="s">
-        <v>440</v>
+        <v>538</v>
       </c>
       <c r="AO16">
-        <v>0.99495142174876894</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP16">
-        <v>92.557267939235231</v>
+        <v>240.53953099643502</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8551,13 +8551,13 @@
         <v>657</v>
       </c>
       <c r="BB16" t="s">
-        <v>581</v>
+        <v>658</v>
       </c>
       <c r="BC16">
-        <v>0.99507162964364948</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD16">
-        <v>90.353456533092867</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8622,16 +8622,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99590738174919524</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB17">
-        <v>75.031334598088264</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8658,16 +8658,16 @@
         <v>455</v>
       </c>
       <c r="AM17" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AN17" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO17">
-        <v>0.99393947890433676</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP17">
-        <v>111.10955342049355</v>
+        <v>104.26406003195649</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8694,16 +8694,16 @@
         <v>621</v>
       </c>
       <c r="BA17" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="BB17" t="s">
-        <v>659</v>
+        <v>542</v>
       </c>
       <c r="BC17">
-        <v>0.98805842341846151</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD17">
-        <v>218.92890399487229</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8768,16 +8768,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99299045119957896</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB18">
-        <v>128.50839467438524</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8804,16 +8804,16 @@
         <v>457</v>
       </c>
       <c r="AM18" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN18" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO18">
-        <v>0.99576662598769528</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP18">
-        <v>77.611856892252987</v>
+        <v>56.43597346825765</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8846,10 +8846,10 @@
         <v>661</v>
       </c>
       <c r="BC18">
-        <v>0.99481516601444531</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD18">
-        <v>95.055289735168813</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8914,16 +8914,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99715332943801627</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB19">
-        <v>52.188960303034925</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8950,16 +8950,16 @@
         <v>459</v>
       </c>
       <c r="AM19" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AN19" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AO19">
-        <v>0.99796084623978776</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP19">
-        <v>37.384485603890518</v>
+        <v>31.154905747485419</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8989,13 +8989,13 @@
         <v>662</v>
       </c>
       <c r="BB19" t="s">
-        <v>406</v>
+        <v>663</v>
       </c>
       <c r="BC19">
-        <v>0.98830355217046739</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD19">
-        <v>214.43487687476414</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9060,16 +9060,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99341896335341162</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB20">
-        <v>120.65233852078616</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9096,16 +9096,16 @@
         <v>461</v>
       </c>
       <c r="AM20" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN20" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO20">
-        <v>0.99517693573038513</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP20">
-        <v>88.42284494294006</v>
+        <v>38.807874939569167</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9132,16 +9132,16 @@
         <v>627</v>
       </c>
       <c r="BA20" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="BB20" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="BC20">
-        <v>0.99447517161328947</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD20">
-        <v>101.28852042302684</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9206,16 +9206,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99601318900739955</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB21">
-        <v>73.091534864341</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9242,16 +9242,16 @@
         <v>463</v>
       </c>
       <c r="AM21" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AN21" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AO21">
-        <v>0.99838396904917182</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP21">
-        <v>29.627234098515917</v>
+        <v>59.203841808565592</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,16 +9278,16 @@
         <v>629</v>
       </c>
       <c r="BA21" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="BB21" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="BC21">
-        <v>0.99672758029478525</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD21">
-        <v>59.994361262269514</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9352,16 +9352,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99695083910621241</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB22">
-        <v>55.901283052772143</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9388,16 +9388,16 @@
         <v>465</v>
       </c>
       <c r="AM22" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN22" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AO22">
-        <v>0.99578710491059208</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP22">
-        <v>77.236409972479407</v>
+        <v>32.141331469648897</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9424,16 +9424,16 @@
         <v>631</v>
       </c>
       <c r="BA22" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="BB22" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="BC22">
-        <v>0.99231435496704667</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD22">
-        <v>140.90349227081035</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9498,16 +9498,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99758018972146978</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB23">
-        <v>44.363188439721</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9534,16 +9534,16 @@
         <v>467</v>
       </c>
       <c r="AM23" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AN23" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AO23">
-        <v>0.99514523900053742</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP23">
-        <v>89.003951656813172</v>
+        <v>90.729435350939028</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9570,16 +9570,16 @@
         <v>633</v>
       </c>
       <c r="BA23" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="BB23" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="BC23">
-        <v>0.99229811324031303</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD23">
-        <v>141.20125726092687</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9644,16 +9644,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99588759895151135</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB24">
-        <v>75.394019222291774</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9680,16 +9680,16 @@
         <v>469</v>
       </c>
       <c r="AM24" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN24" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO24">
-        <v>0.99178008656222316</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP24">
-        <v>150.6984130259078</v>
+        <v>72.069660828511601</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9716,16 +9716,16 @@
         <v>635</v>
       </c>
       <c r="BA24" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="BB24" t="s">
-        <v>672</v>
+        <v>569</v>
       </c>
       <c r="BC24">
-        <v>0.99582070241731502</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD24">
-        <v>76.620455682557321</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9790,16 +9790,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99545581573707076</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB25">
-        <v>83.310044820369185</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9826,16 +9826,16 @@
         <v>471</v>
       </c>
       <c r="AM25" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AN25" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AO25">
-        <v>0.99572114955867075</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP25">
-        <v>78.445591424369994</v>
+        <v>89.511926450871471</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9868,10 +9868,10 @@
         <v>674</v>
       </c>
       <c r="BC25">
-        <v>0.98843991010136767</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD25">
-        <v>211.93498147492642</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9936,16 +9936,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99491802052597356</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB26">
-        <v>93.169623690484769</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9972,16 +9972,16 @@
         <v>473</v>
       </c>
       <c r="AM26" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN26" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO26">
-        <v>0.99606892759117205</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP26">
-        <v>72.069660828511601</v>
+        <v>100.63855719912947</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10014,10 +10014,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.99545422785121029</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD26">
-        <v>83.33915606114418</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10082,16 +10082,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.9967349730525964</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB27">
-        <v>59.858827369067072</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10118,16 +10118,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AN27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AO27">
-        <v>0.99511753128449787</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP27">
-        <v>89.511926450871471</v>
+        <v>154.37346914756148</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10157,13 +10157,13 @@
         <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>678</v>
+        <v>430</v>
       </c>
       <c r="BC27">
-        <v>0.991900752046595</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD27">
-        <v>148.48621247909063</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10228,16 +10228,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>302</v>
+        <v>268</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99648891019904884</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB28">
-        <v>64.369979684103896</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10264,16 +10264,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AN28" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO28">
-        <v>0.9945106241527748</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP28">
-        <v>100.63855719912947</v>
+        <v>111.02977673354209</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10300,16 +10300,16 @@
         <v>643</v>
       </c>
       <c r="BA28" t="s">
+        <v>678</v>
+      </c>
+      <c r="BB28" t="s">
         <v>679</v>
       </c>
-      <c r="BB28" t="s">
-        <v>597</v>
-      </c>
       <c r="BC28">
-        <v>0.99581145929743231</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD28">
-        <v>76.789912880408167</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10374,16 +10374,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99849249864903489</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB29">
-        <v>27.63752476769432</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10410,16 +10410,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AN29" t="s">
-        <v>563</v>
+        <v>428</v>
       </c>
       <c r="AO29">
-        <v>0.9915796289555876</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP29">
-        <v>154.37346914756148</v>
+        <v>73.443263495810669</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10452,10 +10452,10 @@
         <v>681</v>
       </c>
       <c r="BC29">
-        <v>0.99429876975975018</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD29">
-        <v>104.52255440457925</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10520,16 +10520,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99484635552608569</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB30">
-        <v>94.483482021761333</v>
+        <v>73.421601000514329</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10562,10 +10562,10 @@
         <v>565</v>
       </c>
       <c r="AO30">
-        <v>0.99394383035998857</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP30">
-        <v>111.02977673354209</v>
+        <v>38.251429847691753</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10598,10 +10598,10 @@
         <v>683</v>
       </c>
       <c r="BC30">
-        <v>0.98743040674179927</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD30">
-        <v>230.44254306701379</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10666,16 +10666,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99492995157662933</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB31">
-        <v>92.95088776179594</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10708,10 +10708,10 @@
         <v>567</v>
       </c>
       <c r="AO31">
-        <v>0.98860885963065015</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP31">
-        <v>208.83757343808102</v>
+        <v>77.236409972479407</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10776,16 +10776,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99197366299435197</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB32">
-        <v>147.14951177021345</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10818,10 +10818,10 @@
         <v>569</v>
       </c>
       <c r="AO32">
-        <v>0.99333075340694588</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP32">
-        <v>122.26952087265865</v>
+        <v>97.492467996683757</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10886,16 +10886,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99635918407512603</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB33">
-        <v>66.748291956023195</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10928,10 +10928,10 @@
         <v>571</v>
       </c>
       <c r="AO33">
-        <v>0.99201650479533909</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP33">
-        <v>146.36407875211563</v>
+        <v>110.17470964763046</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10996,16 +10996,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99305283137490208</v>
+        <v>0.99446824002516876</v>
       </c>
       <c r="AB34">
-        <v>127.36475812679497</v>
+        <v>101.41559953857198</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11038,10 +11038,10 @@
         <v>573</v>
       </c>
       <c r="AO34">
-        <v>0.9951764810877296</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP34">
-        <v>88.431180058290352</v>
+        <v>64.84977570462992</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11106,16 +11106,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99567500995545699</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB35">
-        <v>79.29148414995565</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11148,10 +11148,10 @@
         <v>575</v>
       </c>
       <c r="AO35">
-        <v>0.99247550518926964</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP35">
-        <v>137.94907153005732</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11216,16 +11216,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>277</v>
+        <v>301</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99519943077301054</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB36">
-        <v>88.010435828140345</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11258,10 +11258,10 @@
         <v>577</v>
       </c>
       <c r="AO36">
-        <v>0.98687966194564902</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP36">
-        <v>240.53953099643502</v>
+        <v>83.095996952896456</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11326,16 +11326,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99398571695284077</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB37">
-        <v>110.2618558645854</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11368,10 +11368,10 @@
         <v>579</v>
       </c>
       <c r="AO37">
-        <v>0.99431286945280239</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP37">
-        <v>104.26406003195649</v>
+        <v>59.260154763351615</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11436,16 +11436,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99726845868655478</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB38">
-        <v>50.078257413162468</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11478,10 +11478,10 @@
         <v>581</v>
       </c>
       <c r="AO38">
-        <v>0.99692167417445865</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP38">
-        <v>56.43597346825765</v>
+        <v>75.626528315847352</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11546,16 +11546,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99615584710269711</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB39">
-        <v>70.476136450553028</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11588,10 +11588,10 @@
         <v>583</v>
       </c>
       <c r="AO39">
-        <v>0.99830064150468256</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP39">
-        <v>31.154905747485419</v>
+        <v>78.289282890438841</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11656,16 +11656,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>307</v>
+        <v>286</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99599518539997189</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB40">
-        <v>73.421601000514329</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11698,10 +11698,10 @@
         <v>585</v>
       </c>
       <c r="AO40">
-        <v>0.99788320682147802</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP40">
-        <v>38.807874939569167</v>
+        <v>72.473564293852363</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11766,16 +11766,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99294071263677341</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB41">
-        <v>129.42026832582172</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11808,10 +11808,10 @@
         <v>587</v>
       </c>
       <c r="AO41">
-        <v>0.99677069953771458</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP41">
-        <v>59.203841808565592</v>
+        <v>153.25643118471478</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11876,16 +11876,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99535442409010222</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB42">
-        <v>85.168891681458845</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11918,10 +11918,10 @@
         <v>589</v>
       </c>
       <c r="AO42">
-        <v>0.99824683646529189</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP42">
-        <v>32.141331469648897</v>
+        <v>89.003951656813172</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11986,16 +11986,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99309463181702251</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB43">
-        <v>126.5984166879211</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12028,10 +12028,10 @@
         <v>591</v>
       </c>
       <c r="AO43">
-        <v>0.99587491663731742</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP43">
-        <v>75.626528315847352</v>
+        <v>150.6984130259078</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12096,16 +12096,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99827081845920873</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB44">
-        <v>31.701661581174136</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12138,10 +12138,10 @@
         <v>593</v>
       </c>
       <c r="AO44">
-        <v>0.99572967547870339</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP44">
-        <v>78.289282890438841</v>
+        <v>78.445591424369994</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12206,16 +12206,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>265</v>
+        <v>303</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99021255380204343</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB45">
-        <v>179.43651362920434</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12248,10 +12248,10 @@
         <v>595</v>
       </c>
       <c r="AO45">
-        <v>0.99505112170813059</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP45">
-        <v>90.729435350939028</v>
+        <v>88.42284494294006</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12316,16 +12316,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.99766238113026029</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB46">
-        <v>42.856345945228725</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12358,10 +12358,10 @@
         <v>597</v>
       </c>
       <c r="AO46">
-        <v>0.99468222901836267</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP46">
-        <v>97.492467996683757</v>
+        <v>29.627234098515917</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12426,16 +12426,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99331672850632224</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB47">
-        <v>122.52664405075954</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12468,10 +12468,10 @@
         <v>599</v>
       </c>
       <c r="AO47">
-        <v>0.99399047038285648</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP47">
-        <v>110.17470964763046</v>
+        <v>73.025825491381909</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12536,16 +12536,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99698458324869177</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB48">
-        <v>55.282640440651299</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12578,10 +12578,10 @@
         <v>601</v>
       </c>
       <c r="AO48">
-        <v>0.99646273950702013</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP48">
-        <v>64.84977570462992</v>
+        <v>69.53999647349201</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12646,16 +12646,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.98298990306503153</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB49">
-        <v>311.85177714108931</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12685,13 +12685,13 @@
         <v>602</v>
       </c>
       <c r="AN49" t="s">
-        <v>603</v>
+        <v>415</v>
       </c>
       <c r="AO49">
-        <v>0.99604689649306255</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP49">
-        <v>72.473564293852363</v>
+        <v>92.557267939235231</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12756,16 +12756,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99495781957805363</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB50">
-        <v>92.439974402351027</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12792,16 +12792,16 @@
         <v>521</v>
       </c>
       <c r="AM50" t="s">
+        <v>603</v>
+      </c>
+      <c r="AN50" t="s">
         <v>604</v>
       </c>
-      <c r="AN50" t="s">
-        <v>605</v>
-      </c>
       <c r="AO50">
-        <v>0.99164055829901554</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP50">
-        <v>153.25643118471478</v>
+        <v>111.10955342049355</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12866,16 +12866,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99564550658027606</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB51">
-        <v>79.832379361605149</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12902,16 +12902,16 @@
         <v>523</v>
       </c>
       <c r="AM51" t="s">
+        <v>605</v>
+      </c>
+      <c r="AN51" t="s">
         <v>606</v>
       </c>
-      <c r="AN51" t="s">
-        <v>420</v>
-      </c>
       <c r="AO51">
-        <v>0.99599400380931946</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP51">
-        <v>73.443263495810669</v>
+        <v>77.611856892252987</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12976,16 +12976,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99464845307754257</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB52">
-        <v>98.111693578387175</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13018,10 +13018,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99791355837194406</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP52">
-        <v>38.251429847691753</v>
+        <v>37.384485603890518</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13086,16 +13086,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99446824002516876</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB53">
-        <v>101.41559953857198</v>
+        <v>44.363188439721</v>
       </c>
     </row>
   </sheetData>
@@ -13104,7 +13104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE2951F-9BD9-4E0B-A53B-FFC9678D92E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB81A15-E3DD-4417-96CD-FB5BEAB4993C}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13216,7 +13216,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>606</v>
+        <v>563</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13249,7 +13249,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13284,7 +13284,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>598</v>
+        <v>570</v>
       </c>
       <c r="L12">
         <v>41.38517014727136</v>
@@ -13317,7 +13317,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>677</v>
+        <v>670</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13352,7 +13352,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>550</v>
+        <v>588</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13385,7 +13385,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>675</v>
+        <v>662</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13420,7 +13420,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13453,7 +13453,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>662</v>
+        <v>677</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13488,7 +13488,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="L15">
         <v>13.570215224493221</v>
@@ -13521,7 +13521,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>679</v>
+        <v>672</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13556,7 +13556,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="L16">
         <v>59.282276232111244</v>
@@ -13589,7 +13589,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13624,7 +13624,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>604</v>
+        <v>586</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13657,7 +13657,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>671</v>
+        <v>654</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13692,7 +13692,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>531</v>
+        <v>578</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13725,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13760,7 +13760,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>582</v>
+        <v>543</v>
       </c>
       <c r="L19">
         <v>15.766767829784982</v>
@@ -13793,7 +13793,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13828,7 +13828,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>586</v>
+        <v>547</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13861,7 +13861,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13896,7 +13896,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>607</v>
+        <v>564</v>
       </c>
       <c r="L21">
         <v>11.016586435503244</v>
@@ -13929,7 +13929,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>663</v>
+        <v>678</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13964,7 +13964,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="L22">
         <v>6.1733535033999489</v>
@@ -13997,7 +13997,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>649</v>
+        <v>682</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14032,7 +14032,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="L23">
         <v>4.8541340927283274</v>
@@ -14065,7 +14065,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14100,7 +14100,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="L24">
         <v>13.114783900591691</v>
@@ -14133,7 +14133,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14168,7 +14168,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>588</v>
+        <v>549</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14201,7 +14201,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14236,7 +14236,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>572</v>
+        <v>533</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14269,7 +14269,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>680</v>
+        <v>673</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14304,7 +14304,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>580</v>
+        <v>541</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14337,7 +14337,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14372,7 +14372,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>535</v>
+        <v>600</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14405,7 +14405,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14440,7 +14440,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>584</v>
+        <v>545</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14473,7 +14473,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>651</v>
+        <v>666</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14508,7 +14508,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>537</v>
+        <v>602</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14541,7 +14541,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>669</v>
+        <v>652</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14576,7 +14576,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>574</v>
+        <v>535</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14611,7 +14611,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>542</v>
+        <v>607</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14646,7 +14646,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>594</v>
+        <v>551</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14681,7 +14681,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>540</v>
+        <v>605</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14716,7 +14716,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>546</v>
+        <v>596</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14751,7 +14751,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>529</v>
+        <v>576</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14786,7 +14786,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14821,7 +14821,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>600</v>
+        <v>572</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14856,7 +14856,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>568</v>
+        <v>529</v>
       </c>
       <c r="L39">
         <v>26.291803917155487</v>
@@ -14891,7 +14891,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>570</v>
+        <v>531</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14926,7 +14926,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14961,7 +14961,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>566</v>
+        <v>527</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14996,7 +14996,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>552</v>
+        <v>590</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15031,7 +15031,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15066,7 +15066,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>533</v>
+        <v>598</v>
       </c>
       <c r="L45">
         <v>10.919135648131764</v>
@@ -15101,7 +15101,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>602</v>
+        <v>584</v>
       </c>
       <c r="L46">
         <v>33.912640160809843</v>
@@ -15136,7 +15136,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>527</v>
+        <v>574</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15171,7 +15171,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>596</v>
+        <v>568</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15206,7 +15206,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>578</v>
+        <v>539</v>
       </c>
       <c r="L49">
         <v>62.791395577971592</v>
@@ -15241,7 +15241,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>538</v>
+        <v>603</v>
       </c>
       <c r="L50">
         <v>37.678782480143312</v>
@@ -15276,7 +15276,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15311,7 +15311,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>576</v>
+        <v>537</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15326,7 +15326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D8352A-7DB6-49F1-BAB5-47A58B4391A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2500E93-9FE5-4090-A24E-31E585E7B159}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17143,7 +17143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978C7A1F-94A8-429F-A77B-D459C1490F03}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02B7C72-E53E-47DA-83C9-D268A267C3C4}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BC5E887-29A5-425A-B7F9-22FFF3A9DD78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3CE390B-790C-4CDF-B570-65A2E7EACAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1078,6 +1078,30 @@
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_002</t>
   </si>
   <si>
@@ -1102,6 +1126,138 @@
     <t>connecting solar to buses in cluster 27</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_006</t>
   </si>
   <si>
@@ -1144,34 +1300,16 @@
     <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
+    <t>distr_solelc_spv_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
     <t>distr_solelc_spv_ZAF_034</t>
@@ -1186,144 +1324,6 @@
     <t>connecting solar to buses in cluster 43</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1336,6 +1336,18 @@
     <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
   </si>
   <si>
@@ -1348,6 +1360,72 @@
     <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
   </si>
   <si>
+    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
   </si>
   <si>
@@ -1369,19 +1447,10 @@
     <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
-    <t>e_ZA25-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
   </si>
   <si>
     <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
@@ -1390,75 +1459,6 @@
     <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
   </si>
   <si>
-    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ZAF_032</t>
   </si>
   <si>
@@ -1489,6 +1489,114 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wonelc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_ZAF_042</t>
   </si>
   <si>
@@ -1531,10 +1639,10 @@
     <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
+    <t>distr_wonelc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_041</t>
@@ -1567,16 +1675,22 @@
     <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
+    <t>distr_wonelc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_027</t>
@@ -1585,54 +1699,6 @@
     <t>connecting wind onshore to buses in cluster 27</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_ZAF_036</t>
   </si>
   <si>
@@ -1645,72 +1711,6 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
     <t>elc_won_ZAF_032</t>
   </si>
   <si>
@@ -1741,6 +1741,108 @@
     <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
   </si>
   <si>
+    <t>elc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_004</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_031</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_001</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_won_ZAF_042</t>
   </si>
   <si>
@@ -1783,10 +1885,10 @@
     <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+    <t>elc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_041</t>
@@ -1819,13 +1921,22 @@
     <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_001</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_027</t>
@@ -1834,54 +1945,6 @@
     <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_004</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w586032034-765_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_031</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
-  </si>
-  <si>
     <t>elc_won_ZAF_036</t>
   </si>
   <si>
@@ -1894,67 +1957,70 @@
     <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
+    <t>distr_wofelc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_017</t>
@@ -1963,48 +2029,6 @@
     <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ZAF_003</t>
   </si>
   <si>
@@ -2017,105 +2041,102 @@
     <t>connecting wind offshore to buses in cluster 8</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_ZAF_019</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
+    <t>elc_wof_ZAF_006</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_009</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_001</t>
+  </si>
+  <si>
+    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_020</t>
+  </si>
+  <si>
+    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_017</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_020</t>
-  </si>
-  <si>
-    <t>e_w934819484-400_ZAF,e_w169789536-400_ZAF,e_w90454383-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_006</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF,e_r17287657-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_009</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_wof_ZAF_003</t>
   </si>
   <si>
@@ -2128,58 +2149,37 @@
     <t>e_ZA36-400_ZAF</t>
   </si>
   <si>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_005</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_016</t>
+  </si>
+  <si>
+    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_wof_ZAF_019</t>
   </si>
   <si>
     <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w107431792-400_ZAF,e_w193978748-400_ZAF,e_w836844162-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_005</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_016</t>
-  </si>
-  <si>
-    <t>e_w62218063-400_ZAF,e_w102682082-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_001</t>
-  </si>
-  <si>
-    <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
   </si>
   <si>
     <t>e_won_ZAF_001</t>
@@ -7508,7 +7508,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FF81764-647E-48B5-8A20-93D993B32ABF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBC17C-BBD7-421A-A5FB-C5FEEF0F665C}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7821,13 +7821,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>424</v>
+        <v>564</v>
       </c>
       <c r="BC11">
-        <v>0.99010219056094972</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD11">
-        <v>181.45983971592244</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7970,10 +7970,10 @@
         <v>651</v>
       </c>
       <c r="BC12">
-        <v>0.99231435496704667</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD12">
-        <v>140.90349227081035</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8038,16 +8038,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99294071263677341</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB13">
-        <v>129.42026832582172</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8113,13 +8113,13 @@
         <v>652</v>
       </c>
       <c r="BB13" t="s">
-        <v>653</v>
+        <v>576</v>
       </c>
       <c r="BC13">
-        <v>0.99229811324031303</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD13">
-        <v>141.20125726092687</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8184,16 +8184,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99535442409010222</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB14">
-        <v>85.168891681458845</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8256,16 +8256,16 @@
         <v>615</v>
       </c>
       <c r="BA14" t="s">
+        <v>653</v>
+      </c>
+      <c r="BB14" t="s">
         <v>654</v>
       </c>
-      <c r="BB14" t="s">
-        <v>655</v>
-      </c>
       <c r="BC14">
-        <v>0.99582070241731502</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD14">
-        <v>76.620455682557321</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8330,16 +8330,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>305</v>
+        <v>279</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99309463181702251</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB15">
-        <v>126.5984166879211</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8402,16 +8402,16 @@
         <v>617</v>
       </c>
       <c r="BA15" t="s">
+        <v>655</v>
+      </c>
+      <c r="BB15" t="s">
         <v>656</v>
       </c>
-      <c r="BB15" t="s">
-        <v>569</v>
-      </c>
       <c r="BC15">
-        <v>0.99223220184557481</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD15">
-        <v>142.40963283112865</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8476,16 +8476,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99827081845920873</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB16">
-        <v>31.701661581174136</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8518,10 +8518,10 @@
         <v>538</v>
       </c>
       <c r="AO16">
-        <v>0.98687966194564902</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP16">
-        <v>240.53953099643502</v>
+        <v>73.025825491381909</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8554,10 +8554,10 @@
         <v>658</v>
       </c>
       <c r="BC16">
-        <v>0.99462081464868646</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD16">
-        <v>98.618398107414592</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8622,16 +8622,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99588759895151135</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB17">
-        <v>75.394019222291774</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8664,10 +8664,10 @@
         <v>540</v>
       </c>
       <c r="AO17">
-        <v>0.99431286945280239</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP17">
-        <v>104.26406003195649</v>
+        <v>69.53999647349201</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8697,13 +8697,13 @@
         <v>659</v>
       </c>
       <c r="BB17" t="s">
-        <v>542</v>
+        <v>660</v>
       </c>
       <c r="BC17">
-        <v>0.99507162964364948</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD17">
-        <v>90.353456533092867</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8768,16 +8768,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99545581573707076</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB18">
-        <v>83.310044820369185</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8807,13 +8807,13 @@
         <v>541</v>
       </c>
       <c r="AN18" t="s">
-        <v>542</v>
+        <v>430</v>
       </c>
       <c r="AO18">
-        <v>0.99692167417445865</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP18">
-        <v>56.43597346825765</v>
+        <v>92.557267939235231</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,16 +8840,16 @@
         <v>623</v>
       </c>
       <c r="BA18" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="BB18" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="BC18">
-        <v>0.98805842341846151</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD18">
-        <v>218.92890399487229</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8914,16 +8914,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99491802052597356</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB19">
-        <v>93.169623690484769</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8950,16 +8950,16 @@
         <v>459</v>
       </c>
       <c r="AM19" t="s">
+        <v>542</v>
+      </c>
+      <c r="AN19" t="s">
         <v>543</v>
       </c>
-      <c r="AN19" t="s">
-        <v>544</v>
-      </c>
       <c r="AO19">
-        <v>0.99830064150468256</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP19">
-        <v>31.154905747485419</v>
+        <v>75.626528315847352</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8986,16 +8986,16 @@
         <v>625</v>
       </c>
       <c r="BA19" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="BB19" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="BC19">
-        <v>0.99545422785121029</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD19">
-        <v>83.33915606114418</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9060,16 +9060,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.9967349730525964</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB20">
-        <v>59.858827369067072</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9096,16 +9096,16 @@
         <v>461</v>
       </c>
       <c r="AM20" t="s">
+        <v>544</v>
+      </c>
+      <c r="AN20" t="s">
         <v>545</v>
       </c>
-      <c r="AN20" t="s">
-        <v>546</v>
-      </c>
       <c r="AO20">
-        <v>0.99788320682147802</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP20">
-        <v>38.807874939569167</v>
+        <v>78.289282890438841</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9132,16 +9132,16 @@
         <v>627</v>
       </c>
       <c r="BA20" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="BB20" t="s">
-        <v>665</v>
+        <v>420</v>
       </c>
       <c r="BC20">
-        <v>0.99672758029478525</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD20">
-        <v>59.994361262269514</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9206,16 +9206,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99648891019904884</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB21">
-        <v>64.369979684103896</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9242,16 +9242,16 @@
         <v>463</v>
       </c>
       <c r="AM21" t="s">
+        <v>546</v>
+      </c>
+      <c r="AN21" t="s">
         <v>547</v>
       </c>
-      <c r="AN21" t="s">
-        <v>548</v>
-      </c>
       <c r="AO21">
-        <v>0.99677069953771458</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP21">
-        <v>59.203841808565592</v>
+        <v>111.10955342049355</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9284,10 +9284,10 @@
         <v>667</v>
       </c>
       <c r="BC21">
-        <v>0.99279657608325511</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD21">
-        <v>132.06277180699064</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9352,16 +9352,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99849249864903489</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB22">
-        <v>27.63752476769432</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9388,16 +9388,16 @@
         <v>465</v>
       </c>
       <c r="AM22" t="s">
+        <v>548</v>
+      </c>
+      <c r="AN22" t="s">
         <v>549</v>
       </c>
-      <c r="AN22" t="s">
-        <v>550</v>
-      </c>
       <c r="AO22">
-        <v>0.99824683646529189</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP22">
-        <v>32.141331469648897</v>
+        <v>77.611856892252987</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9427,13 +9427,13 @@
         <v>668</v>
       </c>
       <c r="BB22" t="s">
-        <v>669</v>
+        <v>404</v>
       </c>
       <c r="BC22">
-        <v>0.98843991010136767</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD22">
-        <v>211.93498147492642</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9498,16 +9498,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99484635552608569</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB23">
-        <v>94.483482021761333</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9534,16 +9534,16 @@
         <v>467</v>
       </c>
       <c r="AM23" t="s">
+        <v>550</v>
+      </c>
+      <c r="AN23" t="s">
         <v>551</v>
       </c>
-      <c r="AN23" t="s">
-        <v>552</v>
-      </c>
       <c r="AO23">
-        <v>0.99505112170813059</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP23">
-        <v>90.729435350939028</v>
+        <v>37.384485603890518</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9570,16 +9570,16 @@
         <v>633</v>
       </c>
       <c r="BA23" t="s">
+        <v>669</v>
+      </c>
+      <c r="BB23" t="s">
         <v>670</v>
       </c>
-      <c r="BB23" t="s">
-        <v>671</v>
-      </c>
       <c r="BC23">
-        <v>0.991900752046595</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD23">
-        <v>148.48621247909063</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9644,16 +9644,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.98298990306503153</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB24">
-        <v>311.85177714108931</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9680,16 +9680,16 @@
         <v>469</v>
       </c>
       <c r="AM24" t="s">
+        <v>552</v>
+      </c>
+      <c r="AN24" t="s">
         <v>553</v>
       </c>
-      <c r="AN24" t="s">
-        <v>554</v>
-      </c>
       <c r="AO24">
-        <v>0.99606892759117205</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP24">
-        <v>72.069660828511601</v>
+        <v>83.095996952896456</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9716,16 +9716,16 @@
         <v>635</v>
       </c>
       <c r="BA24" t="s">
+        <v>671</v>
+      </c>
+      <c r="BB24" t="s">
         <v>672</v>
       </c>
-      <c r="BB24" t="s">
-        <v>569</v>
-      </c>
       <c r="BC24">
-        <v>0.99581145929743231</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD24">
-        <v>76.789912880408167</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9790,16 +9790,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99495781957805363</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB25">
-        <v>92.439974402351027</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9826,16 +9826,16 @@
         <v>471</v>
       </c>
       <c r="AM25" t="s">
+        <v>554</v>
+      </c>
+      <c r="AN25" t="s">
         <v>555</v>
       </c>
-      <c r="AN25" t="s">
-        <v>556</v>
-      </c>
       <c r="AO25">
-        <v>0.99511753128449787</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP25">
-        <v>89.511926450871471</v>
+        <v>59.260154763351615</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9868,10 +9868,10 @@
         <v>674</v>
       </c>
       <c r="BC25">
-        <v>0.99429876975975018</v>
+        <v>0.98843991010136767</v>
       </c>
       <c r="BD25">
-        <v>104.52255440457925</v>
+        <v>211.93498147492642</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9936,16 +9936,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99564550658027606</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB26">
-        <v>79.832379361605149</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9972,16 +9972,16 @@
         <v>473</v>
       </c>
       <c r="AM26" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AN26" t="s">
-        <v>558</v>
+        <v>417</v>
       </c>
       <c r="AO26">
-        <v>0.9945106241527748</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP26">
-        <v>100.63855719912947</v>
+        <v>73.443263495810669</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10014,10 +10014,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.98743040674179927</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD26">
-        <v>230.44254306701379</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10082,16 +10082,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99635918407512603</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB27">
-        <v>66.748291956023195</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10118,16 +10118,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AN27" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="AO27">
-        <v>0.9915796289555876</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP27">
-        <v>154.37346914756148</v>
+        <v>38.251429847691753</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10157,13 +10157,13 @@
         <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>430</v>
+        <v>564</v>
       </c>
       <c r="BC27">
-        <v>0.98830355217046739</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD27">
-        <v>214.43487687476414</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10228,16 +10228,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99305283137490208</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB28">
-        <v>127.36475812679497</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10264,16 +10264,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AN28" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AO28">
-        <v>0.99394383035998857</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP28">
-        <v>111.02977673354209</v>
+        <v>88.42284494294006</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10306,10 +10306,10 @@
         <v>679</v>
       </c>
       <c r="BC28">
-        <v>0.99447517161328947</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD28">
-        <v>101.28852042302684</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10374,16 +10374,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99615584710269711</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB29">
-        <v>70.476136450553028</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10410,16 +10410,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AN29" t="s">
-        <v>428</v>
+        <v>562</v>
       </c>
       <c r="AO29">
-        <v>0.99599400380931946</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP29">
-        <v>73.443263495810669</v>
+        <v>29.627234098515917</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10452,10 +10452,10 @@
         <v>681</v>
       </c>
       <c r="BC29">
-        <v>0.99481516601444531</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD29">
-        <v>95.055289735168813</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10520,16 +10520,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99599518539997189</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB30">
-        <v>73.421601000514329</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10556,16 +10556,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
+        <v>563</v>
+      </c>
+      <c r="AN30" t="s">
         <v>564</v>
       </c>
-      <c r="AN30" t="s">
-        <v>565</v>
-      </c>
       <c r="AO30">
-        <v>0.99791355837194406</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP30">
-        <v>38.251429847691753</v>
+        <v>97.492467996683757</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10598,10 +10598,10 @@
         <v>683</v>
       </c>
       <c r="BC30">
-        <v>0.99501631001524238</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD30">
-        <v>91.367649720556983</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10666,16 +10666,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99567500995545699</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB31">
-        <v>79.29148414995565</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10702,16 +10702,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
+        <v>565</v>
+      </c>
+      <c r="AN31" t="s">
         <v>566</v>
       </c>
-      <c r="AN31" t="s">
-        <v>567</v>
-      </c>
       <c r="AO31">
-        <v>0.99578710491059208</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP31">
-        <v>77.236409972479407</v>
+        <v>110.17470964763046</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10776,16 +10776,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99519943077301054</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB32">
-        <v>88.010435828140345</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10812,16 +10812,16 @@
         <v>485</v>
       </c>
       <c r="AM32" t="s">
+        <v>567</v>
+      </c>
+      <c r="AN32" t="s">
         <v>568</v>
       </c>
-      <c r="AN32" t="s">
-        <v>569</v>
-      </c>
       <c r="AO32">
-        <v>0.99468222901836267</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP32">
-        <v>97.492467996683757</v>
+        <v>64.84977570462992</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10886,16 +10886,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99464845307754257</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB33">
-        <v>98.111693578387175</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10922,16 +10922,16 @@
         <v>487</v>
       </c>
       <c r="AM33" t="s">
+        <v>569</v>
+      </c>
+      <c r="AN33" t="s">
         <v>570</v>
       </c>
-      <c r="AN33" t="s">
-        <v>571</v>
-      </c>
       <c r="AO33">
-        <v>0.99399047038285648</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP33">
-        <v>110.17470964763046</v>
+        <v>90.729435350939028</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10996,16 +10996,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99446824002516876</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB34">
-        <v>101.41559953857198</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11032,16 +11032,16 @@
         <v>489</v>
       </c>
       <c r="AM34" t="s">
+        <v>571</v>
+      </c>
+      <c r="AN34" t="s">
         <v>572</v>
       </c>
-      <c r="AN34" t="s">
-        <v>573</v>
-      </c>
       <c r="AO34">
-        <v>0.99646273950702013</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP34">
-        <v>64.84977570462992</v>
+        <v>240.53953099643502</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11106,16 +11106,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>279</v>
+        <v>303</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99398571695284077</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB35">
-        <v>110.2618558645854</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11142,16 +11142,16 @@
         <v>491</v>
       </c>
       <c r="AM35" t="s">
+        <v>573</v>
+      </c>
+      <c r="AN35" t="s">
         <v>574</v>
       </c>
-      <c r="AN35" t="s">
-        <v>575</v>
-      </c>
       <c r="AO35">
-        <v>0.99504825389388352</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP35">
-        <v>90.782011945468795</v>
+        <v>104.26406003195649</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11216,16 +11216,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.99726845868655478</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB36">
-        <v>50.078257413162468</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11252,16 +11252,16 @@
         <v>493</v>
       </c>
       <c r="AM36" t="s">
+        <v>575</v>
+      </c>
+      <c r="AN36" t="s">
         <v>576</v>
       </c>
-      <c r="AN36" t="s">
-        <v>577</v>
-      </c>
       <c r="AO36">
-        <v>0.99546749107529653</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP36">
-        <v>83.095996952896456</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11326,16 +11326,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99021255380204343</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB37">
-        <v>179.43651362920434</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11362,16 +11362,16 @@
         <v>495</v>
       </c>
       <c r="AM37" t="s">
+        <v>577</v>
+      </c>
+      <c r="AN37" t="s">
         <v>578</v>
       </c>
-      <c r="AN37" t="s">
-        <v>579</v>
-      </c>
       <c r="AO37">
-        <v>0.99676762792199902</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP37">
-        <v>59.260154763351615</v>
+        <v>31.154905747485419</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11436,16 +11436,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.99766238113026029</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB38">
-        <v>42.856345945228725</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11472,16 +11472,16 @@
         <v>497</v>
       </c>
       <c r="AM38" t="s">
+        <v>579</v>
+      </c>
+      <c r="AN38" t="s">
         <v>580</v>
       </c>
-      <c r="AN38" t="s">
-        <v>581</v>
-      </c>
       <c r="AO38">
-        <v>0.99587491663731742</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP38">
-        <v>75.626528315847352</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11546,16 +11546,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.99492995157662933</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB39">
-        <v>92.95088776179594</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11582,16 +11582,16 @@
         <v>499</v>
       </c>
       <c r="AM39" t="s">
+        <v>581</v>
+      </c>
+      <c r="AN39" t="s">
         <v>582</v>
       </c>
-      <c r="AN39" t="s">
-        <v>583</v>
-      </c>
       <c r="AO39">
-        <v>0.99572967547870339</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP39">
-        <v>78.289282890438841</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11656,16 +11656,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99197366299435197</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB40">
-        <v>147.14951177021345</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11692,16 +11692,16 @@
         <v>501</v>
       </c>
       <c r="AM40" t="s">
+        <v>583</v>
+      </c>
+      <c r="AN40" t="s">
         <v>584</v>
       </c>
-      <c r="AN40" t="s">
-        <v>585</v>
-      </c>
       <c r="AO40">
-        <v>0.99604689649306255</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP40">
-        <v>72.473564293852363</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11766,16 +11766,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99590738174919524</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB41">
-        <v>75.031334598088264</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11802,16 +11802,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
+        <v>585</v>
+      </c>
+      <c r="AN41" t="s">
         <v>586</v>
       </c>
-      <c r="AN41" t="s">
-        <v>587</v>
-      </c>
       <c r="AO41">
-        <v>0.99164055829901554</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP41">
-        <v>153.25643118471478</v>
+        <v>90.782011945468795</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11876,16 +11876,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99299045119957896</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB42">
-        <v>128.50839467438524</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11912,16 +11912,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
+        <v>587</v>
+      </c>
+      <c r="AN42" t="s">
         <v>588</v>
       </c>
-      <c r="AN42" t="s">
-        <v>589</v>
-      </c>
       <c r="AO42">
-        <v>0.99514523900053742</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP42">
-        <v>89.003951656813172</v>
+        <v>72.069660828511601</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11986,16 +11986,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99456731509164431</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB43">
-        <v>99.599223319854588</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12022,16 +12022,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
+        <v>589</v>
+      </c>
+      <c r="AN43" t="s">
         <v>590</v>
       </c>
-      <c r="AN43" t="s">
-        <v>591</v>
-      </c>
       <c r="AO43">
-        <v>0.99178008656222316</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP43">
-        <v>150.6984130259078</v>
+        <v>89.511926450871471</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12096,16 +12096,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99466941924265306</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB44">
-        <v>97.727313884694652</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12132,16 +12132,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
+        <v>591</v>
+      </c>
+      <c r="AN44" t="s">
         <v>592</v>
       </c>
-      <c r="AN44" t="s">
-        <v>593</v>
-      </c>
       <c r="AO44">
-        <v>0.99572114955867075</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP44">
-        <v>78.445591424369994</v>
+        <v>100.63855719912947</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12206,16 +12206,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>303</v>
+        <v>269</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99527761530085967</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB45">
-        <v>86.577052817573119</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12242,16 +12242,16 @@
         <v>511</v>
       </c>
       <c r="AM45" t="s">
+        <v>593</v>
+      </c>
+      <c r="AN45" t="s">
         <v>594</v>
       </c>
-      <c r="AN45" t="s">
-        <v>595</v>
-      </c>
       <c r="AO45">
-        <v>0.99517693573038513</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP45">
-        <v>88.42284494294006</v>
+        <v>154.37346914756148</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12316,16 +12316,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.9951066982538278</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB46">
-        <v>89.710532013157362</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12352,16 +12352,16 @@
         <v>513</v>
       </c>
       <c r="AM46" t="s">
+        <v>595</v>
+      </c>
+      <c r="AN46" t="s">
         <v>596</v>
       </c>
-      <c r="AN46" t="s">
-        <v>597</v>
-      </c>
       <c r="AO46">
-        <v>0.99838396904917182</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP46">
-        <v>29.627234098515917</v>
+        <v>111.02977673354209</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12426,16 +12426,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99681791473814529</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB47">
-        <v>58.33822980066963</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12462,16 +12462,16 @@
         <v>515</v>
       </c>
       <c r="AM47" t="s">
+        <v>597</v>
+      </c>
+      <c r="AN47" t="s">
         <v>598</v>
       </c>
-      <c r="AN47" t="s">
-        <v>599</v>
-      </c>
       <c r="AO47">
-        <v>0.99601677315501558</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP47">
-        <v>73.025825491381909</v>
+        <v>89.003951656813172</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12536,16 +12536,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.98958063849079669</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB48">
-        <v>191.02162766872783</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12572,16 +12572,16 @@
         <v>517</v>
       </c>
       <c r="AM48" t="s">
+        <v>599</v>
+      </c>
+      <c r="AN48" t="s">
         <v>600</v>
       </c>
-      <c r="AN48" t="s">
-        <v>601</v>
-      </c>
       <c r="AO48">
-        <v>0.99620690928326405</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP48">
-        <v>69.53999647349201</v>
+        <v>150.6984130259078</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12646,16 +12646,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99715332943801627</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB49">
-        <v>52.188960303034925</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12682,16 +12682,16 @@
         <v>519</v>
       </c>
       <c r="AM49" t="s">
+        <v>601</v>
+      </c>
+      <c r="AN49" t="s">
         <v>602</v>
       </c>
-      <c r="AN49" t="s">
-        <v>415</v>
-      </c>
       <c r="AO49">
-        <v>0.99495142174876894</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP49">
-        <v>92.557267939235231</v>
+        <v>78.445591424369994</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12756,16 +12756,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99341896335341162</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB50">
-        <v>120.65233852078616</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12798,10 +12798,10 @@
         <v>604</v>
       </c>
       <c r="AO50">
-        <v>0.99393947890433676</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP50">
-        <v>111.10955342049355</v>
+        <v>77.236409972479407</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12866,16 +12866,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99601318900739955</v>
+        <v>0.99446824002516876</v>
       </c>
       <c r="AB51">
-        <v>73.091534864341</v>
+        <v>101.41559953857198</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12908,10 +12908,10 @@
         <v>606</v>
       </c>
       <c r="AO51">
-        <v>0.99576662598769528</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP51">
-        <v>77.611856892252987</v>
+        <v>72.473564293852363</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12976,16 +12976,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99695083910621241</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB52">
-        <v>55.901283052772143</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13018,10 +13018,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99796084623978776</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP52">
-        <v>37.384485603890518</v>
+        <v>153.25643118471478</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13086,16 +13086,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99758018972146978</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB53">
-        <v>44.363188439721</v>
+        <v>73.421601000514329</v>
       </c>
     </row>
   </sheetData>
@@ -13104,7 +13104,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB81A15-E3DD-4417-96CD-FB5BEAB4993C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B87E366-61FA-415C-9F0F-2BF6A7932EA1}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13216,7 +13216,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13249,7 +13249,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>680</v>
+        <v>657</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13284,7 +13284,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="L12">
         <v>41.38517014727136</v>
@@ -13317,7 +13317,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13352,7 +13352,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13385,7 +13385,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13420,7 +13420,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>580</v>
+        <v>542</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13453,7 +13453,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>677</v>
+        <v>665</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13488,7 +13488,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>561</v>
+        <v>595</v>
       </c>
       <c r="L15">
         <v>13.570215224493221</v>
@@ -13521,7 +13521,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13556,7 +13556,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>555</v>
+        <v>589</v>
       </c>
       <c r="L16">
         <v>59.282276232111244</v>
@@ -13589,7 +13589,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13624,7 +13624,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>586</v>
+        <v>607</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13657,7 +13657,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13692,7 +13692,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>578</v>
+        <v>554</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13725,7 +13725,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13760,7 +13760,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>543</v>
+        <v>577</v>
       </c>
       <c r="L19">
         <v>15.766767829784982</v>
@@ -13793,7 +13793,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13828,7 +13828,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>547</v>
+        <v>581</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13861,7 +13861,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13896,7 +13896,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="L21">
         <v>11.016586435503244</v>
@@ -13929,7 +13929,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>678</v>
+        <v>666</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13964,7 +13964,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="L22">
         <v>6.1733535033999489</v>
@@ -13997,7 +13997,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14032,7 +14032,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>594</v>
+        <v>559</v>
       </c>
       <c r="L23">
         <v>4.8541340927283274</v>
@@ -14065,7 +14065,7 @@
         <v>792</v>
       </c>
       <c r="X23" t="s">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="Y23">
         <v>36.704999999999998</v>
@@ -14100,7 +14100,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>559</v>
+        <v>593</v>
       </c>
       <c r="L24">
         <v>13.114783900591691</v>
@@ -14133,7 +14133,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>675</v>
+        <v>680</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14168,7 +14168,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>549</v>
+        <v>583</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14201,7 +14201,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14269,7 +14269,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>673</v>
+        <v>678</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14304,7 +14304,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14337,7 +14337,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>649</v>
+        <v>668</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14372,7 +14372,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>600</v>
+        <v>539</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14405,7 +14405,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14440,7 +14440,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>545</v>
+        <v>579</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14473,7 +14473,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>666</v>
+        <v>682</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14508,7 +14508,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>602</v>
+        <v>541</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14541,7 +14541,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14611,7 +14611,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>607</v>
+        <v>550</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14646,7 +14646,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14681,7 +14681,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>605</v>
+        <v>548</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14716,7 +14716,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>596</v>
+        <v>561</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14751,7 +14751,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14786,7 +14786,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14821,7 +14821,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14926,7 +14926,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>582</v>
+        <v>544</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14996,7 +14996,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15031,7 +15031,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>557</v>
+        <v>591</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15066,7 +15066,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>598</v>
+        <v>537</v>
       </c>
       <c r="L45">
         <v>10.919135648131764</v>
@@ -15101,7 +15101,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>584</v>
+        <v>605</v>
       </c>
       <c r="L46">
         <v>33.912640160809843</v>
@@ -15136,7 +15136,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15171,7 +15171,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15206,7 +15206,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>539</v>
+        <v>573</v>
       </c>
       <c r="L49">
         <v>62.791395577971592</v>
@@ -15241,7 +15241,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>603</v>
+        <v>546</v>
       </c>
       <c r="L50">
         <v>37.678782480143312</v>
@@ -15276,7 +15276,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>553</v>
+        <v>587</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15311,7 +15311,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>537</v>
+        <v>571</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15326,7 +15326,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2500E93-9FE5-4090-A24E-31E585E7B159}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC06812-3E21-46B1-805D-E93591A303C9}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -17143,7 +17143,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02B7C72-E53E-47DA-83C9-D268A267C3C4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FDF600-58CA-46FD-851C-C97F038B9D2B}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3CE390B-790C-4CDF-B570-65A2E7EACAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979904E6-EF16-40D5-89B9-92C6506E9657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2963" uniqueCount="882">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2966" uniqueCount="886">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -1060,180 +1060,240 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_ZAF_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_ZAF_020</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 20</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_040</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 40</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_008</t>
   </si>
   <si>
@@ -1252,54 +1312,6 @@
     <t>connecting solar to buses in cluster 25</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_ZAF_014</t>
   </si>
   <si>
@@ -1312,108 +1324,126 @@
     <t>connecting solar to buses in cluster 9</t>
   </si>
   <si>
-    <t>distr_solelc_spv_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_ZAF_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
+  </si>
+  <si>
+    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
     <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF</t>
   </si>
   <si>
     <t>e_w685294883-400_ZAF,e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w1146878078-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF,e_w586032034-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_ZA28-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA3-400_ZAF,e_w182408147-400_ZAF,e_ZA2-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF,e_w142414070-765_ZAF,e_w181366662-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193977981-765_ZAF,e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_ZA28-765_ZAF,e_w92348290-765_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w631673098-400_ZAF,e_w105759402-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w238322344-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167590549-400_ZAF,e_w89173873-400_ZAF,e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167648085-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w219596295-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w230551819-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA31-400_ZAF,e_ZA30-400_ZAF,e_w107391770-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_ZA39-400_ZAF,e_w125769921-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102682082-400_ZAF,e_w177800991-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF,e_w105759402-400_ZAF,e_ZA31-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w208749745-400_ZAF,e_ZA7-400_ZAF,e_w156418705-400_ZAF</t>
-  </si>
-  <si>
     <t>e_ZA25-400_ZAF</t>
   </si>
   <si>
@@ -1423,40 +1453,130 @@
     <t>e_w208749745-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF</t>
   </si>
   <si>
-    <t>e_ZA23-400_ZAF,e_w260486370-400_ZAF,e_w156418705-400_ZAF,e_ZA11-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_w125754107-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w586032034-400_ZAF,e_w934819484-400_ZAF,e_w586032034-765_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w142414070-765_ZAF,e_ZA28-765_ZAF,e_w496302277-400_ZAF,e_w92348290-765_ZAF,e_w181366662-765_ZAF</t>
-  </si>
-  <si>
-    <t>e_w167540668-400_ZAF,e_w103079596-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w87434264-400_ZAF,e_ZA24-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w359805008-400_ZAF,e_w184581460-400_ZAF,e_ZA14-400_ZAF,e_w170672051-400_ZAF,e_w1146812331-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w131625968-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
     <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF</t>
   </si>
   <si>
     <t>e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF,e_w200757306-400_ZAF</t>
   </si>
   <si>
-    <t>e_w107937167-400_ZAF,e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_ZA24-400_ZAF,e_w105759402-400_ZAF,e_w98231311-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w178968761-400_ZAF</t>
+    <t>distr_wonelc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_032</t>
@@ -1489,22 +1609,46 @@
     <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
+    <t>distr_wonelc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_004</t>
@@ -1519,34 +1663,40 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
+    <t>distr_wonelc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wonelc_won_ZAF_001</t>
@@ -1561,154 +1711,121 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
+    <t>elc_won_ZAF_037</t>
+  </si>
+  <si>
+    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_026</t>
+  </si>
+  <si>
+    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_035</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_018</t>
+  </si>
+  <si>
+    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_020</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_040</t>
+  </si>
+  <si>
+    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_024</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_022</t>
+  </si>
+  <si>
+    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_025</t>
+  </si>
+  <si>
+    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_027</t>
+  </si>
+  <si>
+    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_003</t>
+  </si>
+  <si>
+    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_033</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_041</t>
+  </si>
+  <si>
+    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_006</t>
+  </si>
+  <si>
+    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_034</t>
+  </si>
+  <si>
+    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_014</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_005</t>
+  </si>
+  <si>
+    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_032</t>
@@ -1741,19 +1858,46 @@
     <t>e_ZA11-400_ZAF,e_w156418705-400_ZAF,e_ZA7-400_ZAF,e_w208749745-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_035</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w193978748-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w107431792-400_ZAF,e_w102682082-400_ZAF,e_w545652232-400_ZAF,e_ZA43-400_ZAF,e_w182042518-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_018</t>
-  </si>
-  <si>
-    <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_020</t>
+    <t>elc_won_ZAF_042</t>
+  </si>
+  <si>
+    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_039</t>
+  </si>
+  <si>
+    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_017</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_009</t>
+  </si>
+  <si>
+    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_010</t>
+  </si>
+  <si>
+    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_015</t>
+  </si>
+  <si>
+    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_004</t>
@@ -1768,34 +1912,40 @@
     <t>e_w496302277-400_ZAF,e_w92348290-765_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_040</t>
-  </si>
-  <si>
-    <t>e_w183402339-400_ZAF,e_ZA38-765_ZAF,e_w142414070-400_ZAF,e_w142414070-765_ZAF,e_w107937167-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_024</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w230551819-400_ZAF,e_ZA3-400_ZAF,e_w182408147-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_022</t>
-  </si>
-  <si>
-    <t>e_w1146812331-400_ZAF,e_ZA4-400_ZAF,e_w184560833-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_026</t>
-  </si>
-  <si>
-    <t>e_w184581460-400_ZAF,e_w230551819-400_ZAF,e_ZA2-400_ZAF,e_ZA14-400_ZAF,e_w685294883-400_ZAF,e_w170672051-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_w105759402-400_ZAF,e_ZA26-400_ZAF,e_w179136373-400_ZAF,e_w104080393-400_ZAF,e_w213181313-400_ZAF</t>
+    <t>elc_won_ZAF_023</t>
+  </si>
+  <si>
+    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_038</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_002</t>
+  </si>
+  <si>
+    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_028</t>
+  </si>
+  <si>
+    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_036</t>
+  </si>
+  <si>
+    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_won_ZAF_007</t>
+  </si>
+  <si>
+    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
   </si>
   <si>
     <t>elc_won_ZAF_001</t>
@@ -1807,154 +1957,22 @@
     <t>e_ZA29-400_ZAF,e_ZA26-400_ZAF,e_ZA30-400_ZAF,e_w167648085-400_ZAF,e_w183759046-400_ZAF,e_w104080393-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
   </si>
   <si>
-    <t>elc_won_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_w934819484-400_ZAF,e_w169789536-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_025</t>
-  </si>
-  <si>
-    <t>e_w693869805-400_ZAF,e_w87404898-400_ZAF,e_w184201271-400_ZAF,e_w230551819-400_ZAF,e_w359805008-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_038</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_002</t>
-  </si>
-  <si>
-    <t>e_w89173873-400_ZAF,e_w89637370-400_ZAF,e_w142414070-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_028</t>
-  </si>
-  <si>
-    <t>e_w496302277-400_ZAF,e_w103079596-400_ZAF,e_w200223220-400_ZAF,e_w167540668-400_ZAF,e_w693869805-400_ZAF,e_w184201271-400_ZAF,e_w87434264-400_ZAF,e_w105811523-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_023</t>
-  </si>
-  <si>
-    <t>e_ZA2-400_ZAF,e_w685294883-400_ZAF,e_ZA1-400_ZAF,e_w208749745-400_ZAF,e_w184552955-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_042</t>
-  </si>
-  <si>
-    <t>e_ZA25-400_ZAF,e_w663042845-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_039</t>
-  </si>
-  <si>
-    <t>e_w125754107-400_ZAF,e_w125769921-400_ZAF,e_ZA39-400_ZAF,e_w167590549-400_ZAF,e_w183402339-400_ZAF,e_w193977981-765_ZAF,e_ZA38-765_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_017</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_009</t>
-  </si>
-  <si>
-    <t>e_w98231311-400_ZAF,e_ZA14-400_ZAF,e_w178968761-400_ZAF,e_w179140081-400_ZAF,e_w185497473-400_ZAF,e_w179136373-765_ZAF,e_w209365700-400_ZAF,e_w209976655-400_ZAF,e_ZA20-400_ZAF,e_w238322344-400_ZAF,e_w260486370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w207991752-400_ZAF,e_w176362710-400_ZAF,e_ZA33-400_ZAF,e_ZA36-400_ZAF,e_w107391770-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_010</t>
-  </si>
-  <si>
-    <t>e_ZA31-400_ZAF,e_w181284049-400_ZAF,e_w167648085-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_015</t>
-  </si>
-  <si>
-    <t>e_w219596295-400_ZAF,e_w183757901-400_ZAF,e_ZA23-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_037</t>
-  </si>
-  <si>
-    <t>e_w193978748-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_041</t>
-  </si>
-  <si>
-    <t>e_w162871098-400_ZAF,e_ZA25-400_ZAF,e_w125769921-400_ZAF,e_w663042845-400_ZAF,e_w663042849-400_ZAF,e_w183402339-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_006</t>
-  </si>
-  <si>
-    <t>e_w586032034-765_ZAF,e_ZA39-400_ZAF,e_w934819484-400_ZAF,e_w167590549-400_ZAF,e_w89173873-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_034</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF,e_w183402339-400_ZAF,e_w496302277-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_014</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w167590549-400_ZAF,e_w90454383-400_ZAF,e_w169647963-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_005</t>
-  </si>
-  <si>
-    <t>e_w90454383-400_ZAF,e_w89173873-400_ZAF,e_w89637370-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_003</t>
-  </si>
-  <si>
-    <t>e_w177800991-400_ZAF,e_ZA39-400_ZAF,e_w193978748-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_033</t>
-  </si>
-  <si>
-    <t>e_w200757306-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_w169647963-400_ZAF,e_w89637370-400_ZAF,e_r17287657-400_ZAF,e_w107937167-400_ZAF,e_w631673098-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_027</t>
-  </si>
-  <si>
-    <t>e_w102925909-400_ZAF,e_w200223220-400_ZAF,e_w167540668-765_ZAF,e_w178240552-400_ZAF,e_w105759402-400_ZAF,e_ZA24-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_036</t>
-  </si>
-  <si>
-    <t>e_w193465369-400_ZAF,e_w162871098-400_ZAF,e_w125754107-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_won_ZAF_007</t>
-  </si>
-  <si>
-    <t>e_w631673098-400_ZAF,e_w207991752-400_ZAF,e_w127585817-400_ZAF</t>
+    <t>distr_wofelc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_006</t>
@@ -1981,18 +1999,30 @@
     <t>connecting wind offshore to buses in cluster 10</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ZAF_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_ZAF_015</t>
   </si>
   <si>
@@ -2011,22 +2041,10 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
+    <t>distr_wofelc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_ZAF_003</t>
@@ -2035,18 +2053,6 @@
     <t>connecting wind offshore to buses in cluster 3</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_ZAF_002</t>
   </si>
   <si>
@@ -2071,10 +2077,19 @@
     <t>connecting wind offshore to buses in cluster 14</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
+    <t>elc_wof_ZAF_012</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_019</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_017</t>
   </si>
   <si>
     <t>elc_wof_ZAF_006</t>
@@ -2095,18 +2110,27 @@
     <t>e_w131625968-400_ZAF,e_ZA23-400_ZAF,e_ZA11-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_012</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF,e_w107391770-400_ZAF,e_w120941269-400_ZAF,e_w131625968-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_wof_ZAF_001</t>
   </si>
   <si>
     <t>e_w107431792-400_ZAF,e_w836844162-400_ZAF,e_w62218063-400_ZAF</t>
   </si>
   <si>
+    <t>elc_wof_ZAF_004</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_011</t>
+  </si>
+  <si>
+    <t>e_w131625968-400_ZAF</t>
+  </si>
+  <si>
+    <t>elc_wof_ZAF_008</t>
+  </si>
+  <si>
+    <t>e_ZA36-400_ZAF</t>
+  </si>
+  <si>
     <t>elc_wof_ZAF_015</t>
   </si>
   <si>
@@ -2125,16 +2149,10 @@
     <t>e_r17287657-400_ZAF,e_w631673098-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_004</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_011</t>
-  </si>
-  <si>
-    <t>e_w131625968-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_017</t>
+    <t>elc_wof_ZAF_013</t>
+  </si>
+  <si>
+    <t>e_w169789536-400_ZAF</t>
   </si>
   <si>
     <t>elc_wof_ZAF_003</t>
@@ -2143,18 +2161,6 @@
     <t>e_w193978748-400_ZAF,e_w193465369-400_ZAF,e_w107431792-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_008</t>
-  </si>
-  <si>
-    <t>e_ZA36-400_ZAF</t>
-  </si>
-  <si>
-    <t>elc_wof_ZAF_013</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF</t>
-  </si>
-  <si>
     <t>elc_wof_ZAF_002</t>
   </si>
   <si>
@@ -2176,12 +2182,6 @@
     <t>e_w102682082-400_ZAF,e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
   </si>
   <si>
-    <t>elc_wof_ZAF_019</t>
-  </si>
-  <si>
-    <t>e_w169789536-400_ZAF,e_w934819484-400_ZAF</t>
-  </si>
-  <si>
     <t>e_won_ZAF_001</t>
   </si>
   <si>
@@ -2774,6 +2774,18 @@
   </si>
   <si>
     <t>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</t>
+  </si>
+  <si>
+    <t>pcg</t>
+  </si>
+  <si>
+    <t>NRGO</t>
+  </si>
+  <si>
+    <t>*FLO_FUNC</t>
+  </si>
+  <si>
+    <t>*NCAP_AFC</t>
   </si>
 </sst>
 </file>
@@ -4717,7 +4729,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD6D8AA-F8A9-4BBE-94C7-C767CA3BCC03}">
-  <dimension ref="B2:W61"/>
+  <dimension ref="B2:X61"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="18.86328125" bestFit="1" customWidth="1"/>
@@ -4729,8 +4741,8 @@
     <col min="8" max="8" width="10.265625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="19.265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.73046875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="9.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="7.59765625" bestFit="1" customWidth="1"/>
@@ -4742,7 +4754,7 @@
     <col min="23" max="23" width="3.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23">
+    <row r="2" spans="2:24">
       <c r="B2" s="3" t="s">
         <v>23</v>
       </c>
@@ -4754,7 +4766,7 @@
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="2:23">
+    <row r="3" spans="2:24">
       <c r="B3" s="3" t="s">
         <v>38</v>
       </c>
@@ -4780,7 +4792,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="2:23">
+    <row r="4" spans="2:24">
       <c r="B4" s="3" t="s">
         <v>45</v>
       </c>
@@ -4800,7 +4812,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="2:23">
+    <row r="5" spans="2:24">
       <c r="C5" s="3" t="s">
         <v>49</v>
       </c>
@@ -4815,7 +4827,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:23">
+    <row r="8" spans="2:24">
       <c r="B8" s="5" t="s">
         <v>0</v>
       </c>
@@ -4825,14 +4837,13 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="6"/>
+      <c r="N8" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="O8" s="6"/>
       <c r="P8" s="6"/>
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
@@ -4841,8 +4852,9 @@
       <c r="U8" s="6"/>
       <c r="V8" s="6"/>
       <c r="W8" s="6"/>
-    </row>
-    <row r="9" spans="2:23">
+      <c r="X8" s="6"/>
+    </row>
+    <row r="9" spans="2:24">
       <c r="B9" s="5" t="s">
         <v>6</v>
       </c>
@@ -4861,61 +4873,63 @@
       <c r="G9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6" t="s">
+      <c r="H9" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="J9" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="K9" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="L9" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="M9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="7" t="s">
+      <c r="N9" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="6">
-        <f>J35</f>
+      <c r="O9" s="6">
+        <f t="shared" ref="O9:U9" si="0">J35</f>
         <v>2020</v>
-      </c>
-      <c r="O9" s="6">
-        <f t="shared" ref="O9:T9" si="0">K35</f>
-        <v>2025</v>
       </c>
       <c r="P9" s="6">
         <f t="shared" si="0"/>
-        <v>2030</v>
+        <v>2025</v>
       </c>
       <c r="Q9" s="6">
         <f t="shared" si="0"/>
-        <v>2035</v>
+        <v>2030</v>
       </c>
       <c r="R9" s="6">
         <f t="shared" si="0"/>
-        <v>2040</v>
+        <v>2035</v>
       </c>
       <c r="S9" s="6">
         <f t="shared" si="0"/>
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="T9" s="6">
         <f t="shared" si="0"/>
+        <v>2045</v>
+      </c>
+      <c r="U9" s="6">
+        <f t="shared" si="0"/>
         <v>2050</v>
       </c>
-      <c r="U9" s="6" t="s">
+      <c r="V9" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="V9" s="6" t="s">
+      <c r="W9" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="W9" t="s">
+      <c r="X9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="2:23">
+    <row r="10" spans="2:24">
       <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
@@ -4934,44 +4948,46 @@
       <c r="G10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6" t="s">
+      <c r="H10" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="K10" s="3" t="s">
+      <c r="K10" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="9">
-        <f>1/N17</f>
+      <c r="O10" s="9">
+        <f>1/O17</f>
         <v>1.1764705882352942</v>
       </c>
-      <c r="O10" s="9"/>
       <c r="P10" s="9"/>
       <c r="Q10" s="9"/>
       <c r="R10" s="9"/>
       <c r="S10" s="9"/>
       <c r="T10" s="9"/>
-      <c r="U10" s="6"/>
-      <c r="V10" s="5" t="str">
-        <f>K10</f>
+      <c r="U10" s="9"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="5" t="str">
+        <f>L10</f>
         <v>AuxStoOUT</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:23">
+    <row r="11" spans="2:24">
       <c r="B11" s="5"/>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>62</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -4986,38 +5002,37 @@
       <c r="G11" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6" t="s">
+      <c r="H11" s="6" t="s">
+        <v>883</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J11" s="6" t="s">
-        <v>65</v>
-      </c>
       <c r="K11" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="L11" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="M11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="N11" s="9">
+      <c r="O11" s="9">
         <f>4/24</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
-      <c r="U11" s="5" t="str">
-        <f>L11</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23">
+      <c r="U11" s="4"/>
+      <c r="V11" s="5"/>
+    </row>
+    <row r="12" spans="2:24">
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
       <c r="D12" s="5"/>
@@ -5025,32 +5040,32 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="6"/>
-      <c r="I12" s="6" t="s">
+      <c r="J12" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J12" s="6" t="s">
+      <c r="K12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="6"/>
-      <c r="M12" s="7" t="s">
+      <c r="M12" s="6"/>
+      <c r="N12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="N12" s="9">
+      <c r="O12" s="9">
         <v>1</v>
       </c>
-      <c r="O12" s="9"/>
       <c r="P12" s="9"/>
       <c r="Q12" s="9"/>
       <c r="R12" s="9"/>
       <c r="S12" s="9"/>
       <c r="T12" s="9"/>
-      <c r="U12" s="6"/>
+      <c r="U12" s="9"/>
       <c r="V12" s="6"/>
-    </row>
-    <row r="13" spans="2:23">
+      <c r="W12" s="6"/>
+    </row>
+    <row r="13" spans="2:24">
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
@@ -5058,352 +5073,349 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="6"/>
-      <c r="I13" s="6" t="s">
+      <c r="J13" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="K13" s="6"/>
       <c r="L13" s="6"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9">
-        <f>J40</f>
+      <c r="M13" s="6"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="9">
+        <f t="shared" ref="O13:U13" si="1">J40</f>
         <v>1363</v>
-      </c>
-      <c r="O13" s="9">
-        <f t="shared" ref="O13:T13" si="1">K40</f>
-        <v>956</v>
       </c>
       <c r="P13" s="9">
         <f t="shared" si="1"/>
-        <v>784</v>
+        <v>956</v>
       </c>
       <c r="Q13" s="9">
         <f t="shared" si="1"/>
-        <v>735</v>
+        <v>784</v>
       </c>
       <c r="R13" s="9">
         <f t="shared" si="1"/>
-        <v>686</v>
+        <v>735</v>
       </c>
       <c r="S13" s="9">
         <f t="shared" si="1"/>
-        <v>637</v>
+        <v>686</v>
       </c>
       <c r="T13" s="9">
         <f t="shared" si="1"/>
+        <v>637</v>
+      </c>
+      <c r="U13" s="9">
+        <f t="shared" si="1"/>
         <v>588</v>
       </c>
-      <c r="U13" s="6"/>
       <c r="V13" s="6"/>
-    </row>
-    <row r="14" spans="2:23">
-      <c r="I14" t="s">
+      <c r="W13" s="6"/>
+    </row>
+    <row r="14" spans="2:24">
+      <c r="J14" t="s">
         <v>62</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>68</v>
       </c>
-      <c r="N14" s="4">
-        <f>J44</f>
+      <c r="O14" s="4">
+        <f t="shared" ref="O14:U14" si="2">J44</f>
         <v>34</v>
-      </c>
-      <c r="O14" s="4">
-        <f t="shared" ref="O14:T14" si="2">K44</f>
-        <v>24</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Q14" s="4">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R14" s="4">
         <f t="shared" si="2"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S14" s="4">
         <f t="shared" si="2"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="T14" s="4">
         <f t="shared" si="2"/>
+        <v>16</v>
+      </c>
+      <c r="U14" s="4">
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:23">
-      <c r="I15" t="s">
+    <row r="15" spans="2:24">
+      <c r="J15" t="s">
         <v>62</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>69</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>18</v>
       </c>
-      <c r="N15" s="4">
+      <c r="O15" s="4">
         <v>1</v>
       </c>
-      <c r="O15" s="4"/>
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="4"/>
       <c r="T15" s="4"/>
-    </row>
-    <row r="16" spans="2:23">
-      <c r="I16" t="s">
+      <c r="U15" s="4"/>
+    </row>
+    <row r="16" spans="2:24">
+      <c r="J16" t="s">
         <v>62</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>70</v>
       </c>
-      <c r="N16" s="9">
+      <c r="O16" s="9">
         <v>31.536000000000001</v>
       </c>
-      <c r="O16" s="4"/>
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
-    </row>
-    <row r="17" spans="9:23">
-      <c r="I17" t="s">
+      <c r="U16" s="4"/>
+    </row>
+    <row r="17" spans="9:24">
+      <c r="J17" t="s">
         <v>62</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>71</v>
       </c>
-      <c r="N17" s="4">
+      <c r="O17" s="4">
         <v>0.85</v>
       </c>
-      <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
       <c r="S17" s="4"/>
       <c r="T17" s="4"/>
-    </row>
-    <row r="18" spans="9:23">
-      <c r="I18" t="s">
+      <c r="U17" s="4"/>
+    </row>
+    <row r="18" spans="9:24">
+      <c r="J18" t="s">
         <v>60</v>
       </c>
-      <c r="J18" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" s="3" t="s">
+      <c r="K18" s="6" t="s">
+        <v>884</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>18</v>
       </c>
-      <c r="N18" s="9">
-        <f>1/N25</f>
+      <c r="O18" s="9">
+        <f>1/O25</f>
         <v>1.1764705882352942</v>
       </c>
-      <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="6"/>
-      <c r="V18" s="5" t="str">
-        <f>K18</f>
+      <c r="U18" s="4"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="5" t="str">
+        <f>L18</f>
         <v>AuxStoOUT</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="9:23">
-      <c r="I19" t="s">
+    <row r="19" spans="9:24">
+      <c r="J19" t="s">
         <v>60</v>
       </c>
-      <c r="J19" t="s">
-        <v>65</v>
-      </c>
-      <c r="K19" t="s">
+      <c r="K19" s="6" t="s">
+        <v>885</v>
+      </c>
+      <c r="L19" t="s">
         <v>66</v>
       </c>
-      <c r="L19" t="s">
+      <c r="M19" t="s">
         <v>19</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>14</v>
       </c>
-      <c r="N19" s="4">
+      <c r="O19" s="4">
         <f>8/24</f>
         <v>0.33333333333333331</v>
       </c>
-      <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="5" t="str">
-        <f>L19</f>
-        <v>ELC</v>
-      </c>
-    </row>
-    <row r="20" spans="9:23">
-      <c r="I20" t="s">
+      <c r="U19" s="4"/>
+      <c r="V19" s="5"/>
+    </row>
+    <row r="20" spans="9:24">
+      <c r="J20" t="s">
         <v>60</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>65</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" t="s">
         <v>26</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>14</v>
       </c>
-      <c r="N20" s="4">
+      <c r="O20" s="4">
         <v>1</v>
       </c>
-      <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-    </row>
-    <row r="21" spans="9:23">
-      <c r="I21" t="s">
+      <c r="U20" s="4"/>
+    </row>
+    <row r="21" spans="9:24">
+      <c r="J21" t="s">
         <v>60</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>67</v>
       </c>
-      <c r="N21" s="4">
-        <f>J49</f>
+      <c r="O21" s="4">
+        <f t="shared" ref="O21:U21" si="3">J49</f>
         <v>2470</v>
-      </c>
-      <c r="O21" s="4">
-        <f t="shared" ref="O21:T21" si="3">K49</f>
-        <v>1714</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="3"/>
-        <v>1371</v>
+        <v>1714</v>
       </c>
       <c r="Q21" s="4">
         <f t="shared" si="3"/>
-        <v>1277</v>
+        <v>1371</v>
       </c>
       <c r="R21" s="4">
         <f t="shared" si="3"/>
-        <v>1183</v>
+        <v>1277</v>
       </c>
       <c r="S21" s="4">
         <f t="shared" si="3"/>
-        <v>1089</v>
+        <v>1183</v>
       </c>
       <c r="T21" s="4">
         <f t="shared" si="3"/>
+        <v>1089</v>
+      </c>
+      <c r="U21" s="4">
+        <f t="shared" si="3"/>
         <v>995</v>
       </c>
     </row>
-    <row r="22" spans="9:23">
-      <c r="I22" t="s">
+    <row r="22" spans="9:24">
+      <c r="J22" t="s">
         <v>60</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>68</v>
       </c>
-      <c r="N22" s="4">
-        <f>J53</f>
+      <c r="O22" s="4">
+        <f t="shared" ref="O22:U22" si="4">J53</f>
         <v>62</v>
-      </c>
-      <c r="O22" s="4">
-        <f t="shared" ref="O22:T22" si="4">K53</f>
-        <v>43</v>
       </c>
       <c r="P22" s="4">
         <f t="shared" si="4"/>
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="Q22" s="4">
         <f t="shared" si="4"/>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R22" s="4">
         <f t="shared" si="4"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="S22" s="4">
         <f t="shared" si="4"/>
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="T22" s="4">
         <f t="shared" si="4"/>
+        <v>27</v>
+      </c>
+      <c r="U22" s="4">
+        <f t="shared" si="4"/>
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="9:23">
-      <c r="I23" t="s">
+    <row r="23" spans="9:24">
+      <c r="J23" t="s">
         <v>60</v>
       </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>69</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>18</v>
       </c>
-      <c r="N23" s="4">
+      <c r="O23" s="4">
         <v>1</v>
       </c>
-      <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
-    </row>
-    <row r="24" spans="9:23">
-      <c r="I24" t="s">
+      <c r="U23" s="4"/>
+    </row>
+    <row r="24" spans="9:24">
+      <c r="J24" t="s">
         <v>60</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>70</v>
       </c>
-      <c r="N24" s="9">
+      <c r="O24" s="9">
         <v>31.536000000000001</v>
       </c>
-      <c r="O24" s="4"/>
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
-    </row>
-    <row r="25" spans="9:23">
-      <c r="I25" t="s">
+      <c r="U24" s="4"/>
+    </row>
+    <row r="25" spans="9:24">
+      <c r="J25" t="s">
         <v>60</v>
       </c>
-      <c r="J25" t="s">
+      <c r="K25" t="s">
         <v>71</v>
       </c>
-      <c r="N25" s="4">
+      <c r="O25" s="4">
         <v>0.85</v>
       </c>
-      <c r="O25" s="4"/>
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-    </row>
-    <row r="31" spans="9:23" ht="15.75">
+      <c r="U25" s="4"/>
+    </row>
+    <row r="31" spans="9:24" ht="15.75">
       <c r="I31" s="10" t="s">
         <v>72</v>
       </c>
@@ -5415,7 +5427,7 @@
       <c r="O31" s="11"/>
       <c r="P31" s="11"/>
     </row>
-    <row r="32" spans="9:23" ht="15.75">
+    <row r="32" spans="9:24" ht="15.75">
       <c r="I32" s="10" t="s">
         <v>73</v>
       </c>
@@ -7508,7 +7520,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1BBC17C-BBD7-421A-A5FB-C5FEEF0F665C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6349821-E822-47D3-B720-A5ADB53547C8}">
   <dimension ref="B9:BD53"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7746,16 +7758,16 @@
         <v>310</v>
       </c>
       <c r="Y11" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Z11" t="s">
         <v>400</v>
       </c>
       <c r="AA11">
-        <v>0.99331672850632224</v>
+        <v>0.99456731509164431</v>
       </c>
       <c r="AB11">
-        <v>122.52664405075954</v>
+        <v>99.599223319854588</v>
       </c>
       <c r="AD11" t="s">
         <v>309</v>
@@ -7788,10 +7800,10 @@
         <v>528</v>
       </c>
       <c r="AO11">
-        <v>0.98860885963065015</v>
+        <v>0.99504825389388352</v>
       </c>
       <c r="AP11">
-        <v>208.83757343808102</v>
+        <v>90.782011945468795</v>
       </c>
       <c r="AR11" t="s">
         <v>309</v>
@@ -7821,13 +7833,13 @@
         <v>649</v>
       </c>
       <c r="BB11" t="s">
-        <v>564</v>
+        <v>650</v>
       </c>
       <c r="BC11">
-        <v>0.99223220184557481</v>
+        <v>0.99501631001524238</v>
       </c>
       <c r="BD11">
-        <v>142.40963283112865</v>
+        <v>91.367649720556983</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7892,16 +7904,16 @@
         <v>314</v>
       </c>
       <c r="Y12" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="Z12" t="s">
         <v>401</v>
       </c>
       <c r="AA12">
-        <v>0.99698458324869177</v>
+        <v>0.99466941924265306</v>
       </c>
       <c r="AB12">
-        <v>55.282640440651299</v>
+        <v>97.727313884694652</v>
       </c>
       <c r="AD12" t="s">
         <v>309</v>
@@ -7934,10 +7946,10 @@
         <v>530</v>
       </c>
       <c r="AO12">
-        <v>0.99333075340694588</v>
+        <v>0.99546749107529653</v>
       </c>
       <c r="AP12">
-        <v>122.26952087265865</v>
+        <v>83.095996952896456</v>
       </c>
       <c r="AR12" t="s">
         <v>309</v>
@@ -7964,16 +7976,16 @@
         <v>611</v>
       </c>
       <c r="BA12" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="BB12" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="BC12">
-        <v>0.99462081464868646</v>
+        <v>0.99279657608325511</v>
       </c>
       <c r="BD12">
-        <v>98.618398107414592</v>
+        <v>132.06277180699064</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8038,16 +8050,16 @@
         <v>316</v>
       </c>
       <c r="Y13" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="Z13" t="s">
         <v>402</v>
       </c>
       <c r="AA13">
-        <v>0.99635918407512603</v>
+        <v>0.99527761530085967</v>
       </c>
       <c r="AB13">
-        <v>66.748291956023195</v>
+        <v>86.577052817573119</v>
       </c>
       <c r="AD13" t="s">
         <v>309</v>
@@ -8080,10 +8092,10 @@
         <v>532</v>
       </c>
       <c r="AO13">
-        <v>0.99201650479533909</v>
+        <v>0.99676762792199902</v>
       </c>
       <c r="AP13">
-        <v>146.36407875211563</v>
+        <v>59.260154763351615</v>
       </c>
       <c r="AR13" t="s">
         <v>309</v>
@@ -8110,16 +8122,16 @@
         <v>613</v>
       </c>
       <c r="BA13" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="BB13" t="s">
-        <v>576</v>
+        <v>426</v>
       </c>
       <c r="BC13">
-        <v>0.99507162964364948</v>
+        <v>0.99010219056094972</v>
       </c>
       <c r="BD13">
-        <v>90.353456533092867</v>
+        <v>181.45983971592244</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8184,16 +8196,16 @@
         <v>318</v>
       </c>
       <c r="Y14" t="s">
-        <v>268</v>
+        <v>297</v>
       </c>
       <c r="Z14" t="s">
         <v>403</v>
       </c>
       <c r="AA14">
-        <v>0.99305283137490208</v>
+        <v>0.9951066982538278</v>
       </c>
       <c r="AB14">
-        <v>127.36475812679497</v>
+        <v>89.710532013157362</v>
       </c>
       <c r="AD14" t="s">
         <v>309</v>
@@ -8226,10 +8238,10 @@
         <v>534</v>
       </c>
       <c r="AO14">
-        <v>0.9951764810877296</v>
+        <v>0.99601677315501558</v>
       </c>
       <c r="AP14">
-        <v>88.431180058290352</v>
+        <v>73.025825491381909</v>
       </c>
       <c r="AR14" t="s">
         <v>309</v>
@@ -8256,16 +8268,16 @@
         <v>615</v>
       </c>
       <c r="BA14" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="BB14" t="s">
-        <v>654</v>
+        <v>597</v>
       </c>
       <c r="BC14">
-        <v>0.98805842341846151</v>
+        <v>0.99223220184557481</v>
       </c>
       <c r="BD14">
-        <v>218.92890399487229</v>
+        <v>142.40963283112865</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8330,16 +8342,16 @@
         <v>320</v>
       </c>
       <c r="Y15" t="s">
-        <v>279</v>
+        <v>296</v>
       </c>
       <c r="Z15" t="s">
         <v>404</v>
       </c>
       <c r="AA15">
-        <v>0.99398571695284077</v>
+        <v>0.99681791473814529</v>
       </c>
       <c r="AB15">
-        <v>110.2618558645854</v>
+        <v>58.33822980066963</v>
       </c>
       <c r="AD15" t="s">
         <v>309</v>
@@ -8372,10 +8384,10 @@
         <v>536</v>
       </c>
       <c r="AO15">
-        <v>0.99247550518926964</v>
+        <v>0.99620690928326405</v>
       </c>
       <c r="AP15">
-        <v>137.94907153005732</v>
+        <v>69.53999647349201</v>
       </c>
       <c r="AR15" t="s">
         <v>309</v>
@@ -8408,10 +8420,10 @@
         <v>656</v>
       </c>
       <c r="BC15">
-        <v>0.99501631001524238</v>
+        <v>0.99462081464868646</v>
       </c>
       <c r="BD15">
-        <v>91.367649720556983</v>
+        <v>98.618398107414592</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8476,16 +8488,16 @@
         <v>322</v>
       </c>
       <c r="Y16" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="Z16" t="s">
         <v>405</v>
       </c>
       <c r="AA16">
-        <v>0.99726845868655478</v>
+        <v>0.98958063849079669</v>
       </c>
       <c r="AB16">
-        <v>50.078257413162468</v>
+        <v>191.02162766872783</v>
       </c>
       <c r="AD16" t="s">
         <v>309</v>
@@ -8515,13 +8527,13 @@
         <v>537</v>
       </c>
       <c r="AN16" t="s">
-        <v>538</v>
+        <v>440</v>
       </c>
       <c r="AO16">
-        <v>0.99601677315501558</v>
+        <v>0.99495142174876894</v>
       </c>
       <c r="AP16">
-        <v>73.025825491381909</v>
+        <v>92.557267939235231</v>
       </c>
       <c r="AR16" t="s">
         <v>309</v>
@@ -8551,13 +8563,13 @@
         <v>657</v>
       </c>
       <c r="BB16" t="s">
-        <v>658</v>
+        <v>581</v>
       </c>
       <c r="BC16">
-        <v>0.99481516601444531</v>
+        <v>0.99507162964364948</v>
       </c>
       <c r="BD16">
-        <v>95.055289735168813</v>
+        <v>90.353456533092867</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8622,16 +8634,16 @@
         <v>324</v>
       </c>
       <c r="Y17" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="Z17" t="s">
         <v>406</v>
       </c>
       <c r="AA17">
-        <v>0.99294071263677341</v>
+        <v>0.99590738174919524</v>
       </c>
       <c r="AB17">
-        <v>129.42026832582172</v>
+        <v>75.031334598088264</v>
       </c>
       <c r="AD17" t="s">
         <v>309</v>
@@ -8658,16 +8670,16 @@
         <v>455</v>
       </c>
       <c r="AM17" t="s">
+        <v>538</v>
+      </c>
+      <c r="AN17" t="s">
         <v>539</v>
       </c>
-      <c r="AN17" t="s">
-        <v>540</v>
-      </c>
       <c r="AO17">
-        <v>0.99620690928326405</v>
+        <v>0.99393947890433676</v>
       </c>
       <c r="AP17">
-        <v>69.53999647349201</v>
+        <v>111.10955342049355</v>
       </c>
       <c r="AR17" t="s">
         <v>309</v>
@@ -8694,16 +8706,16 @@
         <v>621</v>
       </c>
       <c r="BA17" t="s">
+        <v>658</v>
+      </c>
+      <c r="BB17" t="s">
         <v>659</v>
       </c>
-      <c r="BB17" t="s">
-        <v>660</v>
-      </c>
       <c r="BC17">
-        <v>0.99231435496704667</v>
+        <v>0.98805842341846151</v>
       </c>
       <c r="BD17">
-        <v>140.90349227081035</v>
+        <v>218.92890399487229</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8768,16 +8780,16 @@
         <v>326</v>
       </c>
       <c r="Y18" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Z18" t="s">
         <v>407</v>
       </c>
       <c r="AA18">
-        <v>0.99535442409010222</v>
+        <v>0.99299045119957896</v>
       </c>
       <c r="AB18">
-        <v>85.168891681458845</v>
+        <v>128.50839467438524</v>
       </c>
       <c r="AD18" t="s">
         <v>309</v>
@@ -8804,16 +8816,16 @@
         <v>457</v>
       </c>
       <c r="AM18" t="s">
+        <v>540</v>
+      </c>
+      <c r="AN18" t="s">
         <v>541</v>
       </c>
-      <c r="AN18" t="s">
-        <v>430</v>
-      </c>
       <c r="AO18">
-        <v>0.99495142174876894</v>
+        <v>0.99576662598769528</v>
       </c>
       <c r="AP18">
-        <v>92.557267939235231</v>
+        <v>77.611856892252987</v>
       </c>
       <c r="AR18" t="s">
         <v>309</v>
@@ -8840,16 +8852,16 @@
         <v>623</v>
       </c>
       <c r="BA18" t="s">
+        <v>660</v>
+      </c>
+      <c r="BB18" t="s">
         <v>661</v>
       </c>
-      <c r="BB18" t="s">
-        <v>662</v>
-      </c>
       <c r="BC18">
-        <v>0.99229811324031303</v>
+        <v>0.99481516601444531</v>
       </c>
       <c r="BD18">
-        <v>141.20125726092687</v>
+        <v>95.055289735168813</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8914,16 +8926,16 @@
         <v>328</v>
       </c>
       <c r="Y19" t="s">
-        <v>305</v>
+        <v>274</v>
       </c>
       <c r="Z19" t="s">
         <v>408</v>
       </c>
       <c r="AA19">
-        <v>0.99309463181702251</v>
+        <v>0.99715332943801627</v>
       </c>
       <c r="AB19">
-        <v>126.5984166879211</v>
+        <v>52.188960303034925</v>
       </c>
       <c r="AD19" t="s">
         <v>309</v>
@@ -8956,10 +8968,10 @@
         <v>543</v>
       </c>
       <c r="AO19">
-        <v>0.99587491663731742</v>
+        <v>0.99796084623978776</v>
       </c>
       <c r="AP19">
-        <v>75.626528315847352</v>
+        <v>37.384485603890518</v>
       </c>
       <c r="AR19" t="s">
         <v>309</v>
@@ -8986,16 +8998,16 @@
         <v>625</v>
       </c>
       <c r="BA19" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="BB19" t="s">
-        <v>664</v>
+        <v>406</v>
       </c>
       <c r="BC19">
-        <v>0.99582070241731502</v>
+        <v>0.98830355217046739</v>
       </c>
       <c r="BD19">
-        <v>76.620455682557321</v>
+        <v>214.43487687476414</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9060,16 +9072,16 @@
         <v>330</v>
       </c>
       <c r="Y20" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="Z20" t="s">
         <v>409</v>
       </c>
       <c r="AA20">
-        <v>0.99827081845920873</v>
+        <v>0.99341896335341162</v>
       </c>
       <c r="AB20">
-        <v>31.701661581174136</v>
+        <v>120.65233852078616</v>
       </c>
       <c r="AD20" t="s">
         <v>309</v>
@@ -9102,10 +9114,10 @@
         <v>545</v>
       </c>
       <c r="AO20">
-        <v>0.99572967547870339</v>
+        <v>0.99517693573038513</v>
       </c>
       <c r="AP20">
-        <v>78.289282890438841</v>
+        <v>88.42284494294006</v>
       </c>
       <c r="AR20" t="s">
         <v>309</v>
@@ -9132,16 +9144,16 @@
         <v>627</v>
       </c>
       <c r="BA20" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="BB20" t="s">
-        <v>420</v>
+        <v>664</v>
       </c>
       <c r="BC20">
-        <v>0.98830355217046739</v>
+        <v>0.99447517161328947</v>
       </c>
       <c r="BD20">
-        <v>214.43487687476414</v>
+        <v>101.28852042302684</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9206,16 +9218,16 @@
         <v>332</v>
       </c>
       <c r="Y21" t="s">
-        <v>274</v>
+        <v>300</v>
       </c>
       <c r="Z21" t="s">
         <v>410</v>
       </c>
       <c r="AA21">
-        <v>0.99715332943801627</v>
+        <v>0.99601318900739955</v>
       </c>
       <c r="AB21">
-        <v>52.188960303034925</v>
+        <v>73.091534864341</v>
       </c>
       <c r="AD21" t="s">
         <v>309</v>
@@ -9248,10 +9260,10 @@
         <v>547</v>
       </c>
       <c r="AO21">
-        <v>0.99393947890433676</v>
+        <v>0.99838396904917182</v>
       </c>
       <c r="AP21">
-        <v>111.10955342049355</v>
+        <v>29.627234098515917</v>
       </c>
       <c r="AR21" t="s">
         <v>309</v>
@@ -9278,16 +9290,16 @@
         <v>629</v>
       </c>
       <c r="BA21" t="s">
+        <v>665</v>
+      </c>
+      <c r="BB21" t="s">
         <v>666</v>
       </c>
-      <c r="BB21" t="s">
-        <v>667</v>
-      </c>
       <c r="BC21">
-        <v>0.99447517161328947</v>
+        <v>0.99672758029478525</v>
       </c>
       <c r="BD21">
-        <v>101.28852042302684</v>
+        <v>59.994361262269514</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9352,16 +9364,16 @@
         <v>334</v>
       </c>
       <c r="Y22" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="Z22" t="s">
         <v>411</v>
       </c>
       <c r="AA22">
-        <v>0.99341896335341162</v>
+        <v>0.99695083910621241</v>
       </c>
       <c r="AB22">
-        <v>120.65233852078616</v>
+        <v>55.901283052772143</v>
       </c>
       <c r="AD22" t="s">
         <v>309</v>
@@ -9394,10 +9406,10 @@
         <v>549</v>
       </c>
       <c r="AO22">
-        <v>0.99576662598769528</v>
+        <v>0.99578710491059208</v>
       </c>
       <c r="AP22">
-        <v>77.611856892252987</v>
+        <v>77.236409972479407</v>
       </c>
       <c r="AR22" t="s">
         <v>309</v>
@@ -9424,16 +9436,16 @@
         <v>631</v>
       </c>
       <c r="BA22" t="s">
+        <v>667</v>
+      </c>
+      <c r="BB22" t="s">
         <v>668</v>
       </c>
-      <c r="BB22" t="s">
-        <v>404</v>
-      </c>
       <c r="BC22">
-        <v>0.99010219056094972</v>
+        <v>0.99231435496704667</v>
       </c>
       <c r="BD22">
-        <v>181.45983971592244</v>
+        <v>140.90349227081035</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9498,16 +9510,16 @@
         <v>336</v>
       </c>
       <c r="Y23" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="Z23" t="s">
         <v>412</v>
       </c>
       <c r="AA23">
-        <v>0.99601318900739955</v>
+        <v>0.99758018972146978</v>
       </c>
       <c r="AB23">
-        <v>73.091534864341</v>
+        <v>44.363188439721</v>
       </c>
       <c r="AD23" t="s">
         <v>309</v>
@@ -9540,10 +9552,10 @@
         <v>551</v>
       </c>
       <c r="AO23">
-        <v>0.99796084623978776</v>
+        <v>0.99514523900053742</v>
       </c>
       <c r="AP23">
-        <v>37.384485603890518</v>
+        <v>89.003951656813172</v>
       </c>
       <c r="AR23" t="s">
         <v>309</v>
@@ -9576,10 +9588,10 @@
         <v>670</v>
       </c>
       <c r="BC23">
-        <v>0.99545422785121029</v>
+        <v>0.99229811324031303</v>
       </c>
       <c r="BD23">
-        <v>83.33915606114418</v>
+        <v>141.20125726092687</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9644,16 +9656,16 @@
         <v>338</v>
       </c>
       <c r="Y24" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="Z24" t="s">
         <v>413</v>
       </c>
       <c r="AA24">
-        <v>0.99695083910621241</v>
+        <v>0.99588759895151135</v>
       </c>
       <c r="AB24">
-        <v>55.901283052772143</v>
+        <v>75.394019222291774</v>
       </c>
       <c r="AD24" t="s">
         <v>309</v>
@@ -9686,10 +9698,10 @@
         <v>553</v>
       </c>
       <c r="AO24">
-        <v>0.99546749107529653</v>
+        <v>0.99178008656222316</v>
       </c>
       <c r="AP24">
-        <v>83.095996952896456</v>
+        <v>150.6984130259078</v>
       </c>
       <c r="AR24" t="s">
         <v>309</v>
@@ -9722,10 +9734,10 @@
         <v>672</v>
       </c>
       <c r="BC24">
-        <v>0.99672758029478525</v>
+        <v>0.99582070241731502</v>
       </c>
       <c r="BD24">
-        <v>59.994361262269514</v>
+        <v>76.620455682557321</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9790,16 +9802,16 @@
         <v>340</v>
       </c>
       <c r="Y25" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="Z25" t="s">
         <v>414</v>
       </c>
       <c r="AA25">
-        <v>0.99758018972146978</v>
+        <v>0.99545581573707076</v>
       </c>
       <c r="AB25">
-        <v>44.363188439721</v>
+        <v>83.310044820369185</v>
       </c>
       <c r="AD25" t="s">
         <v>309</v>
@@ -9832,10 +9844,10 @@
         <v>555</v>
       </c>
       <c r="AO25">
-        <v>0.99676762792199902</v>
+        <v>0.99572114955867075</v>
       </c>
       <c r="AP25">
-        <v>59.260154763351615</v>
+        <v>78.445591424369994</v>
       </c>
       <c r="AR25" t="s">
         <v>309</v>
@@ -9936,16 +9948,16 @@
         <v>342</v>
       </c>
       <c r="Y26" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Z26" t="s">
         <v>415</v>
       </c>
       <c r="AA26">
-        <v>0.99021255380204343</v>
+        <v>0.99491802052597356</v>
       </c>
       <c r="AB26">
-        <v>179.43651362920434</v>
+        <v>93.169623690484769</v>
       </c>
       <c r="AD26" t="s">
         <v>309</v>
@@ -9975,13 +9987,13 @@
         <v>556</v>
       </c>
       <c r="AN26" t="s">
-        <v>417</v>
+        <v>557</v>
       </c>
       <c r="AO26">
-        <v>0.99599400380931946</v>
+        <v>0.99606892759117205</v>
       </c>
       <c r="AP26">
-        <v>73.443263495810669</v>
+        <v>72.069660828511601</v>
       </c>
       <c r="AR26" t="s">
         <v>309</v>
@@ -10014,10 +10026,10 @@
         <v>676</v>
       </c>
       <c r="BC26">
-        <v>0.991900752046595</v>
+        <v>0.99545422785121029</v>
       </c>
       <c r="BD26">
-        <v>148.48621247909063</v>
+        <v>83.33915606114418</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10082,16 +10094,16 @@
         <v>344</v>
       </c>
       <c r="Y27" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="Z27" t="s">
         <v>416</v>
       </c>
       <c r="AA27">
-        <v>0.99766238113026029</v>
+        <v>0.9967349730525964</v>
       </c>
       <c r="AB27">
-        <v>42.856345945228725</v>
+        <v>59.858827369067072</v>
       </c>
       <c r="AD27" t="s">
         <v>309</v>
@@ -10118,16 +10130,16 @@
         <v>475</v>
       </c>
       <c r="AM27" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AN27" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AO27">
-        <v>0.99791355837194406</v>
+        <v>0.99511753128449787</v>
       </c>
       <c r="AP27">
-        <v>38.251429847691753</v>
+        <v>89.511926450871471</v>
       </c>
       <c r="AR27" t="s">
         <v>309</v>
@@ -10157,13 +10169,13 @@
         <v>677</v>
       </c>
       <c r="BB27" t="s">
-        <v>564</v>
+        <v>678</v>
       </c>
       <c r="BC27">
-        <v>0.99581145929743231</v>
+        <v>0.991900752046595</v>
       </c>
       <c r="BD27">
-        <v>76.789912880408167</v>
+        <v>148.48621247909063</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10228,16 +10240,16 @@
         <v>346</v>
       </c>
       <c r="Y28" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Z28" t="s">
         <v>417</v>
       </c>
       <c r="AA28">
-        <v>0.99492995157662933</v>
+        <v>0.99648891019904884</v>
       </c>
       <c r="AB28">
-        <v>92.95088776179594</v>
+        <v>64.369979684103896</v>
       </c>
       <c r="AD28" t="s">
         <v>309</v>
@@ -10264,16 +10276,16 @@
         <v>477</v>
       </c>
       <c r="AM28" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AN28" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AO28">
-        <v>0.99517693573038513</v>
+        <v>0.9945106241527748</v>
       </c>
       <c r="AP28">
-        <v>88.42284494294006</v>
+        <v>100.63855719912947</v>
       </c>
       <c r="AR28" t="s">
         <v>309</v>
@@ -10300,16 +10312,16 @@
         <v>643</v>
       </c>
       <c r="BA28" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="BB28" t="s">
-        <v>679</v>
+        <v>597</v>
       </c>
       <c r="BC28">
-        <v>0.99429876975975018</v>
+        <v>0.99581145929743231</v>
       </c>
       <c r="BD28">
-        <v>104.52255440457925</v>
+        <v>76.789912880408167</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10374,16 +10386,16 @@
         <v>348</v>
       </c>
       <c r="Y29" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Z29" t="s">
         <v>418</v>
       </c>
       <c r="AA29">
-        <v>0.99197366299435197</v>
+        <v>0.99849249864903489</v>
       </c>
       <c r="AB29">
-        <v>147.14951177021345</v>
+        <v>27.63752476769432</v>
       </c>
       <c r="AD29" t="s">
         <v>309</v>
@@ -10410,16 +10422,16 @@
         <v>479</v>
       </c>
       <c r="AM29" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN29" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO29">
-        <v>0.99838396904917182</v>
+        <v>0.9915796289555876</v>
       </c>
       <c r="AP29">
-        <v>29.627234098515917</v>
+        <v>154.37346914756148</v>
       </c>
       <c r="AR29" t="s">
         <v>309</v>
@@ -10452,10 +10464,10 @@
         <v>681</v>
       </c>
       <c r="BC29">
-        <v>0.98743040674179927</v>
+        <v>0.99429876975975018</v>
       </c>
       <c r="BD29">
-        <v>230.44254306701379</v>
+        <v>104.52255440457925</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10520,16 +10532,16 @@
         <v>350</v>
       </c>
       <c r="Y30" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="Z30" t="s">
         <v>419</v>
       </c>
       <c r="AA30">
-        <v>0.99519943077301054</v>
+        <v>0.99484635552608569</v>
       </c>
       <c r="AB30">
-        <v>88.010435828140345</v>
+        <v>94.483482021761333</v>
       </c>
       <c r="AD30" t="s">
         <v>309</v>
@@ -10556,16 +10568,16 @@
         <v>481</v>
       </c>
       <c r="AM30" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN30" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO30">
-        <v>0.99468222901836267</v>
+        <v>0.99394383035998857</v>
       </c>
       <c r="AP30">
-        <v>97.492467996683757</v>
+        <v>111.02977673354209</v>
       </c>
       <c r="AR30" t="s">
         <v>309</v>
@@ -10598,10 +10610,10 @@
         <v>683</v>
       </c>
       <c r="BC30">
-        <v>0.99279657608325511</v>
+        <v>0.98743040674179927</v>
       </c>
       <c r="BD30">
-        <v>132.06277180699064</v>
+        <v>230.44254306701379</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10666,16 +10678,16 @@
         <v>352</v>
       </c>
       <c r="Y31" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="Z31" t="s">
         <v>420</v>
       </c>
       <c r="AA31">
-        <v>0.99590738174919524</v>
+        <v>0.99492995157662933</v>
       </c>
       <c r="AB31">
-        <v>75.031334598088264</v>
+        <v>92.95088776179594</v>
       </c>
       <c r="AD31" t="s">
         <v>309</v>
@@ -10702,16 +10714,16 @@
         <v>483</v>
       </c>
       <c r="AM31" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AN31" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO31">
-        <v>0.99399047038285648</v>
+        <v>0.98860885963065015</v>
       </c>
       <c r="AP31">
-        <v>110.17470964763046</v>
+        <v>208.83757343808102</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10776,16 +10788,16 @@
         <v>354</v>
       </c>
       <c r="Y32" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="Z32" t="s">
         <v>421</v>
       </c>
       <c r="AA32">
-        <v>0.99299045119957896</v>
+        <v>0.99197366299435197</v>
       </c>
       <c r="AB32">
-        <v>128.50839467438524</v>
+        <v>147.14951177021345</v>
       </c>
       <c r="AD32" t="s">
         <v>309</v>
@@ -10812,16 +10824,16 @@
         <v>485</v>
       </c>
       <c r="AM32" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AN32" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO32">
-        <v>0.99646273950702013</v>
+        <v>0.99333075340694588</v>
       </c>
       <c r="AP32">
-        <v>64.84977570462992</v>
+        <v>122.26952087265865</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10886,16 +10898,16 @@
         <v>356</v>
       </c>
       <c r="Y33" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="Z33" t="s">
         <v>422</v>
       </c>
       <c r="AA33">
-        <v>0.99456731509164431</v>
+        <v>0.99635918407512603</v>
       </c>
       <c r="AB33">
-        <v>99.599223319854588</v>
+        <v>66.748291956023195</v>
       </c>
       <c r="AD33" t="s">
         <v>309</v>
@@ -10922,16 +10934,16 @@
         <v>487</v>
       </c>
       <c r="AM33" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AN33" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AO33">
-        <v>0.99505112170813059</v>
+        <v>0.99201650479533909</v>
       </c>
       <c r="AP33">
-        <v>90.729435350939028</v>
+        <v>146.36407875211563</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10996,16 +11008,16 @@
         <v>358</v>
       </c>
       <c r="Y34" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="Z34" t="s">
         <v>423</v>
       </c>
       <c r="AA34">
-        <v>0.99466941924265306</v>
+        <v>0.99305283137490208</v>
       </c>
       <c r="AB34">
-        <v>97.727313884694652</v>
+        <v>127.36475812679497</v>
       </c>
       <c r="AD34" t="s">
         <v>309</v>
@@ -11032,16 +11044,16 @@
         <v>489</v>
       </c>
       <c r="AM34" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN34" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO34">
-        <v>0.98687966194564902</v>
+        <v>0.9951764810877296</v>
       </c>
       <c r="AP34">
-        <v>240.53953099643502</v>
+        <v>88.431180058290352</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -11106,16 +11118,16 @@
         <v>360</v>
       </c>
       <c r="Y35" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="Z35" t="s">
         <v>424</v>
       </c>
       <c r="AA35">
-        <v>0.99527761530085967</v>
+        <v>0.99567500995545699</v>
       </c>
       <c r="AB35">
-        <v>86.577052817573119</v>
+        <v>79.29148414995565</v>
       </c>
       <c r="AD35" t="s">
         <v>309</v>
@@ -11142,16 +11154,16 @@
         <v>491</v>
       </c>
       <c r="AM35" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AN35" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AO35">
-        <v>0.99431286945280239</v>
+        <v>0.99247550518926964</v>
       </c>
       <c r="AP35">
-        <v>104.26406003195649</v>
+        <v>137.94907153005732</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -11216,16 +11228,16 @@
         <v>362</v>
       </c>
       <c r="Y36" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="Z36" t="s">
         <v>425</v>
       </c>
       <c r="AA36">
-        <v>0.9951066982538278</v>
+        <v>0.99519943077301054</v>
       </c>
       <c r="AB36">
-        <v>89.710532013157362</v>
+        <v>88.010435828140345</v>
       </c>
       <c r="AD36" t="s">
         <v>309</v>
@@ -11252,16 +11264,16 @@
         <v>493</v>
       </c>
       <c r="AM36" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AN36" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AO36">
-        <v>0.99692167417445865</v>
+        <v>0.98687966194564902</v>
       </c>
       <c r="AP36">
-        <v>56.43597346825765</v>
+        <v>240.53953099643502</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -11326,16 +11338,16 @@
         <v>364</v>
       </c>
       <c r="Y37" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="Z37" t="s">
         <v>426</v>
       </c>
       <c r="AA37">
-        <v>0.99681791473814529</v>
+        <v>0.99398571695284077</v>
       </c>
       <c r="AB37">
-        <v>58.33822980066963</v>
+        <v>110.2618558645854</v>
       </c>
       <c r="AD37" t="s">
         <v>309</v>
@@ -11362,16 +11374,16 @@
         <v>495</v>
       </c>
       <c r="AM37" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AN37" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AO37">
-        <v>0.99830064150468256</v>
+        <v>0.99431286945280239</v>
       </c>
       <c r="AP37">
-        <v>31.154905747485419</v>
+        <v>104.26406003195649</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -11436,16 +11448,16 @@
         <v>366</v>
       </c>
       <c r="Y38" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="Z38" t="s">
         <v>427</v>
       </c>
       <c r="AA38">
-        <v>0.98958063849079669</v>
+        <v>0.99726845868655478</v>
       </c>
       <c r="AB38">
-        <v>191.02162766872783</v>
+        <v>50.078257413162468</v>
       </c>
       <c r="AD38" t="s">
         <v>309</v>
@@ -11472,16 +11484,16 @@
         <v>497</v>
       </c>
       <c r="AM38" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN38" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO38">
-        <v>0.99788320682147802</v>
+        <v>0.99692167417445865</v>
       </c>
       <c r="AP38">
-        <v>38.807874939569167</v>
+        <v>56.43597346825765</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -11546,16 +11558,16 @@
         <v>368</v>
       </c>
       <c r="Y39" t="s">
-        <v>272</v>
+        <v>298</v>
       </c>
       <c r="Z39" t="s">
         <v>428</v>
       </c>
       <c r="AA39">
-        <v>0.98298990306503153</v>
+        <v>0.99615584710269711</v>
       </c>
       <c r="AB39">
-        <v>311.85177714108931</v>
+        <v>70.476136450553028</v>
       </c>
       <c r="AD39" t="s">
         <v>309</v>
@@ -11582,16 +11594,16 @@
         <v>499</v>
       </c>
       <c r="AM39" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AN39" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AO39">
-        <v>0.99677069953771458</v>
+        <v>0.99830064150468256</v>
       </c>
       <c r="AP39">
-        <v>59.203841808565592</v>
+        <v>31.154905747485419</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -11656,16 +11668,16 @@
         <v>370</v>
       </c>
       <c r="Y40" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="Z40" t="s">
         <v>429</v>
       </c>
       <c r="AA40">
-        <v>0.99495781957805363</v>
+        <v>0.99599518539997189</v>
       </c>
       <c r="AB40">
-        <v>92.439974402351027</v>
+        <v>73.421601000514329</v>
       </c>
       <c r="AD40" t="s">
         <v>309</v>
@@ -11692,16 +11704,16 @@
         <v>501</v>
       </c>
       <c r="AM40" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AN40" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO40">
-        <v>0.99824683646529189</v>
+        <v>0.99788320682147802</v>
       </c>
       <c r="AP40">
-        <v>32.141331469648897</v>
+        <v>38.807874939569167</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11766,16 +11778,16 @@
         <v>372</v>
       </c>
       <c r="Y41" t="s">
-        <v>289</v>
+        <v>266</v>
       </c>
       <c r="Z41" t="s">
         <v>430</v>
       </c>
       <c r="AA41">
-        <v>0.99564550658027606</v>
+        <v>0.99294071263677341</v>
       </c>
       <c r="AB41">
-        <v>79.832379361605149</v>
+        <v>129.42026832582172</v>
       </c>
       <c r="AD41" t="s">
         <v>309</v>
@@ -11802,16 +11814,16 @@
         <v>503</v>
       </c>
       <c r="AM41" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN41" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO41">
-        <v>0.99504825389388352</v>
+        <v>0.99677069953771458</v>
       </c>
       <c r="AP41">
-        <v>90.782011945468795</v>
+        <v>59.203841808565592</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11876,16 +11888,16 @@
         <v>374</v>
       </c>
       <c r="Y42" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="Z42" t="s">
         <v>431</v>
       </c>
       <c r="AA42">
-        <v>0.99567500995545699</v>
+        <v>0.99535442409010222</v>
       </c>
       <c r="AB42">
-        <v>79.29148414995565</v>
+        <v>85.168891681458845</v>
       </c>
       <c r="AD42" t="s">
         <v>309</v>
@@ -11912,16 +11924,16 @@
         <v>505</v>
       </c>
       <c r="AM42" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN42" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO42">
-        <v>0.99606892759117205</v>
+        <v>0.99824683646529189</v>
       </c>
       <c r="AP42">
-        <v>72.069660828511601</v>
+        <v>32.141331469648897</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11986,16 +11998,16 @@
         <v>376</v>
       </c>
       <c r="Y43" t="s">
-        <v>270</v>
+        <v>305</v>
       </c>
       <c r="Z43" t="s">
         <v>432</v>
       </c>
       <c r="AA43">
-        <v>0.99588759895151135</v>
+        <v>0.99309463181702251</v>
       </c>
       <c r="AB43">
-        <v>75.394019222291774</v>
+        <v>126.5984166879211</v>
       </c>
       <c r="AD43" t="s">
         <v>309</v>
@@ -12022,16 +12034,16 @@
         <v>507</v>
       </c>
       <c r="AM43" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AN43" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO43">
-        <v>0.99511753128449787</v>
+        <v>0.99587491663731742</v>
       </c>
       <c r="AP43">
-        <v>89.511926450871471</v>
+        <v>75.626528315847352</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -12096,16 +12108,16 @@
         <v>378</v>
       </c>
       <c r="Y44" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="Z44" t="s">
         <v>433</v>
       </c>
       <c r="AA44">
-        <v>0.99545581573707076</v>
+        <v>0.99827081845920873</v>
       </c>
       <c r="AB44">
-        <v>83.310044820369185</v>
+        <v>31.701661581174136</v>
       </c>
       <c r="AD44" t="s">
         <v>309</v>
@@ -12132,16 +12144,16 @@
         <v>509</v>
       </c>
       <c r="AM44" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN44" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO44">
-        <v>0.9945106241527748</v>
+        <v>0.99572967547870339</v>
       </c>
       <c r="AP44">
-        <v>100.63855719912947</v>
+        <v>78.289282890438841</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -12206,16 +12218,16 @@
         <v>380</v>
       </c>
       <c r="Y45" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="Z45" t="s">
         <v>434</v>
       </c>
       <c r="AA45">
-        <v>0.99491802052597356</v>
+        <v>0.99021255380204343</v>
       </c>
       <c r="AB45">
-        <v>93.169623690484769</v>
+        <v>179.43651362920434</v>
       </c>
       <c r="AD45" t="s">
         <v>309</v>
@@ -12242,16 +12254,16 @@
         <v>511</v>
       </c>
       <c r="AM45" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN45" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AO45">
-        <v>0.9915796289555876</v>
+        <v>0.99505112170813059</v>
       </c>
       <c r="AP45">
-        <v>154.37346914756148</v>
+        <v>90.729435350939028</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -12316,16 +12328,16 @@
         <v>382</v>
       </c>
       <c r="Y46" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="Z46" t="s">
         <v>435</v>
       </c>
       <c r="AA46">
-        <v>0.9967349730525964</v>
+        <v>0.99766238113026029</v>
       </c>
       <c r="AB46">
-        <v>59.858827369067072</v>
+        <v>42.856345945228725</v>
       </c>
       <c r="AD46" t="s">
         <v>309</v>
@@ -12352,16 +12364,16 @@
         <v>513</v>
       </c>
       <c r="AM46" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AN46" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AO46">
-        <v>0.99394383035998857</v>
+        <v>0.99468222901836267</v>
       </c>
       <c r="AP46">
-        <v>111.02977673354209</v>
+        <v>97.492467996683757</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -12426,16 +12438,16 @@
         <v>384</v>
       </c>
       <c r="Y47" t="s">
-        <v>302</v>
+        <v>284</v>
       </c>
       <c r="Z47" t="s">
         <v>436</v>
       </c>
       <c r="AA47">
-        <v>0.99648891019904884</v>
+        <v>0.99331672850632224</v>
       </c>
       <c r="AB47">
-        <v>64.369979684103896</v>
+        <v>122.52664405075954</v>
       </c>
       <c r="AD47" t="s">
         <v>309</v>
@@ -12462,16 +12474,16 @@
         <v>515</v>
       </c>
       <c r="AM47" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AN47" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AO47">
-        <v>0.99514523900053742</v>
+        <v>0.99399047038285648</v>
       </c>
       <c r="AP47">
-        <v>89.003951656813172</v>
+        <v>110.17470964763046</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -12536,16 +12548,16 @@
         <v>386</v>
       </c>
       <c r="Y48" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="Z48" t="s">
         <v>437</v>
       </c>
       <c r="AA48">
-        <v>0.99849249864903489</v>
+        <v>0.99698458324869177</v>
       </c>
       <c r="AB48">
-        <v>27.63752476769432</v>
+        <v>55.282640440651299</v>
       </c>
       <c r="AD48" t="s">
         <v>309</v>
@@ -12572,16 +12584,16 @@
         <v>517</v>
       </c>
       <c r="AM48" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN48" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO48">
-        <v>0.99178008656222316</v>
+        <v>0.99646273950702013</v>
       </c>
       <c r="AP48">
-        <v>150.6984130259078</v>
+        <v>64.84977570462992</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12646,16 +12658,16 @@
         <v>388</v>
       </c>
       <c r="Y49" t="s">
-        <v>295</v>
+        <v>272</v>
       </c>
       <c r="Z49" t="s">
         <v>438</v>
       </c>
       <c r="AA49">
-        <v>0.99484635552608569</v>
+        <v>0.98298990306503153</v>
       </c>
       <c r="AB49">
-        <v>94.483482021761333</v>
+        <v>311.85177714108931</v>
       </c>
       <c r="AD49" t="s">
         <v>309</v>
@@ -12682,16 +12694,16 @@
         <v>519</v>
       </c>
       <c r="AM49" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AN49" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AO49">
-        <v>0.99572114955867075</v>
+        <v>0.99604689649306255</v>
       </c>
       <c r="AP49">
-        <v>78.445591424369994</v>
+        <v>72.473564293852363</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12756,16 +12768,16 @@
         <v>390</v>
       </c>
       <c r="Y50" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="Z50" t="s">
         <v>439</v>
       </c>
       <c r="AA50">
-        <v>0.99464845307754257</v>
+        <v>0.99495781957805363</v>
       </c>
       <c r="AB50">
-        <v>98.111693578387175</v>
+        <v>92.439974402351027</v>
       </c>
       <c r="AD50" t="s">
         <v>309</v>
@@ -12792,16 +12804,16 @@
         <v>521</v>
       </c>
       <c r="AM50" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AN50" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AO50">
-        <v>0.99578710491059208</v>
+        <v>0.99164055829901554</v>
       </c>
       <c r="AP50">
-        <v>77.236409972479407</v>
+        <v>153.25643118471478</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -12866,16 +12878,16 @@
         <v>392</v>
       </c>
       <c r="Y51" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="Z51" t="s">
         <v>440</v>
       </c>
       <c r="AA51">
-        <v>0.99446824002516876</v>
+        <v>0.99564550658027606</v>
       </c>
       <c r="AB51">
-        <v>101.41559953857198</v>
+        <v>79.832379361605149</v>
       </c>
       <c r="AD51" t="s">
         <v>309</v>
@@ -12902,16 +12914,16 @@
         <v>523</v>
       </c>
       <c r="AM51" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AN51" t="s">
-        <v>606</v>
+        <v>420</v>
       </c>
       <c r="AO51">
-        <v>0.99604689649306255</v>
+        <v>0.99599400380931946</v>
       </c>
       <c r="AP51">
-        <v>72.473564293852363</v>
+        <v>73.443263495810669</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -12976,16 +12988,16 @@
         <v>394</v>
       </c>
       <c r="Y52" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="Z52" t="s">
         <v>441</v>
       </c>
       <c r="AA52">
-        <v>0.99615584710269711</v>
+        <v>0.99464845307754257</v>
       </c>
       <c r="AB52">
-        <v>70.476136450553028</v>
+        <v>98.111693578387175</v>
       </c>
       <c r="AD52" t="s">
         <v>309</v>
@@ -13018,10 +13030,10 @@
         <v>608</v>
       </c>
       <c r="AO52">
-        <v>0.99164055829901554</v>
+        <v>0.99791355837194406</v>
       </c>
       <c r="AP52">
-        <v>153.25643118471478</v>
+        <v>38.251429847691753</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13086,16 +13098,16 @@
         <v>396</v>
       </c>
       <c r="Y53" t="s">
-        <v>307</v>
+        <v>273</v>
       </c>
       <c r="Z53" t="s">
         <v>442</v>
       </c>
       <c r="AA53">
-        <v>0.99599518539997189</v>
+        <v>0.99446824002516876</v>
       </c>
       <c r="AB53">
-        <v>73.421601000514329</v>
+        <v>101.41559953857198</v>
       </c>
     </row>
   </sheetData>
@@ -13104,7 +13116,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B87E366-61FA-415C-9F0F-2BF6A7932EA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BE2951F-9BD9-4E0B-A53B-FFC9678D92E4}">
   <dimension ref="B9:Z52"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -13216,7 +13228,7 @@
         <v>684</v>
       </c>
       <c r="K11" t="s">
-        <v>556</v>
+        <v>606</v>
       </c>
       <c r="L11">
         <v>9.3348685452622586</v>
@@ -13249,7 +13261,7 @@
         <v>768</v>
       </c>
       <c r="X11" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="Y11">
         <v>22.356000000000002</v>
@@ -13284,7 +13296,7 @@
         <v>686</v>
       </c>
       <c r="K12" t="s">
-        <v>565</v>
+        <v>598</v>
       </c>
       <c r="L12">
         <v>41.38517014727136</v>
@@ -13317,7 +13329,7 @@
         <v>770</v>
       </c>
       <c r="X12" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="Y12">
         <v>71.144999999999996</v>
@@ -13352,7 +13364,7 @@
         <v>688</v>
       </c>
       <c r="K13" t="s">
-        <v>597</v>
+        <v>550</v>
       </c>
       <c r="L13">
         <v>18.676901648902387</v>
@@ -13385,7 +13397,7 @@
         <v>772</v>
       </c>
       <c r="X13" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="Y13">
         <v>20.269500000000001</v>
@@ -13420,7 +13432,7 @@
         <v>690</v>
       </c>
       <c r="K14" t="s">
-        <v>542</v>
+        <v>590</v>
       </c>
       <c r="L14">
         <v>17.522570055216363</v>
@@ -13453,7 +13465,7 @@
         <v>774</v>
       </c>
       <c r="X14" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="Y14">
         <v>91.751999999999995</v>
@@ -13488,7 +13500,7 @@
         <v>692</v>
       </c>
       <c r="K15" t="s">
-        <v>595</v>
+        <v>564</v>
       </c>
       <c r="L15">
         <v>13.570215224493221</v>
@@ -13521,7 +13533,7 @@
         <v>776</v>
       </c>
       <c r="X15" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="Y15">
         <v>9.2227499999999996</v>
@@ -13556,7 +13568,7 @@
         <v>694</v>
       </c>
       <c r="K16" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="L16">
         <v>59.282276232111244</v>
@@ -13589,7 +13601,7 @@
         <v>778</v>
       </c>
       <c r="X16" t="s">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="Y16">
         <v>66.892499999999998</v>
@@ -13624,7 +13636,7 @@
         <v>696</v>
       </c>
       <c r="K17" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="L17">
         <v>7.6187600542008829</v>
@@ -13657,7 +13669,7 @@
         <v>780</v>
       </c>
       <c r="X17" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="Y17">
         <v>16.734749999999998</v>
@@ -13692,7 +13704,7 @@
         <v>698</v>
       </c>
       <c r="K18" t="s">
-        <v>554</v>
+        <v>531</v>
       </c>
       <c r="L18">
         <v>13.317870473911716</v>
@@ -13725,7 +13737,7 @@
         <v>782</v>
       </c>
       <c r="X18" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="Y18">
         <v>6.2925000000000004</v>
@@ -13760,7 +13772,7 @@
         <v>700</v>
       </c>
       <c r="K19" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="L19">
         <v>15.766767829784982</v>
@@ -13793,7 +13805,7 @@
         <v>784</v>
       </c>
       <c r="X19" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="Y19">
         <v>8.7997499999999995</v>
@@ -13828,7 +13840,7 @@
         <v>702</v>
       </c>
       <c r="K20" t="s">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="L20">
         <v>1.242396749224558</v>
@@ -13861,7 +13873,7 @@
         <v>786</v>
       </c>
       <c r="X20" t="s">
-        <v>653</v>
+        <v>658</v>
       </c>
       <c r="Y20">
         <v>12.29025</v>
@@ -13896,7 +13908,7 @@
         <v>704</v>
       </c>
       <c r="K21" t="s">
-        <v>557</v>
+        <v>607</v>
       </c>
       <c r="L21">
         <v>11.016586435503244</v>
@@ -13929,7 +13941,7 @@
         <v>788</v>
       </c>
       <c r="X21" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="Y21">
         <v>7.4317500000000001</v>
@@ -13964,7 +13976,7 @@
         <v>706</v>
       </c>
       <c r="K22" t="s">
-        <v>601</v>
+        <v>554</v>
       </c>
       <c r="L22">
         <v>6.1733535033999489</v>
@@ -13997,7 +14009,7 @@
         <v>790</v>
       </c>
       <c r="X22" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="Y22">
         <v>21.263249999999999</v>
@@ -14032,7 +14044,7 @@
         <v>708</v>
       </c>
       <c r="K23" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="L23">
         <v>4.8541340927283274</v>
@@ -14100,7 +14112,7 @@
         <v>710</v>
       </c>
       <c r="K24" t="s">
-        <v>593</v>
+        <v>562</v>
       </c>
       <c r="L24">
         <v>13.114783900591691</v>
@@ -14133,7 +14145,7 @@
         <v>794</v>
       </c>
       <c r="X24" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="Y24">
         <v>72.104249999999993</v>
@@ -14168,7 +14180,7 @@
         <v>712</v>
       </c>
       <c r="K25" t="s">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="L25">
         <v>2.8310936025572326</v>
@@ -14201,7 +14213,7 @@
         <v>796</v>
       </c>
       <c r="X25" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="Y25">
         <v>7.6185</v>
@@ -14236,7 +14248,7 @@
         <v>714</v>
       </c>
       <c r="K26" t="s">
-        <v>533</v>
+        <v>572</v>
       </c>
       <c r="L26">
         <v>9.8725175016467617</v>
@@ -14269,7 +14281,7 @@
         <v>798</v>
       </c>
       <c r="X26" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="Y26">
         <v>38.655749999999998</v>
@@ -14304,7 +14316,7 @@
         <v>716</v>
       </c>
       <c r="K27" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="L27">
         <v>2.1088679510249264</v>
@@ -14337,7 +14349,7 @@
         <v>800</v>
       </c>
       <c r="X27" t="s">
-        <v>668</v>
+        <v>653</v>
       </c>
       <c r="Y27">
         <v>25.178999999999998</v>
@@ -14372,7 +14384,7 @@
         <v>718</v>
       </c>
       <c r="K28" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="L28">
         <v>3.109672262974355</v>
@@ -14405,7 +14417,7 @@
         <v>802</v>
       </c>
       <c r="X28" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="Y28">
         <v>30.076499999999999</v>
@@ -14440,7 +14452,7 @@
         <v>720</v>
       </c>
       <c r="K29" t="s">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="L29">
         <v>2.2821221811848558</v>
@@ -14473,7 +14485,7 @@
         <v>804</v>
       </c>
       <c r="X29" t="s">
-        <v>682</v>
+        <v>651</v>
       </c>
       <c r="Y29">
         <v>69.197999999999993</v>
@@ -14508,7 +14520,7 @@
         <v>722</v>
       </c>
       <c r="K30" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="L30">
         <v>6.0746622584304504</v>
@@ -14541,7 +14553,7 @@
         <v>806</v>
       </c>
       <c r="X30" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="Y30">
         <v>24.058499999999999</v>
@@ -14576,7 +14588,7 @@
         <v>724</v>
       </c>
       <c r="K31" t="s">
-        <v>535</v>
+        <v>574</v>
       </c>
       <c r="L31">
         <v>16.31886018972364</v>
@@ -14611,7 +14623,7 @@
         <v>726</v>
       </c>
       <c r="K32" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="L32">
         <v>1.1455000262712256</v>
@@ -14646,7 +14658,7 @@
         <v>728</v>
       </c>
       <c r="K33" t="s">
-        <v>569</v>
+        <v>594</v>
       </c>
       <c r="L33">
         <v>11.364861678100382</v>
@@ -14681,7 +14693,7 @@
         <v>730</v>
       </c>
       <c r="K34" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="L34">
         <v>7.8135900005455872</v>
@@ -14716,7 +14728,7 @@
         <v>732</v>
       </c>
       <c r="K35" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="L35">
         <v>1.3654604103287289</v>
@@ -14751,7 +14763,7 @@
         <v>734</v>
       </c>
       <c r="K36" t="s">
-        <v>552</v>
+        <v>529</v>
       </c>
       <c r="L36">
         <v>2.222863284436507</v>
@@ -14786,7 +14798,7 @@
         <v>736</v>
       </c>
       <c r="K37" t="s">
-        <v>603</v>
+        <v>548</v>
       </c>
       <c r="L37">
         <v>9.7399044969678972</v>
@@ -14821,7 +14833,7 @@
         <v>738</v>
       </c>
       <c r="K38" t="s">
-        <v>567</v>
+        <v>600</v>
       </c>
       <c r="L38">
         <v>11.047069314867423</v>
@@ -14856,7 +14868,7 @@
         <v>740</v>
       </c>
       <c r="K39" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
       <c r="L39">
         <v>26.291803917155487</v>
@@ -14891,7 +14903,7 @@
         <v>742</v>
       </c>
       <c r="K40" t="s">
-        <v>531</v>
+        <v>570</v>
       </c>
       <c r="L40">
         <v>13.093319261533304</v>
@@ -14926,7 +14938,7 @@
         <v>744</v>
       </c>
       <c r="K41" t="s">
-        <v>544</v>
+        <v>592</v>
       </c>
       <c r="L41">
         <v>12.996823777257559</v>
@@ -14961,7 +14973,7 @@
         <v>746</v>
       </c>
       <c r="K42" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="L42">
         <v>24.694469143848224</v>
@@ -14996,7 +15008,7 @@
         <v>748</v>
       </c>
       <c r="K43" t="s">
-        <v>599</v>
+        <v>552</v>
       </c>
       <c r="L43">
         <v>28.748060997363154</v>
@@ -15031,7 +15043,7 @@
         <v>750</v>
       </c>
       <c r="K44" t="s">
-        <v>591</v>
+        <v>560</v>
       </c>
       <c r="L44">
         <v>27.436549011428941</v>
@@ -15066,7 +15078,7 @@
         <v>752</v>
       </c>
       <c r="K45" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="L45">
         <v>10.919135648131764</v>
@@ -15101,7 +15113,7 @@
         <v>754</v>
       </c>
       <c r="K46" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="L46">
         <v>33.912640160809843</v>
@@ -15136,7 +15148,7 @@
         <v>756</v>
       </c>
       <c r="K47" t="s">
-        <v>585</v>
+        <v>527</v>
       </c>
       <c r="L47">
         <v>22.57598984879677</v>
@@ -15171,7 +15183,7 @@
         <v>758</v>
       </c>
       <c r="K48" t="s">
-        <v>563</v>
+        <v>596</v>
       </c>
       <c r="L48">
         <v>20.256717029567771</v>
@@ -15206,7 +15218,7 @@
         <v>760</v>
       </c>
       <c r="K49" t="s">
-        <v>573</v>
+        <v>578</v>
       </c>
       <c r="L49">
         <v>62.791395577971592</v>
@@ -15241,7 +15253,7 @@
         <v>762</v>
       </c>
       <c r="K50" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="L50">
         <v>37.678782480143312</v>
@@ -15276,7 +15288,7 @@
         <v>764</v>
       </c>
       <c r="K51" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="L51">
         <v>41.926633570495007</v>
@@ -15311,7 +15323,7 @@
         <v>766</v>
       </c>
       <c r="K52" t="s">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="L52">
         <v>47.281374191365337</v>
@@ -15326,9 +15338,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AC06812-3E21-46B1-805D-E93591A303C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D8352A-7DB6-49F1-BAB5-47A58B4391A4}">
   <dimension ref="B9:P73"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="29.796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="9" spans="2:16">
       <c r="B9" t="s">
@@ -16314,7 +16329,7 @@
         <v>819</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D38" t="s">
         <v>19</v>
@@ -16337,7 +16352,7 @@
         <v>819</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
@@ -16360,7 +16375,7 @@
         <v>819</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D40" t="s">
         <v>19</v>
@@ -17143,7 +17158,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30FDF600-58CA-46FD-851C-C97F038B9D2B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{978C7A1F-94A8-429F-A77B-D459C1490F03}">
   <dimension ref="B2:M19"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_ZAF_grids_kan/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\VerveStacks_ZAF_grids_kan\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979904E6-EF16-40D5-89B9-92C6506E9657}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E16CEFA-EE87-41E1-B717-99E4E07FF732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -2773,9 +2773,6 @@
     <t>Transformer: e_w92348290-400_ZAF → e_w92348290-765_ZAF</t>
   </si>
   <si>
-    <t>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</t>
-  </si>
-  <si>
     <t>pcg</t>
   </si>
   <si>
@@ -2786,6 +2783,9 @@
   </si>
   <si>
     <t>*NCAP_AFC</t>
+  </si>
+  <si>
+    <t>e_ZA11-400_ZAF</t>
   </si>
 </sst>
 </file>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="L27" t="str">
         <f>$V$28</f>
-        <v>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</v>
+        <v>e_ZA11-400_ZAF</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="K28" t="str">
         <f>$V$28</f>
-        <v>e_ZA11-400_ZAF,e_ZA40-400_ZAF,e_ZA41-400_ZAF,e_ZA44-400_ZAF,e_w120941269-400_ZAF,e_w169647963-400_ZAF,e_w169789536-400_ZAF,e_w182042518-400_ZAF,e_w219384657-400_ZAF,e_w219384657-765_ZAF,e_w545652232-400_ZAF,e_w62193952-400_ZAF,e_w62218063-400_ZAF,e_w836844162-400_ZAF,e_w90454383-400_ZAF</v>
+        <v>e_ZA11-400_ZAF</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>50</v>
       </c>
       <c r="V28" s="147" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
   </sheetData>
@@ -4874,7 +4874,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>1</v>
@@ -4949,13 +4949,13 @@
         <v>14</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>62</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>49</v>
@@ -5003,13 +5003,13 @@
         <v>14</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J11" s="6" t="s">
         <v>62</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="L11" s="6" t="s">
         <v>66</v>
@@ -5208,7 +5208,7 @@
         <v>60</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>49</v>
@@ -5243,7 +5243,7 @@
         <v>60</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="L19" t="s">
         <v>66</v>
